--- a/src/attributions/attributions_saliency_traj_313.xlsx
+++ b/src/attributions/attributions_saliency_traj_313.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.347492788132513e-06</v>
+        <v>4.482918924963997e-09</v>
       </c>
       <c r="B4" t="n">
-        <v>2.407346801192034e-05</v>
+        <v>1.220771039811552e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>3.753085820790147e-06</v>
+        <v>5.645917511287735e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.055329903465463e-06</v>
+        <v>8.86508733088931e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>5.037562459619949e-06</v>
+        <v>5.676987768765684e-10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.431836219329853e-05</v>
+        <v>1.454055764682494e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>2.360447979299352e-06</v>
+        <v>1.631654811262706e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.597080533130793e-06</v>
+        <v>1.095299051456777e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.853696964346454e-07</v>
+        <v>8.335329648723189e-11</v>
       </c>
       <c r="J4" t="n">
-        <v>1.014619920169935e-05</v>
+        <v>1.162592244696725e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>1.804707608243916e-05</v>
+        <v>6.000354435542476e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>2.474063421686878e-06</v>
+        <v>1.001883909168555e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.063123131141765e-06</v>
+        <v>8.70399219365936e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.465445272217039e-06</v>
+        <v>5.121453483525329e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.447623708372703e-05</v>
+        <v>3.928994907198557e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>3.094939984293887e-07</v>
+        <v>2.066751392248989e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.040595846774522e-06</v>
+        <v>7.67614682928297e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>5.306995262799319e-06</v>
+        <v>7.514243449691094e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>3.950373184125056e-08</v>
+        <v>2.903219886718489e-10</v>
       </c>
       <c r="T4" t="n">
-        <v>2.323488388356054e-06</v>
+        <v>1.378763148096596e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.155421074372498e-07</v>
+        <v>3.19883630695017e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>1.374933162878733e-06</v>
+        <v>5.529133151327414e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>6.627416041737888e-06</v>
+        <v>1.717183550908885e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>3.451678139754222e-06</v>
+        <v>5.1635975495401e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.713212554932397e-06</v>
+        <v>8.782026661435793e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.077218598766194e-06</v>
+        <v>7.39895078538666e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.338470939226681e-07</v>
+        <v>1.146201356050369e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.57073224929627e-06</v>
+        <v>5.596451080336351e-10</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.257376306464721e-07</v>
+        <v>2.467982707088368e-09</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.871104586825822e-06</v>
+        <v>4.930219787979695e-09</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.617769602395128e-06</v>
+        <v>2.47623965776711e-09</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.321636985579971e-06</v>
+        <v>5.503390632100036e-09</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.899808350775857e-06</v>
+        <v>1.282412309677738e-08</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.491827217454556e-06</v>
+        <v>7.356237841094071e-10</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.316426955279894e-08</v>
+        <v>7.214109309927608e-09</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6.566364163518301e-08</v>
+        <v>4.392501917749314e-10</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.602967689810612e-08</v>
+        <v>1.23583920874637e-11</v>
       </c>
       <c r="AL4" t="n">
-        <v>9.308697599408333e-07</v>
+        <v>9.755996011051593e-10</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.944505922641838e-06</v>
+        <v>2.386728148451311e-09</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.850148237281246e-06</v>
+        <v>6.389947238005789e-09</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.740002630867821e-07</v>
+        <v>5.066044028723127e-09</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.771186468133237e-06</v>
+        <v>2.97477420474479e-09</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.862309313262813e-06</v>
+        <v>4.539251641233477e-09</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.688467131723883e-06</v>
+        <v>2.14836282097508e-09</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.66160542803118e-06</v>
+        <v>2.474542126762458e-09</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.077458477993787e-07</v>
+        <v>3.544686766332461e-10</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.55672169564059e-06</v>
+        <v>1.812061256600828e-08</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.569979632331524e-06</v>
+        <v>5.102150701929986e-09</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.966354830074124e-06</v>
+        <v>2.500561091522968e-09</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.414525053813122e-06</v>
+        <v>4.889910698580024e-09</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.769101335317828e-06</v>
+        <v>5.401103564395271e-09</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.078415132535156e-06</v>
+        <v>3.970084261339935e-09</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.7378687163e-06</v>
+        <v>1.070553068416302e-08</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.033795706462115e-05</v>
+        <v>1.265890503532319e-09</v>
       </c>
       <c r="BC4" t="n">
-        <v>9.614025657356251e-06</v>
+        <v>4.115201512888689e-09</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.639771982008824e-06</v>
+        <v>2.691094902473878e-09</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.716529254736088e-06</v>
+        <v>4.788527796506514e-09</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.937755769176874e-07</v>
+        <v>2.48903342381368e-10</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.982946731819538e-06</v>
+        <v>5.323173013493943e-09</v>
       </c>
       <c r="BH4" t="n">
-        <v>1.162244552688207e-05</v>
+        <v>6.021143583723187e-09</v>
       </c>
       <c r="BI4" t="n">
-        <v>6.943434982531471e-06</v>
+        <v>5.437929218032878e-09</v>
       </c>
       <c r="BJ4" t="n">
-        <v>6.764338991160912e-07</v>
+        <v>1.24886110342004e-08</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.674177373293787e-06</v>
+        <v>6.231406501910897e-10</v>
       </c>
       <c r="BL4" t="n">
-        <v>4.895867959930911e-07</v>
+        <v>6.478711789270619e-09</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.982532798043394e-07</v>
+        <v>5.181733930825771e-10</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.193981339994934e-07</v>
+        <v>3.338775700356678e-09</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.056605237361509e-06</v>
+        <v>1.024287321627071e-10</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.698436209262582e-06</v>
+        <v>5.264820579498064e-09</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.262318947847234e-07</v>
+        <v>2.474500160332127e-09</v>
       </c>
       <c r="BR4" t="n">
-        <v>3.1084896363609e-06</v>
+        <v>1.488435152907641e-09</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.78010122908745e-06</v>
+        <v>7.748728880763167e-10</v>
       </c>
       <c r="BT4" t="n">
-        <v>4.634304332284955e-06</v>
+        <v>5.000343250571859e-09</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.459926238567277e-06</v>
+        <v>2.989557490451489e-10</v>
       </c>
       <c r="BV4" t="n">
-        <v>5.840432550030528e-06</v>
+        <v>1.902261903552471e-09</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.014603862538934e-06</v>
+        <v>3.881790000548335e-09</v>
       </c>
       <c r="BX4" t="n">
-        <v>1.443475639462122e-06</v>
+        <v>1.37584814652314e-08</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.097826033306774e-06</v>
+        <v>1.239158109456184e-08</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.176533709847718e-06</v>
+        <v>3.682805838067793e-09</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.680844090718892e-06</v>
+        <v>2.152691802592699e-09</v>
       </c>
       <c r="CB4" t="n">
-        <v>1.545778786748997e-06</v>
+        <v>1.646707770142086e-09</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.171461230522254e-06</v>
+        <v>1.406117999813716e-10</v>
       </c>
       <c r="CD4" t="n">
-        <v>9.472024657952716e-07</v>
+        <v>5.407503889109933e-10</v>
       </c>
       <c r="CE4" t="n">
-        <v>2.789574409689521e-06</v>
+        <v>9.256515554056932e-10</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.503936573499232e-06</v>
+        <v>2.034395762962049e-09</v>
       </c>
       <c r="CG4" t="n">
-        <v>5.866473884452716e-08</v>
+        <v>6.940653607401259e-10</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.650902390792908e-06</v>
+        <v>4.082958415807525e-10</v>
       </c>
       <c r="CI4" t="n">
-        <v>4.475617515709018e-06</v>
+        <v>7.324565398647565e-10</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.413289737683954e-06</v>
+        <v>7.30821514416391e-10</v>
       </c>
       <c r="CK4" t="n">
-        <v>5.719950308957777e-07</v>
+        <v>1.543179806162698e-09</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.936510782092228e-06</v>
+        <v>3.421270156067635e-09</v>
       </c>
       <c r="CM4" t="n">
-        <v>3.86550891562365e-06</v>
+        <v>1.079139000381701e-10</v>
       </c>
       <c r="CN4" t="n">
-        <v>3.511105433062767e-06</v>
+        <v>1.222496148756136e-08</v>
       </c>
       <c r="CO4" t="n">
-        <v>3.742843546206132e-06</v>
+        <v>2.175706725893178e-09</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.17459592022351e-06</v>
+        <v>5.040922124166514e-10</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.099397079291521e-06</v>
+        <v>4.7764263655381e-09</v>
       </c>
       <c r="CR4" t="n">
-        <v>7.350224677793449e-07</v>
+        <v>5.844707384738967e-09</v>
       </c>
       <c r="CS4" t="n">
-        <v>1.686088126007235e-06</v>
+        <v>1.044459718713142e-08</v>
       </c>
       <c r="CT4" t="n">
-        <v>5.659402404489811e-07</v>
+        <v>4.157273192362254e-09</v>
       </c>
       <c r="CU4" t="n">
-        <v>4.702181740867672e-06</v>
+        <v>2.608854465790955e-09</v>
       </c>
       <c r="CV4" t="n">
-        <v>4.720079971320956e-07</v>
+        <v>9.831354619294075e-10</v>
       </c>
       <c r="CW4" t="n">
-        <v>3.909387032763334e-06</v>
+        <v>1.07578101982142e-09</v>
       </c>
       <c r="CX4" t="n">
-        <v>8.22092601993063e-07</v>
+        <v>1.588545517350326e-09</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.659852841839893e-07</v>
+        <v>2.670776932944818e-10</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.026001766353147e-06</v>
+        <v>1.448288600158776e-09</v>
       </c>
       <c r="DA4" t="n">
-        <v>4.338499820732977e-06</v>
+        <v>3.573486229146994e-10</v>
       </c>
       <c r="DB4" t="n">
-        <v>7.239322030727635e-08</v>
+        <v>1.615562461587672e-09</v>
       </c>
       <c r="DC4" t="n">
-        <v>5.831959128954622e-07</v>
+        <v>1.000129534745042e-09</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.191781161149265e-06</v>
+        <v>2.131124166027121e-09</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.217993596786982e-06</v>
+        <v>9.949807644460407e-10</v>
       </c>
       <c r="DF4" t="n">
-        <v>3.092628048761981e-06</v>
+        <v>1.498700186175483e-08</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.115318122581812e-06</v>
+        <v>5.050353468760704e-09</v>
       </c>
       <c r="DH4" t="n">
-        <v>3.560710410965839e-06</v>
+        <v>5.979583495019369e-09</v>
       </c>
       <c r="DI4" t="n">
-        <v>4.437132702150848e-06</v>
+        <v>5.726538354622335e-09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.455872279620962e-05</v>
+        <v>1.062201615553704e-08</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.239813617663458e-06</v>
+        <v>1.795326332043601e-09</v>
       </c>
       <c r="DL4" t="n">
-        <v>3.719295591508853e-07</v>
+        <v>2.277645405612816e-09</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.15436632768251e-05</v>
+        <v>1.707079144708246e-09</v>
       </c>
       <c r="DN4" t="n">
-        <v>3.374291736690793e-06</v>
+        <v>5.413504755580334e-09</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.745650479278993e-06</v>
+        <v>9.274613854692859e-10</v>
       </c>
       <c r="DP4" t="n">
-        <v>2.856914989024517e-07</v>
+        <v>4.547791032649684e-09</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.917886493174592e-06</v>
+        <v>7.970724524852812e-09</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.064892325710389e-06</v>
+        <v>1.820185890899495e-09</v>
       </c>
       <c r="DS4" t="n">
-        <v>5.575662953560823e-07</v>
+        <v>5.747178732917746e-09</v>
       </c>
       <c r="DT4" t="n">
-        <v>4.320337211538572e-06</v>
+        <v>6.596614809950552e-09</v>
       </c>
       <c r="DU4" t="n">
-        <v>2.390982444921974e-06</v>
+        <v>6.72024746961597e-09</v>
       </c>
       <c r="DV4" t="n">
-        <v>2.970481318698148e-06</v>
+        <v>1.272947081076836e-09</v>
       </c>
       <c r="DW4" t="n">
-        <v>2.366556145716459e-06</v>
+        <v>3.548707105949234e-09</v>
       </c>
       <c r="DX4" t="n">
-        <v>2.007328930631047e-06</v>
+        <v>8.169378062916621e-09</v>
       </c>
       <c r="DY4" t="n">
-        <v>1.25980011489446e-06</v>
+        <v>1.996695253581038e-09</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.724872724182205e-06</v>
+        <v>9.325103356161435e-09</v>
       </c>
       <c r="EA4" t="n">
-        <v>2.480134753568564e-06</v>
+        <v>6.381754680262475e-09</v>
       </c>
       <c r="EB4" t="n">
-        <v>4.567802136534738e-07</v>
+        <v>1.020973305898565e-09</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.972092150026583e-06</v>
+        <v>1.547035832771826e-09</v>
       </c>
       <c r="ED4" t="n">
-        <v>2.875098743970739e-06</v>
+        <v>4.333115199983695e-09</v>
       </c>
       <c r="EE4" t="n">
-        <v>2.980156295961933e-06</v>
+        <v>3.555661542975486e-09</v>
       </c>
       <c r="EF4" t="n">
-        <v>1.814753545659187e-06</v>
+        <v>4.398557962304039e-09</v>
       </c>
       <c r="EG4" t="n">
-        <v>2.248794999104575e-06</v>
+        <v>2.56253263053452e-09</v>
       </c>
       <c r="EH4" t="n">
-        <v>2.153542197902425e-07</v>
+        <v>5.623812526778238e-11</v>
       </c>
       <c r="EI4" t="n">
-        <v>3.995303814008366e-06</v>
+        <v>8.086376013238805e-11</v>
       </c>
       <c r="EJ4" t="n">
-        <v>3.212519459339092e-06</v>
+        <v>2.862850623230884e-09</v>
       </c>
       <c r="EK4" t="n">
-        <v>1.328162511526898e-06</v>
+        <v>9.252751898003453e-10</v>
       </c>
       <c r="EL4" t="n">
-        <v>2.70134432867053e-06</v>
+        <v>4.977076528689395e-10</v>
       </c>
       <c r="EM4" t="n">
-        <v>4.736126868465362e-07</v>
+        <v>3.324266861781666e-09</v>
       </c>
       <c r="EN4" t="n">
-        <v>7.385992830677424e-07</v>
+        <v>3.442962803745786e-09</v>
       </c>
       <c r="EO4" t="n">
-        <v>1.973819962586276e-06</v>
+        <v>2.910718110982202e-09</v>
       </c>
       <c r="EP4" t="n">
-        <v>2.364818556088721e-06</v>
+        <v>4.176722079307638e-09</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1.313650500378571e-06</v>
+        <v>3.539679660491402e-09</v>
       </c>
       <c r="ER4" t="n">
-        <v>1.96381870409823e-06</v>
+        <v>2.461474135628805e-09</v>
       </c>
       <c r="ES4" t="n">
-        <v>6.345583642541897e-06</v>
+        <v>4.057800317980309e-09</v>
       </c>
       <c r="ET4" t="n">
-        <v>9.805786248762161e-06</v>
+        <v>4.165474187800555e-09</v>
       </c>
       <c r="EU4" t="n">
-        <v>3.845628270937596e-06</v>
+        <v>4.253246643770581e-09</v>
       </c>
       <c r="EV4" t="n">
-        <v>1.645672341510362e-06</v>
+        <v>2.224324280319934e-09</v>
       </c>
       <c r="EW4" t="n">
-        <v>6.30592603556579e-06</v>
+        <v>1.731361387591335e-09</v>
       </c>
       <c r="EX4" t="n">
-        <v>4.474198362913739e-07</v>
+        <v>1.203493749102336e-09</v>
       </c>
       <c r="EY4" t="n">
-        <v>4.039026407554047e-06</v>
+        <v>1.346041722527502e-09</v>
       </c>
       <c r="EZ4" t="n">
-        <v>3.043081449050078e-07</v>
+        <v>9.087680608033111e-10</v>
       </c>
       <c r="FA4" t="n">
-        <v>6.770397931177285e-07</v>
+        <v>3.263722625490573e-10</v>
       </c>
       <c r="FB4" t="n">
-        <v>2.868706815206679e-06</v>
+        <v>1.35107491860964e-09</v>
       </c>
       <c r="FC4" t="n">
-        <v>3.53420205101429e-06</v>
+        <v>8.369183124301571e-10</v>
       </c>
       <c r="FD4" t="n">
-        <v>2.233376108051743e-06</v>
+        <v>8.935342465932195e-10</v>
       </c>
       <c r="FE4" t="n">
-        <v>2.167958541576809e-07</v>
+        <v>1.755579237538996e-09</v>
       </c>
       <c r="FF4" t="n">
-        <v>4.275147603038931e-06</v>
+        <v>1.350403788791255e-09</v>
       </c>
       <c r="FG4" t="n">
-        <v>2.876668077078648e-06</v>
+        <v>1.114952219438692e-08</v>
       </c>
       <c r="FH4" t="n">
-        <v>1.346449153061258e-06</v>
+        <v>3.123462821719158e-09</v>
       </c>
       <c r="FI4" t="n">
-        <v>3.84451232093852e-06</v>
+        <v>2.302555479616331e-09</v>
       </c>
       <c r="FJ4" t="n">
-        <v>4.696725682151737e-06</v>
+        <v>2.54151899525823e-09</v>
       </c>
       <c r="FK4" t="n">
-        <v>2.277120529470267e-06</v>
+        <v>3.019983152441341e-09</v>
       </c>
       <c r="FL4" t="n">
-        <v>3.146396238662419e-06</v>
+        <v>8.499166703757055e-09</v>
       </c>
       <c r="FM4" t="n">
-        <v>8.157546744769206e-07</v>
+        <v>4.067699510557077e-10</v>
       </c>
       <c r="FN4" t="n">
-        <v>1.089871261683584e-06</v>
+        <v>1.450541731173871e-08</v>
       </c>
       <c r="FO4" t="n">
-        <v>3.543332695699064e-06</v>
+        <v>7.904552568049894e-09</v>
       </c>
       <c r="FP4" t="n">
-        <v>2.070429161449283e-07</v>
+        <v>3.66802055395965e-09</v>
       </c>
       <c r="FQ4" t="n">
-        <v>5.72213320992887e-06</v>
+        <v>5.104937361721795e-09</v>
       </c>
       <c r="FR4" t="n">
-        <v>4.856002760789124e-06</v>
+        <v>1.307808794592802e-08</v>
       </c>
       <c r="FS4" t="n">
-        <v>1.580657226440962e-06</v>
+        <v>6.816346598270684e-09</v>
       </c>
       <c r="FT4" t="n">
-        <v>4.995783456251957e-06</v>
+        <v>7.357451092815381e-09</v>
       </c>
       <c r="FU4" t="n">
-        <v>8.814369721221738e-06</v>
+        <v>3.854029984040608e-09</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.007662715186598e-06</v>
+        <v>1.778639813210248e-08</v>
       </c>
       <c r="FW4" t="n">
-        <v>3.698115961014992e-06</v>
+        <v>9.423576585732008e-09</v>
       </c>
       <c r="FX4" t="n">
-        <v>3.549893563103979e-06</v>
+        <v>5.516449519404887e-10</v>
       </c>
       <c r="FY4" t="n">
-        <v>3.15142642648425e-06</v>
+        <v>3.993874120311602e-10</v>
       </c>
       <c r="FZ4" t="n">
-        <v>3.588223535189172e-06</v>
+        <v>1.469774857376649e-10</v>
       </c>
       <c r="GA4" t="n">
-        <v>2.262284795051528e-07</v>
+        <v>2.494013440212939e-09</v>
       </c>
       <c r="GB4" t="n">
-        <v>3.554169325070689e-06</v>
+        <v>2.193067949463057e-11</v>
       </c>
       <c r="GC4" t="n">
-        <v>5.072758995083859e-06</v>
+        <v>4.218398963473646e-09</v>
       </c>
       <c r="GD4" t="n">
-        <v>1.270862640012638e-06</v>
+        <v>1.308702812785612e-09</v>
       </c>
       <c r="GE4" t="n">
-        <v>3.496575345707242e-06</v>
+        <v>1.743359567818459e-09</v>
       </c>
       <c r="GF4" t="n">
-        <v>2.116409177688183e-06</v>
+        <v>5.104400457867087e-09</v>
       </c>
       <c r="GG4" t="n">
-        <v>4.396838903630851e-06</v>
+        <v>6.867729052117966e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.34622969198972e-05</v>
+        <v>0.003574614878743887</v>
       </c>
       <c r="B5" t="n">
-        <v>2.19707017095061e-05</v>
+        <v>0.02830493077635765</v>
       </c>
       <c r="C5" t="n">
-        <v>4.716219336842187e-06</v>
+        <v>0.002877265680581331</v>
       </c>
       <c r="D5" t="n">
-        <v>5.93899449086166e-06</v>
+        <v>0.02688257768750191</v>
       </c>
       <c r="E5" t="n">
-        <v>1.553435140522197e-06</v>
+        <v>0.0005975571111775935</v>
       </c>
       <c r="F5" t="n">
-        <v>2.405205123068299e-06</v>
+        <v>0.003201223444193602</v>
       </c>
       <c r="G5" t="n">
-        <v>1.066747927325196e-06</v>
+        <v>0.02079334296286106</v>
       </c>
       <c r="H5" t="n">
-        <v>4.609169081959408e-06</v>
+        <v>0.01096101012080908</v>
       </c>
       <c r="I5" t="n">
-        <v>1.142327073466731e-05</v>
+        <v>0.008979813195765018</v>
       </c>
       <c r="J5" t="n">
-        <v>8.052543307712767e-06</v>
+        <v>0.009074628353118896</v>
       </c>
       <c r="K5" t="n">
-        <v>1.524312938272487e-05</v>
+        <v>0.02435425110161304</v>
       </c>
       <c r="L5" t="n">
-        <v>1.125488870457048e-05</v>
+        <v>0.006246004719287157</v>
       </c>
       <c r="M5" t="n">
-        <v>1.513153165433323e-05</v>
+        <v>0.03866744786500931</v>
       </c>
       <c r="N5" t="n">
-        <v>1.494217212894e-05</v>
+        <v>0.009699116460978985</v>
       </c>
       <c r="O5" t="n">
-        <v>1.949063153006136e-05</v>
+        <v>0.0006567524396814406</v>
       </c>
       <c r="P5" t="n">
-        <v>4.813713530893438e-06</v>
+        <v>0.01988573931157589</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.481848570023431e-06</v>
+        <v>0.0006428647320717573</v>
       </c>
       <c r="R5" t="n">
-        <v>2.08816218218999e-05</v>
+        <v>0.009543754160404205</v>
       </c>
       <c r="S5" t="n">
-        <v>2.503751829863177e-06</v>
+        <v>0.001163066597655416</v>
       </c>
       <c r="T5" t="n">
-        <v>3.859222488244995e-06</v>
+        <v>0.008688604459166527</v>
       </c>
       <c r="U5" t="n">
-        <v>8.905266440706328e-06</v>
+        <v>0.0013750777579844</v>
       </c>
       <c r="V5" t="n">
-        <v>5.876264822290977e-06</v>
+        <v>0.0002754312008619308</v>
       </c>
       <c r="W5" t="n">
-        <v>2.031268650171114e-06</v>
+        <v>0.004281660076230764</v>
       </c>
       <c r="X5" t="n">
-        <v>8.279582289105747e-06</v>
+        <v>0.006514336448162794</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.578028321906459e-06</v>
+        <v>0.001175142358988523</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.516854227811564e-06</v>
+        <v>0.01229573413729668</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.530650843051262e-05</v>
+        <v>0.001831115805543959</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.148629507952137e-05</v>
+        <v>0.001046383637003601</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.713494152179919e-07</v>
+        <v>0.001954714534804225</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.0290299289627e-05</v>
+        <v>0.001693910453468561</v>
       </c>
       <c r="AE5" t="n">
-        <v>9.318267757407739e-07</v>
+        <v>0.003841647878289223</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.870012278639479e-06</v>
+        <v>0.003348680445924401</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.314342509635026e-06</v>
+        <v>0.01375056151300669</v>
       </c>
       <c r="AH5" t="n">
-        <v>4.384072326502064e-06</v>
+        <v>0.0001098103821277618</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.177840871008812e-06</v>
+        <v>0.007225129753351212</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.030342082231073e-05</v>
+        <v>3.054330591112375e-05</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.752165985635656e-06</v>
+        <v>0.001590985339134932</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.873175046464894e-06</v>
+        <v>0.01074431929737329</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.334866283286829e-06</v>
+        <v>0.001259573036804795</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.357874961944617e-07</v>
+        <v>0.001479010563343763</v>
       </c>
       <c r="AO5" t="n">
-        <v>8.332815923495218e-06</v>
+        <v>0.009266060777008533</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.184137545351405e-05</v>
+        <v>0.004664370324462652</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.590132796991384e-06</v>
+        <v>0.005325972102582455</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.274302121601067e-05</v>
+        <v>0.001644571544602513</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.634046952858625e-06</v>
+        <v>0.001032088650390506</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.870444955595303e-06</v>
+        <v>2.577202394604683e-06</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.179933264618739e-05</v>
+        <v>0.01282942574471235</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.338783689192496e-06</v>
+        <v>0.0003061025054194033</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.509469823053223e-06</v>
+        <v>0.01338273845613003</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.88216815533815e-05</v>
+        <v>0.02176580019295216</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.175333616440184e-06</v>
+        <v>0.002171617932617664</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.718366876157233e-06</v>
+        <v>0.0006485404446721077</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.02548256109003e-05</v>
+        <v>0.0004212413623463362</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.700657776382286e-05</v>
+        <v>0.003682955168187618</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.306253559770994e-06</v>
+        <v>0.00585295632481575</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.386325028666761e-06</v>
+        <v>0.00202470226213336</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.878911906620488e-06</v>
+        <v>0.005197897553443909</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.852486876596231e-06</v>
+        <v>0.003112884005531669</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.970633547898615e-06</v>
+        <v>0.01216323394328356</v>
       </c>
       <c r="BH5" t="n">
-        <v>1.000744850898627e-05</v>
+        <v>0.001662896363995969</v>
       </c>
       <c r="BI5" t="n">
-        <v>7.496614216506714e-06</v>
+        <v>0.005148947238922119</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.132145916926675e-05</v>
+        <v>0.01528767496347427</v>
       </c>
       <c r="BK5" t="n">
-        <v>3.065479904762469e-05</v>
+        <v>0.001462700893171132</v>
       </c>
       <c r="BL5" t="n">
-        <v>3.673596893349895e-06</v>
+        <v>0.001374176819808781</v>
       </c>
       <c r="BM5" t="n">
-        <v>6.100632162997499e-06</v>
+        <v>0.007279970683157444</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.295867605222156e-06</v>
+        <v>0.003993421792984009</v>
       </c>
       <c r="BO5" t="n">
-        <v>7.193128112703562e-06</v>
+        <v>0.004751364700496197</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.775740904326085e-05</v>
+        <v>0.00843504536896944</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.303852059209021e-06</v>
+        <v>0.002070608548820019</v>
       </c>
       <c r="BR5" t="n">
-        <v>3.86559622711502e-06</v>
+        <v>0.000374470924725756</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.192765830637654e-05</v>
+        <v>0.0028273556381464</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.866994565119967e-06</v>
+        <v>0.0055391825735569</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.485005890979664e-06</v>
+        <v>0.002457182155922055</v>
       </c>
       <c r="BV5" t="n">
-        <v>1.662671638769098e-05</v>
+        <v>0.01101056486368179</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.324313967023045e-06</v>
+        <v>0.002437596209347248</v>
       </c>
       <c r="BX5" t="n">
-        <v>4.518198693403974e-06</v>
+        <v>0.01695647835731506</v>
       </c>
       <c r="BY5" t="n">
-        <v>7.66077937441878e-06</v>
+        <v>0.002992004388943315</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.203882334266382e-06</v>
+        <v>0.005977336317300797</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.653090854844777e-06</v>
+        <v>0.003380381967872381</v>
       </c>
       <c r="CB5" t="n">
-        <v>5.085403245175257e-06</v>
+        <v>0.002988619729876518</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.094446790579241e-05</v>
+        <v>0.0009515025885775685</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.377427558210911e-07</v>
+        <v>0.0006738327792845666</v>
       </c>
       <c r="CE5" t="n">
-        <v>3.048270627914462e-06</v>
+        <v>0.008029471151530743</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.90787420453853e-06</v>
+        <v>0.0002315141027793288</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.373057213844731e-06</v>
+        <v>0.01051036641001701</v>
       </c>
       <c r="CH5" t="n">
-        <v>2.908497663156595e-06</v>
+        <v>0.002455556066706777</v>
       </c>
       <c r="CI5" t="n">
-        <v>3.575089522200869e-06</v>
+        <v>0.002371799666434526</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.893085249728756e-06</v>
+        <v>1.422502100467682e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>3.898428531101672e-06</v>
+        <v>0.0001643600699026138</v>
       </c>
       <c r="CL5" t="n">
-        <v>8.258888556156307e-06</v>
+        <v>0.0007933271117508411</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.751395211613271e-05</v>
+        <v>0.000735465728212148</v>
       </c>
       <c r="CN5" t="n">
-        <v>7.257690413098317e-06</v>
+        <v>0.0003661401569843292</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.859381427493645e-06</v>
+        <v>0.008092754520475864</v>
       </c>
       <c r="CP5" t="n">
-        <v>8.271897968370467e-06</v>
+        <v>0.01958117447793484</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.40703978104284e-05</v>
+        <v>0.0001577006187289953</v>
       </c>
       <c r="CR5" t="n">
-        <v>5.51961511519039e-06</v>
+        <v>0.004558203276246786</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.102685018850025e-07</v>
+        <v>0.01113258209079504</v>
       </c>
       <c r="CT5" t="n">
-        <v>7.151981208153302e-06</v>
+        <v>0.007298009004443884</v>
       </c>
       <c r="CU5" t="n">
-        <v>4.11227756558219e-06</v>
+        <v>0.004080562852323055</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.5222249178114e-07</v>
+        <v>0.0007982936222106218</v>
       </c>
       <c r="CW5" t="n">
-        <v>3.632115294749383e-06</v>
+        <v>0.007957255467772484</v>
       </c>
       <c r="CX5" t="n">
-        <v>4.248757250024937e-06</v>
+        <v>7.825030479580164e-05</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.69724853549269e-06</v>
+        <v>0.01137423329055309</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.061574377876241e-07</v>
+        <v>0.0008892909972928464</v>
       </c>
       <c r="DA5" t="n">
-        <v>7.084220669639762e-06</v>
+        <v>0.001690709963440895</v>
       </c>
       <c r="DB5" t="n">
-        <v>3.880153599311598e-06</v>
+        <v>0.0001376457512378693</v>
       </c>
       <c r="DC5" t="n">
-        <v>6.129604344096151e-07</v>
+        <v>0.0006557388114742935</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.5309055824182e-06</v>
+        <v>0.0002677437150850892</v>
       </c>
       <c r="DE5" t="n">
-        <v>2.462378688505851e-06</v>
+        <v>0.001829967717640102</v>
       </c>
       <c r="DF5" t="n">
-        <v>3.707654741447186e-06</v>
+        <v>0.009873955510556698</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.066645149374381e-06</v>
+        <v>0.000185083132237196</v>
       </c>
       <c r="DH5" t="n">
-        <v>1.506084299762733e-05</v>
+        <v>0.01478411257266998</v>
       </c>
       <c r="DI5" t="n">
-        <v>1.647208409849554e-05</v>
+        <v>0.001469157519750297</v>
       </c>
       <c r="DJ5" t="n">
-        <v>8.19711021904368e-06</v>
+        <v>0.003771101823076606</v>
       </c>
       <c r="DK5" t="n">
-        <v>7.781587555655278e-06</v>
+        <v>0.001047265715897083</v>
       </c>
       <c r="DL5" t="n">
-        <v>3.827991804428166e-06</v>
+        <v>0.01548622455447912</v>
       </c>
       <c r="DM5" t="n">
-        <v>4.493807068683964e-07</v>
+        <v>0.004613440483808517</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.403350665896141e-06</v>
+        <v>0.001179575338028371</v>
       </c>
       <c r="DO5" t="n">
-        <v>9.298958502768073e-06</v>
+        <v>0.002290717791765928</v>
       </c>
       <c r="DP5" t="n">
-        <v>2.318317001481773e-06</v>
+        <v>0.001569317420944571</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1.56591249833582e-06</v>
+        <v>0.007380649447441101</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.001610927341972e-06</v>
+        <v>0.001601022901013494</v>
       </c>
       <c r="DS5" t="n">
-        <v>8.329131560458336e-06</v>
+        <v>0.001538818120025098</v>
       </c>
       <c r="DT5" t="n">
-        <v>2.240252797491848e-06</v>
+        <v>0.007368386257439852</v>
       </c>
       <c r="DU5" t="n">
-        <v>4.784006705449428e-06</v>
+        <v>0.003835169598460197</v>
       </c>
       <c r="DV5" t="n">
-        <v>7.684596312174108e-06</v>
+        <v>0.01588545367121696</v>
       </c>
       <c r="DW5" t="n">
-        <v>1.813847802623059e-06</v>
+        <v>0.0007086939876899123</v>
       </c>
       <c r="DX5" t="n">
-        <v>8.688539310242049e-07</v>
+        <v>0.0001015816233120859</v>
       </c>
       <c r="DY5" t="n">
-        <v>5.177187176741427e-06</v>
+        <v>0.002854564925655723</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.484477358346339e-06</v>
+        <v>0.003581862896680832</v>
       </c>
       <c r="EA5" t="n">
-        <v>3.552591806510463e-06</v>
+        <v>0.005263146013021469</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.952841193997301e-05</v>
+        <v>0.002269284334033728</v>
       </c>
       <c r="EC5" t="n">
-        <v>5.168234110897174e-06</v>
+        <v>0.002568282652646303</v>
       </c>
       <c r="ED5" t="n">
-        <v>1.219603655044921e-05</v>
+        <v>0.01599543914198875</v>
       </c>
       <c r="EE5" t="n">
-        <v>3.253296654293081e-06</v>
+        <v>0.008698773570358753</v>
       </c>
       <c r="EF5" t="n">
-        <v>6.236489753064234e-06</v>
+        <v>0.005580081138759851</v>
       </c>
       <c r="EG5" t="n">
-        <v>4.28144630859606e-06</v>
+        <v>0.007149857003241777</v>
       </c>
       <c r="EH5" t="n">
-        <v>6.558555014635203e-06</v>
+        <v>0.002484602155163884</v>
       </c>
       <c r="EI5" t="n">
-        <v>6.984066658333177e-08</v>
+        <v>0.009891101159155369</v>
       </c>
       <c r="EJ5" t="n">
-        <v>6.247062174224993e-06</v>
+        <v>0.00295402854681015</v>
       </c>
       <c r="EK5" t="n">
-        <v>6.53920722015755e-08</v>
+        <v>0.006040013395249844</v>
       </c>
       <c r="EL5" t="n">
-        <v>8.477609299006872e-06</v>
+        <v>6.801656854804605e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>1.372710585201276e-07</v>
+        <v>0.001626553013920784</v>
       </c>
       <c r="EN5" t="n">
-        <v>5.676592991221696e-06</v>
+        <v>0.0003756348160095513</v>
       </c>
       <c r="EO5" t="n">
-        <v>1.464993715671881e-06</v>
+        <v>0.001253425376489758</v>
       </c>
       <c r="EP5" t="n">
-        <v>1.184916345664533e-05</v>
+        <v>0.01083800010383129</v>
       </c>
       <c r="EQ5" t="n">
-        <v>5.457412953546736e-06</v>
+        <v>0.005869547836482525</v>
       </c>
       <c r="ER5" t="n">
-        <v>3.068775640713284e-06</v>
+        <v>0.007887675426900387</v>
       </c>
       <c r="ES5" t="n">
-        <v>7.373954304057406e-06</v>
+        <v>0.0006294051418080926</v>
       </c>
       <c r="ET5" t="n">
-        <v>5.718882789551571e-07</v>
+        <v>0.007332996465265751</v>
       </c>
       <c r="EU5" t="n">
-        <v>1.610258095752215e-06</v>
+        <v>0.005489039234817028</v>
       </c>
       <c r="EV5" t="n">
-        <v>1.905216549857869e-06</v>
+        <v>0.000845715869218111</v>
       </c>
       <c r="EW5" t="n">
-        <v>5.917862836213317e-06</v>
+        <v>0.004036908969283104</v>
       </c>
       <c r="EX5" t="n">
-        <v>2.199337131969514e-06</v>
+        <v>0.0008299946202896535</v>
       </c>
       <c r="EY5" t="n">
-        <v>5.979091383778723e-06</v>
+        <v>0.008406737819314003</v>
       </c>
       <c r="EZ5" t="n">
-        <v>4.033439381601056e-06</v>
+        <v>0.0002883923007175326</v>
       </c>
       <c r="FA5" t="n">
-        <v>1.934753981913673e-06</v>
+        <v>0.01425820216536522</v>
       </c>
       <c r="FB5" t="n">
-        <v>1.588516397532658e-06</v>
+        <v>0.001048512640409172</v>
       </c>
       <c r="FC5" t="n">
-        <v>7.360462745964469e-07</v>
+        <v>0.001605341327376664</v>
       </c>
       <c r="FD5" t="n">
-        <v>1.769441951182671e-06</v>
+        <v>0.0009905252372846007</v>
       </c>
       <c r="FE5" t="n">
-        <v>1.63216509463382e-06</v>
+        <v>6.159534677863121e-07</v>
       </c>
       <c r="FF5" t="n">
-        <v>6.007311185385333e-06</v>
+        <v>0.001015111338347197</v>
       </c>
       <c r="FG5" t="n">
-        <v>3.043260676349746e-06</v>
+        <v>0.00397670129314065</v>
       </c>
       <c r="FH5" t="n">
-        <v>7.969463695189916e-06</v>
+        <v>0.002603096421808004</v>
       </c>
       <c r="FI5" t="n">
-        <v>4.866446033702232e-06</v>
+        <v>0.00560898007825017</v>
       </c>
       <c r="FJ5" t="n">
-        <v>6.750427928636782e-06</v>
+        <v>0.006531018298119307</v>
       </c>
       <c r="FK5" t="n">
-        <v>5.170802523934981e-06</v>
+        <v>0.002808624180033803</v>
       </c>
       <c r="FL5" t="n">
-        <v>1.1412899766583e-05</v>
+        <v>0.005654849112033844</v>
       </c>
       <c r="FM5" t="n">
-        <v>6.943761036382057e-06</v>
+        <v>0.0006921079475432634</v>
       </c>
       <c r="FN5" t="n">
-        <v>7.084149729053024e-06</v>
+        <v>0.003258393844589591</v>
       </c>
       <c r="FO5" t="n">
-        <v>3.723217787410249e-06</v>
+        <v>0.007920917123556137</v>
       </c>
       <c r="FP5" t="n">
-        <v>8.572071237722412e-06</v>
+        <v>0.006186088547110558</v>
       </c>
       <c r="FQ5" t="n">
-        <v>1.537976095278282e-05</v>
+        <v>0.008596383035182953</v>
       </c>
       <c r="FR5" t="n">
-        <v>4.139603333896957e-06</v>
+        <v>0.003091801889240742</v>
       </c>
       <c r="FS5" t="n">
-        <v>3.518968242133269e-06</v>
+        <v>0.007379697170108557</v>
       </c>
       <c r="FT5" t="n">
-        <v>3.486072091618553e-05</v>
+        <v>0.001519623678177595</v>
       </c>
       <c r="FU5" t="n">
-        <v>1.25410188047681e-05</v>
+        <v>0.01258687302470207</v>
       </c>
       <c r="FV5" t="n">
-        <v>3.638448106357828e-06</v>
+        <v>0.004566125571727753</v>
       </c>
       <c r="FW5" t="n">
-        <v>8.303500180772971e-06</v>
+        <v>0.001332420622929931</v>
       </c>
       <c r="FX5" t="n">
-        <v>7.766541330056498e-07</v>
+        <v>0.01433263812214136</v>
       </c>
       <c r="FY5" t="n">
-        <v>3.991469384345692e-06</v>
+        <v>0.00341494707390666</v>
       </c>
       <c r="FZ5" t="n">
-        <v>5.195167318561289e-07</v>
+        <v>0.001614471897482872</v>
       </c>
       <c r="GA5" t="n">
-        <v>1.023632194119273e-05</v>
+        <v>0.001356878085061908</v>
       </c>
       <c r="GB5" t="n">
-        <v>1.790521082511987e-07</v>
+        <v>0.01243360340595245</v>
       </c>
       <c r="GC5" t="n">
-        <v>8.661954780109227e-06</v>
+        <v>0.001944103743880987</v>
       </c>
       <c r="GD5" t="n">
-        <v>5.198152848606696e-06</v>
+        <v>0.002026349538937211</v>
       </c>
       <c r="GE5" t="n">
-        <v>2.472386029239715e-07</v>
+        <v>0.006452721543610096</v>
       </c>
       <c r="GF5" t="n">
-        <v>2.527352990000509e-06</v>
+        <v>0.001568116946145892</v>
       </c>
       <c r="GG5" t="n">
-        <v>1.53505652633612e-06</v>
+        <v>0.0006904072361066937</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5.519476431459225e-09</v>
+        <v>2.742148955819923e-13</v>
       </c>
       <c r="B6" t="n">
-        <v>6.86586858478222e-08</v>
+        <v>1.088952886196815e-11</v>
       </c>
       <c r="C6" t="n">
-        <v>5.016012138980841e-08</v>
+        <v>2.221973473270911e-12</v>
       </c>
       <c r="D6" t="n">
-        <v>1.656205483868689e-08</v>
+        <v>3.524464249095305e-13</v>
       </c>
       <c r="E6" t="n">
-        <v>6.222882831252718e-08</v>
+        <v>3.407184690634724e-12</v>
       </c>
       <c r="F6" t="n">
-        <v>8.977639964768969e-08</v>
+        <v>1.670526737773681e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>4.554228638653512e-08</v>
+        <v>1.681216450777345e-11</v>
       </c>
       <c r="H6" t="n">
-        <v>3.920983715488546e-08</v>
+        <v>1.755869408204269e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>1.288103135266283e-08</v>
+        <v>3.75617549217e-12</v>
       </c>
       <c r="J6" t="n">
-        <v>3.228110045938593e-08</v>
+        <v>5.998616100372223e-12</v>
       </c>
       <c r="K6" t="n">
-        <v>4.809587039744656e-08</v>
+        <v>7.047150189787299e-12</v>
       </c>
       <c r="L6" t="n">
-        <v>5.061477459378239e-09</v>
+        <v>6.960121281401888e-12</v>
       </c>
       <c r="M6" t="n">
-        <v>7.709815719181279e-08</v>
+        <v>6.183283919602989e-12</v>
       </c>
       <c r="N6" t="n">
-        <v>9.003458245615548e-08</v>
+        <v>8.480361378404577e-12</v>
       </c>
       <c r="O6" t="n">
-        <v>4.019781840725045e-08</v>
+        <v>2.333787503527862e-11</v>
       </c>
       <c r="P6" t="n">
-        <v>3.346908528101267e-08</v>
+        <v>2.128911630316921e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.071822701234851e-08</v>
+        <v>1.873421036358014e-11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.869996069103763e-08</v>
+        <v>7.115631868448435e-13</v>
       </c>
       <c r="S6" t="n">
-        <v>3.980886020826802e-08</v>
+        <v>1.940037757178215e-12</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74509224848407e-08</v>
+        <v>9.646055655621044e-12</v>
       </c>
       <c r="U6" t="n">
-        <v>3.598865916387695e-08</v>
+        <v>9.766807588379445e-13</v>
       </c>
       <c r="V6" t="n">
-        <v>2.870700299695272e-08</v>
+        <v>7.842522638246141e-12</v>
       </c>
       <c r="W6" t="n">
-        <v>3.455093633419892e-08</v>
+        <v>1.4739001685804e-11</v>
       </c>
       <c r="X6" t="n">
-        <v>4.079751647623198e-08</v>
+        <v>1.509551598305459e-12</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.339626631846613e-09</v>
+        <v>5.523186942524294e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.855591129171444e-08</v>
+        <v>1.38255370693563e-11</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.406625902537598e-08</v>
+        <v>1.420662849513366e-12</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.146730266299301e-08</v>
+        <v>1.154075858315895e-12</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.315198675110878e-08</v>
+        <v>6.002270295374368e-12</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.362712869796724e-08</v>
+        <v>6.420588886946188e-13</v>
       </c>
       <c r="AE6" t="n">
-        <v>4.16200194308658e-08</v>
+        <v>6.933689733479298e-12</v>
       </c>
       <c r="AF6" t="n">
-        <v>7.543562929868131e-08</v>
+        <v>1.075018719876031e-11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.050863147611381e-07</v>
+        <v>1.121827630790051e-11</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.308366913756799e-08</v>
+        <v>3.650317895176336e-12</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.347404569671198e-08</v>
+        <v>1.174541366943949e-11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>6.498540727761792e-08</v>
+        <v>2.47872469077981e-12</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.755189854042328e-09</v>
+        <v>1.847105232438348e-13</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.582016461223247e-08</v>
+        <v>3.35074698022686e-12</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.881220335064882e-08</v>
+        <v>1.093344382044337e-12</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.582121633703082e-08</v>
+        <v>7.495132986479192e-12</v>
       </c>
       <c r="AO6" t="n">
-        <v>6.500197713421585e-08</v>
+        <v>3.092848893659905e-12</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.628010057989741e-08</v>
+        <v>1.098102403278289e-12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.387412388950906e-08</v>
+        <v>2.647733594873802e-12</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.92380750721577e-08</v>
+        <v>1.870354131988661e-12</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.269111896273216e-09</v>
+        <v>3.45373447722952e-12</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.867255315981311e-08</v>
+        <v>1.085887456342416e-12</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.957347706138535e-07</v>
+        <v>1.17818359235411e-11</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.873674548846793e-10</v>
+        <v>4.472080258194344e-12</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.563220201703189e-08</v>
+        <v>2.379439527355753e-12</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.722096681395669e-08</v>
+        <v>8.635879338025898e-12</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.611161337677913e-08</v>
+        <v>1.755511708223523e-11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7.091023235261673e-08</v>
+        <v>6.841462292517253e-12</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.214535191479854e-09</v>
+        <v>1.229871066099619e-11</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.375680179829033e-08</v>
+        <v>1.674135222812234e-12</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.692700284967486e-08</v>
+        <v>1.132922098148748e-12</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.391519231068287e-09</v>
+        <v>9.414684309927424e-12</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.686448182970707e-08</v>
+        <v>3.735393071246929e-12</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.05552526719066e-08</v>
+        <v>1.355855965695651e-11</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.170287285087397e-08</v>
+        <v>8.056368072661968e-12</v>
       </c>
       <c r="BH6" t="n">
-        <v>1.864843284238304e-07</v>
+        <v>4.129945951197866e-12</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.766095263950774e-08</v>
+        <v>9.000213768706189e-13</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.766580350538788e-08</v>
+        <v>1.556680132019927e-11</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.316577152328136e-08</v>
+        <v>4.021553923205801e-12</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.273290095582524e-08</v>
+        <v>3.30617781416076e-12</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.288402415866585e-07</v>
+        <v>8.533065747051705e-13</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.76349592098768e-08</v>
+        <v>1.367489238165986e-12</v>
       </c>
       <c r="BO6" t="n">
-        <v>2.242007113295585e-08</v>
+        <v>4.267322443757965e-13</v>
       </c>
       <c r="BP6" t="n">
-        <v>6.509119998554524e-08</v>
+        <v>3.68572056555494e-12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.478728771710848e-08</v>
+        <v>1.359044170604062e-13</v>
       </c>
       <c r="BR6" t="n">
-        <v>3.715069141208005e-08</v>
+        <v>2.908515876060003e-12</v>
       </c>
       <c r="BS6" t="n">
-        <v>3.110054436206156e-08</v>
+        <v>5.280289660375415e-12</v>
       </c>
       <c r="BT6" t="n">
-        <v>2.24312000085547e-08</v>
+        <v>6.431030187548092e-12</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.678718023067631e-09</v>
+        <v>1.253287079151788e-12</v>
       </c>
       <c r="BV6" t="n">
-        <v>3.602274745162504e-08</v>
+        <v>3.974679092799693e-12</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.639533309116814e-08</v>
+        <v>1.27337593594512e-13</v>
       </c>
       <c r="BX6" t="n">
-        <v>5.051927587373939e-08</v>
+        <v>1.456738028815519e-11</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.514542447011991e-08</v>
+        <v>1.300671549631094e-11</v>
       </c>
       <c r="BZ6" t="n">
-        <v>8.799386819191568e-08</v>
+        <v>6.865996052957124e-12</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.332590452018394e-09</v>
+        <v>3.570312448464286e-12</v>
       </c>
       <c r="CB6" t="n">
-        <v>1.884995981527027e-08</v>
+        <v>5.767311541532427e-12</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.291923343975213e-08</v>
+        <v>4.725558052504075e-12</v>
       </c>
       <c r="CD6" t="n">
-        <v>1.598705612337881e-10</v>
+        <v>1.951930370808208e-13</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.398457172285816e-08</v>
+        <v>3.742899002887046e-14</v>
       </c>
       <c r="CF6" t="n">
-        <v>1.215647138508302e-08</v>
+        <v>1.413423740027897e-12</v>
       </c>
       <c r="CG6" t="n">
-        <v>4.09031697401474e-11</v>
+        <v>1.186872974033581e-12</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.671714144890757e-08</v>
+        <v>1.620929952761418e-12</v>
       </c>
       <c r="CI6" t="n">
-        <v>7.697964932162904e-09</v>
+        <v>4.390266795939457e-12</v>
       </c>
       <c r="CJ6" t="n">
-        <v>8.654655658801857e-09</v>
+        <v>2.838337637839361e-12</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.269165128547911e-08</v>
+        <v>8.707887384253044e-13</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.112100361273406e-08</v>
+        <v>4.372801166302454e-12</v>
       </c>
       <c r="CM6" t="n">
-        <v>7.061746032377414e-08</v>
+        <v>2.383288661908511e-12</v>
       </c>
       <c r="CN6" t="n">
-        <v>9.232427800043297e-08</v>
+        <v>8.582579959226511e-12</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.905661051182506e-08</v>
+        <v>5.454134539839561e-12</v>
       </c>
       <c r="CP6" t="n">
-        <v>6.019146781000018e-08</v>
+        <v>1.305508218890639e-12</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.931053527139738e-08</v>
+        <v>1.02699489537561e-11</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.297134133437794e-08</v>
+        <v>7.493423199653182e-13</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.61133842829986e-08</v>
+        <v>1.146689861120098e-11</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.99846591392361e-08</v>
+        <v>6.48467867944702e-12</v>
       </c>
       <c r="CU6" t="n">
-        <v>5.476693942796373e-08</v>
+        <v>1.403912468049551e-12</v>
       </c>
       <c r="CV6" t="n">
-        <v>5.523007828855953e-09</v>
+        <v>3.756541518823431e-13</v>
       </c>
       <c r="CW6" t="n">
-        <v>4.85207118927633e-09</v>
+        <v>3.284450077363499e-13</v>
       </c>
       <c r="CX6" t="n">
-        <v>4.599762792878437e-10</v>
+        <v>9.937231159468096e-13</v>
       </c>
       <c r="CY6" t="n">
-        <v>6.687157050322412e-09</v>
+        <v>1.677710271055788e-12</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.696512346744839e-09</v>
+        <v>1.441423369552552e-12</v>
       </c>
       <c r="DA6" t="n">
-        <v>5.875257613752183e-09</v>
+        <v>5.590392298387981e-12</v>
       </c>
       <c r="DB6" t="n">
-        <v>2.748019589660089e-09</v>
+        <v>3.142149301166297e-12</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.656117731840823e-08</v>
+        <v>1.617521654811993e-12</v>
       </c>
       <c r="DD6" t="n">
-        <v>9.627916242038737e-09</v>
+        <v>3.634203831967553e-12</v>
       </c>
       <c r="DE6" t="n">
-        <v>7.997891060540496e-08</v>
+        <v>7.772246388149107e-12</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.668984322440338e-08</v>
+        <v>1.792043943793509e-11</v>
       </c>
       <c r="DG6" t="n">
-        <v>6.329541690774931e-08</v>
+        <v>1.007594094964981e-11</v>
       </c>
       <c r="DH6" t="n">
-        <v>2.319956848850779e-08</v>
+        <v>6.640655039746868e-12</v>
       </c>
       <c r="DI6" t="n">
-        <v>5.164558558590215e-08</v>
+        <v>3.57761043012772e-12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>9.354591412602531e-08</v>
+        <v>2.183986151649275e-11</v>
       </c>
       <c r="DK6" t="n">
-        <v>1.277847871961058e-07</v>
+        <v>4.820099180902204e-12</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.392533104966788e-08</v>
+        <v>4.991484656158285e-12</v>
       </c>
       <c r="DM6" t="n">
-        <v>5.046398143804254e-08</v>
+        <v>9.199303645235357e-13</v>
       </c>
       <c r="DN6" t="n">
-        <v>6.282833453497005e-08</v>
+        <v>4.560145230175783e-12</v>
       </c>
       <c r="DO6" t="n">
-        <v>6.266816399147501e-08</v>
+        <v>1.830764706500787e-12</v>
       </c>
       <c r="DP6" t="n">
-        <v>4.445933399210844e-08</v>
+        <v>3.874707846240888e-12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>2.517125707868217e-08</v>
+        <v>1.007100999816934e-11</v>
       </c>
       <c r="DR6" t="n">
-        <v>2.600783233219772e-08</v>
+        <v>3.703641126423518e-12</v>
       </c>
       <c r="DS6" t="n">
-        <v>2.624670969453291e-08</v>
+        <v>1.132101465524393e-12</v>
       </c>
       <c r="DT6" t="n">
-        <v>6.995626478101258e-08</v>
+        <v>4.917666968085044e-12</v>
       </c>
       <c r="DU6" t="n">
-        <v>3.178491070343625e-08</v>
+        <v>6.981991807625265e-12</v>
       </c>
       <c r="DV6" t="n">
-        <v>8.546603424974819e-08</v>
+        <v>1.12245846298209e-12</v>
       </c>
       <c r="DW6" t="n">
-        <v>2.576202362547519e-08</v>
+        <v>3.68070591366676e-12</v>
       </c>
       <c r="DX6" t="n">
-        <v>1.375635694245148e-08</v>
+        <v>1.082170290878093e-11</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.267641630027128e-10</v>
+        <v>5.254932773646193e-14</v>
       </c>
       <c r="DZ6" t="n">
-        <v>8.418595598413958e-09</v>
+        <v>9.240948284361394e-12</v>
       </c>
       <c r="EA6" t="n">
-        <v>3.496210876363648e-09</v>
+        <v>4.769770949736296e-12</v>
       </c>
       <c r="EB6" t="n">
-        <v>9.918136356645846e-08</v>
+        <v>5.380590504394656e-12</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.96737398489222e-08</v>
+        <v>2.534204833828935e-12</v>
       </c>
       <c r="ED6" t="n">
-        <v>1.786493442068604e-08</v>
+        <v>3.129542198304636e-12</v>
       </c>
       <c r="EE6" t="n">
-        <v>2.31663683791794e-08</v>
+        <v>3.376845244401627e-12</v>
       </c>
       <c r="EF6" t="n">
-        <v>2.923274511346108e-09</v>
+        <v>1.916464599863166e-12</v>
       </c>
       <c r="EG6" t="n">
-        <v>5.03056867273699e-08</v>
+        <v>2.106713675037453e-12</v>
       </c>
       <c r="EH6" t="n">
-        <v>3.0266701145365e-08</v>
+        <v>1.701381657087664e-12</v>
       </c>
       <c r="EI6" t="n">
-        <v>4.035199907548304e-08</v>
+        <v>4.358863530534718e-12</v>
       </c>
       <c r="EJ6" t="n">
-        <v>5.02649255551546e-09</v>
+        <v>2.871604429938168e-12</v>
       </c>
       <c r="EK6" t="n">
-        <v>1.846854935649844e-08</v>
+        <v>3.254673657318574e-12</v>
       </c>
       <c r="EL6" t="n">
-        <v>4.430817313050284e-08</v>
+        <v>1.717146932457558e-13</v>
       </c>
       <c r="EM6" t="n">
-        <v>1.70339049532231e-08</v>
+        <v>1.349142585843621e-12</v>
       </c>
       <c r="EN6" t="n">
-        <v>2.969048296108667e-08</v>
+        <v>7.176673318121107e-12</v>
       </c>
       <c r="EO6" t="n">
-        <v>5.162831229199583e-08</v>
+        <v>1.904007116901307e-12</v>
       </c>
       <c r="EP6" t="n">
-        <v>2.81503567123309e-08</v>
+        <v>5.490287911802394e-12</v>
       </c>
       <c r="EQ6" t="n">
-        <v>4.763730743206906e-09</v>
+        <v>1.588900018500983e-12</v>
       </c>
       <c r="ER6" t="n">
-        <v>2.291176137703133e-08</v>
+        <v>2.755364512940783e-12</v>
       </c>
       <c r="ES6" t="n">
-        <v>2.958873679403951e-08</v>
+        <v>1.354050985918898e-11</v>
       </c>
       <c r="ET6" t="n">
-        <v>7.574269744736739e-08</v>
+        <v>1.922453082142672e-12</v>
       </c>
       <c r="EU6" t="n">
-        <v>2.475709592886233e-08</v>
+        <v>1.208227528443073e-12</v>
       </c>
       <c r="EV6" t="n">
-        <v>2.732721782194858e-08</v>
+        <v>1.867242038072758e-12</v>
       </c>
       <c r="EW6" t="n">
-        <v>5.923879697888879e-08</v>
+        <v>1.511355710720474e-12</v>
       </c>
       <c r="EX6" t="n">
-        <v>2.378905517019803e-09</v>
+        <v>5.155457766421734e-13</v>
       </c>
       <c r="EY6" t="n">
-        <v>1.854554732005909e-09</v>
+        <v>2.852160781857682e-13</v>
       </c>
       <c r="EZ6" t="n">
-        <v>1.748870914752843e-08</v>
+        <v>8.860463903380411e-13</v>
       </c>
       <c r="FA6" t="n">
-        <v>1.076930011834065e-08</v>
+        <v>6.316321164018257e-13</v>
       </c>
       <c r="FB6" t="n">
-        <v>1.003065541738124e-08</v>
+        <v>1.488054471310285e-13</v>
       </c>
       <c r="FC6" t="n">
-        <v>6.982987521553241e-09</v>
+        <v>4.82207589830308e-12</v>
       </c>
       <c r="FD6" t="n">
-        <v>7.524391776314587e-09</v>
+        <v>3.134045323607837e-12</v>
       </c>
       <c r="FE6" t="n">
-        <v>1.089550583088794e-08</v>
+        <v>1.114311442597382e-12</v>
       </c>
       <c r="FF6" t="n">
-        <v>9.758449159846805e-09</v>
+        <v>2.546819092424935e-12</v>
       </c>
       <c r="FG6" t="n">
-        <v>1.714443698119794e-08</v>
+        <v>1.042720250421514e-11</v>
       </c>
       <c r="FH6" t="n">
-        <v>4.545813681033906e-08</v>
+        <v>5.822611923861354e-12</v>
       </c>
       <c r="FI6" t="n">
-        <v>5.917599921190231e-08</v>
+        <v>3.830122417142201e-12</v>
       </c>
       <c r="FJ6" t="n">
-        <v>2.570617851915813e-08</v>
+        <v>8.737975620842775e-13</v>
       </c>
       <c r="FK6" t="n">
-        <v>9.127675504316812e-09</v>
+        <v>5.524247292248985e-12</v>
       </c>
       <c r="FL6" t="n">
-        <v>4.323138469430887e-08</v>
+        <v>2.484491778975695e-12</v>
       </c>
       <c r="FM6" t="n">
-        <v>2.932767095842337e-08</v>
+        <v>3.085343612541092e-12</v>
       </c>
       <c r="FN6" t="n">
-        <v>5.929236479573774e-08</v>
+        <v>9.799657613163149e-12</v>
       </c>
       <c r="FO6" t="n">
-        <v>3.109990043270727e-09</v>
+        <v>7.093676340774735e-12</v>
       </c>
       <c r="FP6" t="n">
-        <v>5.204881858844601e-08</v>
+        <v>1.95364557864508e-13</v>
       </c>
       <c r="FQ6" t="n">
-        <v>1.750672939948572e-10</v>
+        <v>1.052013684499364e-11</v>
       </c>
       <c r="FR6" t="n">
-        <v>8.669043438658264e-08</v>
+        <v>1.215435738166626e-11</v>
       </c>
       <c r="FS6" t="n">
-        <v>1.299247465169628e-08</v>
+        <v>4.156313748032714e-12</v>
       </c>
       <c r="FT6" t="n">
-        <v>6.421944931389589e-08</v>
+        <v>8.583086498481496e-12</v>
       </c>
       <c r="FU6" t="n">
-        <v>5.215334653030368e-08</v>
+        <v>1.63747596211572e-13</v>
       </c>
       <c r="FV6" t="n">
-        <v>3.30457936570383e-08</v>
+        <v>1.323532949903949e-11</v>
       </c>
       <c r="FW6" t="n">
-        <v>1.659888226868134e-08</v>
+        <v>5.375911955179946e-12</v>
       </c>
       <c r="FX6" t="n">
-        <v>1.828426832162222e-08</v>
+        <v>3.764174844218815e-13</v>
       </c>
       <c r="FY6" t="n">
-        <v>1.14772618076131e-08</v>
+        <v>2.726258021418237e-12</v>
       </c>
       <c r="FZ6" t="n">
-        <v>1.088569234752867e-07</v>
+        <v>1.742820406221146e-12</v>
       </c>
       <c r="GA6" t="n">
-        <v>5.895595567295686e-09</v>
+        <v>1.580187911943975e-12</v>
       </c>
       <c r="GB6" t="n">
-        <v>5.528973900936762e-08</v>
+        <v>4.129216066295349e-12</v>
       </c>
       <c r="GC6" t="n">
-        <v>3.09561620781551e-08</v>
+        <v>7.727323989015211e-12</v>
       </c>
       <c r="GD6" t="n">
-        <v>2.889079908641179e-08</v>
+        <v>1.024686498846128e-11</v>
       </c>
       <c r="GE6" t="n">
-        <v>9.438467429845332e-08</v>
+        <v>1.474458033966231e-12</v>
       </c>
       <c r="GF6" t="n">
-        <v>4.089360317038881e-08</v>
+        <v>6.618092358856575e-12</v>
       </c>
       <c r="GG6" t="n">
-        <v>7.773097365770809e-08</v>
+        <v>4.613014397553128e-12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5.143754519543187e-11</v>
+        <v>1.926051675149302e-17</v>
       </c>
       <c r="B7" t="n">
-        <v>1.240113289835421e-10</v>
+        <v>7.650064089910919e-19</v>
       </c>
       <c r="C7" t="n">
-        <v>4.167469494498199e-11</v>
+        <v>1.296031613006208e-16</v>
       </c>
       <c r="D7" t="n">
-        <v>3.562928077571748e-11</v>
+        <v>9.589062134263411e-17</v>
       </c>
       <c r="E7" t="n">
-        <v>1.226037240481537e-11</v>
+        <v>1.571112279333616e-17</v>
       </c>
       <c r="F7" t="n">
-        <v>3.849517579701534e-11</v>
+        <v>1.912881239261784e-16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.54298671062314e-10</v>
+        <v>5.077272319286416e-17</v>
       </c>
       <c r="H7" t="n">
-        <v>3.598930875536865e-11</v>
+        <v>5.004395722087024e-17</v>
       </c>
       <c r="I7" t="n">
-        <v>7.629677445386562e-11</v>
+        <v>1.388800249576275e-16</v>
       </c>
       <c r="J7" t="n">
-        <v>4.789964952456316e-11</v>
+        <v>2.368803737613006e-17</v>
       </c>
       <c r="K7" t="n">
-        <v>6.688323506143234e-12</v>
+        <v>1.733486278478224e-16</v>
       </c>
       <c r="L7" t="n">
-        <v>6.007408459574037e-11</v>
+        <v>1.282807575814996e-16</v>
       </c>
       <c r="M7" t="n">
-        <v>6.520000511711643e-11</v>
+        <v>1.815592887824727e-16</v>
       </c>
       <c r="N7" t="n">
-        <v>1.916128367085435e-10</v>
+        <v>1.5315202719305e-17</v>
       </c>
       <c r="O7" t="n">
-        <v>1.091991688045857e-11</v>
+        <v>1.48331417106438e-16</v>
       </c>
       <c r="P7" t="n">
-        <v>6.578781963639813e-11</v>
+        <v>1.028275498654059e-16</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.208683319044781e-13</v>
+        <v>1.148516590077135e-16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.499390195336403e-11</v>
+        <v>8.211607229271118e-17</v>
       </c>
       <c r="S7" t="n">
-        <v>2.291473781557141e-11</v>
+        <v>3.70375049267069e-17</v>
       </c>
       <c r="T7" t="n">
-        <v>7.736675883274202e-12</v>
+        <v>1.086604238809909e-16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.793145493200754e-11</v>
+        <v>2.82623263112136e-17</v>
       </c>
       <c r="V7" t="n">
-        <v>2.960524880801785e-11</v>
+        <v>1.088346810575538e-16</v>
       </c>
       <c r="W7" t="n">
-        <v>9.480875806655575e-11</v>
+        <v>1.734009718369847e-16</v>
       </c>
       <c r="X7" t="n">
-        <v>8.400385942408661e-11</v>
+        <v>1.107040827721441e-16</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.254419220748538e-11</v>
+        <v>4.776763889318557e-17</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.743780120300187e-11</v>
+        <v>8.010096767630339e-17</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.668933871309952e-12</v>
+        <v>4.83632188603911e-17</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.073756621811084e-11</v>
+        <v>2.669092468410171e-17</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.519549937267772e-11</v>
+        <v>2.859677197648104e-17</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.40459360493162e-11</v>
+        <v>7.239910884515686e-17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.028204466013705e-10</v>
+        <v>9.53850551696866e-17</v>
       </c>
       <c r="AF7" t="n">
-        <v>4.195181702026929e-11</v>
+        <v>9.682750430238515e-18</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.82140577462431e-11</v>
+        <v>5.477509945242854e-17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.274037732951205e-11</v>
+        <v>1.727178430737466e-17</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.802794454859203e-11</v>
+        <v>1.045233826177029e-16</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4.916176146729789e-11</v>
+        <v>4.79327606870634e-17</v>
       </c>
       <c r="AK7" t="n">
-        <v>6.240047541183902e-13</v>
+        <v>5.513887694221711e-17</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.475528553507299e-11</v>
+        <v>3.947145079191968e-17</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.232618781349393e-11</v>
+        <v>2.952583807944345e-17</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.96986706060931e-11</v>
+        <v>8.576229766773472e-17</v>
       </c>
       <c r="AO7" t="n">
-        <v>8.994204686585405e-11</v>
+        <v>8.375113704848759e-17</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.341964701814476e-12</v>
+        <v>2.293429385835949e-18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.746887703935052e-11</v>
+        <v>3.303413605040745e-17</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.913346118851081e-11</v>
+        <v>7.377054783099017e-17</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.039560364873848e-11</v>
+        <v>4.994667416338911e-17</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.493200611242141e-11</v>
+        <v>9.360547865217472e-18</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.04821137880684e-10</v>
+        <v>2.525920011348104e-16</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.730687988754642e-11</v>
+        <v>1.163033973786911e-17</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.906950986008127e-11</v>
+        <v>3.559803529857477e-17</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.633818494528043e-12</v>
+        <v>5.468606834873823e-17</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.503963620308468e-11</v>
+        <v>1.715538676029865e-17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7.793904410746677e-13</v>
+        <v>1.45386306709892e-17</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.212763636881391e-11</v>
+        <v>7.131290158686652e-17</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.558254468323142e-11</v>
+        <v>6.313229046950899e-17</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.421468928148762e-11</v>
+        <v>7.40688556296564e-17</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.114667287447027e-11</v>
+        <v>1.165289298270649e-16</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.839701556180742e-11</v>
+        <v>6.411877283314993e-18</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.104324932840413e-12</v>
+        <v>6.073755627405367e-17</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.075163289098739e-11</v>
+        <v>3.902452841567973e-18</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.975513057114966e-12</v>
+        <v>9.136485151356048e-17</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.623060189194115e-12</v>
+        <v>6.695198554515226e-17</v>
       </c>
       <c r="BJ7" t="n">
-        <v>3.095861067503591e-11</v>
+        <v>2.334266134624834e-17</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.119941778204847e-10</v>
+        <v>3.927978311782379e-17</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.104878428331846e-11</v>
+        <v>7.012649959533887e-17</v>
       </c>
       <c r="BM7" t="n">
-        <v>2.424770106923546e-11</v>
+        <v>8.856639362217518e-17</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.541474847072122e-12</v>
+        <v>2.052105397824013e-17</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.710660598232884e-11</v>
+        <v>1.312966498230618e-17</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.518039999259813e-10</v>
+        <v>9.719581970501419e-17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.686857582065663e-11</v>
+        <v>7.569088401897898e-17</v>
       </c>
       <c r="BR7" t="n">
-        <v>4.35068300830288e-11</v>
+        <v>8.884998422338286e-17</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.641420234263727e-11</v>
+        <v>3.163067855742343e-17</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.182584834033776e-12</v>
+        <v>1.87593776491839e-17</v>
       </c>
       <c r="BU7" t="n">
-        <v>8.10480588891993e-12</v>
+        <v>4.705080251998589e-18</v>
       </c>
       <c r="BV7" t="n">
-        <v>4.433265560210842e-11</v>
+        <v>4.338821385808482e-17</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.282444289651963e-11</v>
+        <v>6.412716375328367e-17</v>
       </c>
       <c r="BX7" t="n">
-        <v>3.264618089748872e-11</v>
+        <v>9.414237180928084e-17</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.473260287855666e-11</v>
+        <v>9.8958720261377e-17</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.480865859966208e-11</v>
+        <v>1.226889239964126e-16</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.255573249536734e-11</v>
+        <v>3.544407713424395e-18</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.6637211533731e-11</v>
+        <v>7.735620373284014e-17</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.441093243683468e-11</v>
+        <v>9.850364519301973e-17</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.00802742888928e-11</v>
+        <v>1.898586962706827e-17</v>
       </c>
       <c r="CE7" t="n">
-        <v>4.778281069428569e-12</v>
+        <v>4.958769928423702e-18</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.436921754140787e-12</v>
+        <v>2.95757170703804e-17</v>
       </c>
       <c r="CG7" t="n">
-        <v>1.155826215987199e-11</v>
+        <v>5.060137107461258e-17</v>
       </c>
       <c r="CH7" t="n">
-        <v>3.616694617403216e-13</v>
+        <v>1.298466352964809e-17</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.567573501559671e-11</v>
+        <v>3.699521614507073e-17</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.146173516681671e-11</v>
+        <v>1.955468368401281e-17</v>
       </c>
       <c r="CK7" t="n">
-        <v>4.632861802522648e-12</v>
+        <v>1.196281092301438e-17</v>
       </c>
       <c r="CL7" t="n">
-        <v>3.158223682575567e-11</v>
+        <v>4.369947530514362e-17</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.396699769729004e-11</v>
+        <v>4.478206530261526e-18</v>
       </c>
       <c r="CN7" t="n">
-        <v>9.756173299790838e-12</v>
+        <v>6.982805283032973e-17</v>
       </c>
       <c r="CO7" t="n">
-        <v>2.624269204720697e-11</v>
+        <v>5.153434147006624e-17</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.590525280925625e-11</v>
+        <v>4.735461437844804e-17</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.921080903885766e-11</v>
+        <v>3.609342384126542e-17</v>
       </c>
       <c r="CR7" t="n">
-        <v>2.158800568863306e-11</v>
+        <v>1.134484496689133e-17</v>
       </c>
       <c r="CS7" t="n">
-        <v>9.435654341194422e-11</v>
+        <v>2.02398059525272e-17</v>
       </c>
       <c r="CT7" t="n">
-        <v>6.657038115198688e-11</v>
+        <v>4.436641118071043e-17</v>
       </c>
       <c r="CU7" t="n">
-        <v>2.479042839065304e-11</v>
+        <v>8.01229574457075e-17</v>
       </c>
       <c r="CV7" t="n">
-        <v>4.685320274117055e-12</v>
+        <v>2.935629252364968e-17</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.507113878140842e-12</v>
+        <v>3.441551112975876e-19</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.100155990613194e-12</v>
+        <v>2.019655764138048e-17</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.124465534047992e-12</v>
+        <v>4.689368948879879e-17</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.025558323501264e-12</v>
+        <v>1.459094653601072e-17</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.270636373895684e-11</v>
+        <v>3.09102009351673e-17</v>
       </c>
       <c r="DB7" t="n">
-        <v>2.768040657796789e-11</v>
+        <v>1.319048509120537e-17</v>
       </c>
       <c r="DC7" t="n">
-        <v>4.8937034979879e-12</v>
+        <v>2.803068182529364e-18</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.195324221547889e-11</v>
+        <v>3.98189493672532e-17</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.392992665660842e-11</v>
+        <v>1.267810625873287e-17</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.479281142025002e-10</v>
+        <v>3.415034349515386e-17</v>
       </c>
       <c r="DG7" t="n">
-        <v>6.924105733219221e-11</v>
+        <v>5.476869542012616e-18</v>
       </c>
       <c r="DH7" t="n">
-        <v>1.296808632700319e-10</v>
+        <v>9.41853454964642e-17</v>
       </c>
       <c r="DI7" t="n">
-        <v>8.306394461143896e-11</v>
+        <v>4.698040448677395e-17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>5.511528733403992e-11</v>
+        <v>1.472513177497908e-17</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.756277052237913e-11</v>
+        <v>1.920241889398975e-17</v>
       </c>
       <c r="DL7" t="n">
-        <v>4.169869310954866e-11</v>
+        <v>6.194235310804328e-18</v>
       </c>
       <c r="DM7" t="n">
-        <v>7.453083289421514e-13</v>
+        <v>2.338228991503453e-17</v>
       </c>
       <c r="DN7" t="n">
-        <v>5.433189922271486e-12</v>
+        <v>3.625761340259291e-18</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.747752025911154e-11</v>
+        <v>1.246754660662689e-17</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.868002454108453e-11</v>
+        <v>1.789075032485829e-18</v>
       </c>
       <c r="DQ7" t="n">
-        <v>3.114924637670491e-11</v>
+        <v>9.260691283414561e-17</v>
       </c>
       <c r="DR7" t="n">
-        <v>3.149082730691255e-11</v>
+        <v>4.373609955394502e-18</v>
       </c>
       <c r="DS7" t="n">
-        <v>2.538938156937398e-11</v>
+        <v>6.916556718645846e-17</v>
       </c>
       <c r="DT7" t="n">
-        <v>5.724039298105055e-11</v>
+        <v>4.832602882005071e-17</v>
       </c>
       <c r="DU7" t="n">
-        <v>1.806193389297661e-11</v>
+        <v>2.195732738048536e-18</v>
       </c>
       <c r="DV7" t="n">
-        <v>2.042850263950236e-12</v>
+        <v>2.092950170264841e-18</v>
       </c>
       <c r="DW7" t="n">
-        <v>1.078730854642274e-11</v>
+        <v>5.177922332732889e-17</v>
       </c>
       <c r="DX7" t="n">
-        <v>3.215196511807683e-11</v>
+        <v>1.07434730810367e-17</v>
       </c>
       <c r="DY7" t="n">
-        <v>3.479266874606424e-11</v>
+        <v>1.30603381479875e-18</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.084052375117551e-11</v>
+        <v>3.044640076570881e-18</v>
       </c>
       <c r="EA7" t="n">
-        <v>1.055524764814741e-11</v>
+        <v>4.452142151878041e-17</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.141748154354083e-11</v>
+        <v>8.467292065333709e-18</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.219503656726186e-13</v>
+        <v>4.770328424152894e-17</v>
       </c>
       <c r="ED7" t="n">
-        <v>5.520593704400056e-11</v>
+        <v>2.247455018262497e-17</v>
       </c>
       <c r="EE7" t="n">
-        <v>4.500158926057374e-12</v>
+        <v>4.998804973762901e-17</v>
       </c>
       <c r="EF7" t="n">
-        <v>1.508891622759023e-11</v>
+        <v>1.070798537839695e-17</v>
       </c>
       <c r="EG7" t="n">
-        <v>2.922172920305499e-11</v>
+        <v>3.809095252401768e-17</v>
       </c>
       <c r="EH7" t="n">
-        <v>2.889711560316588e-11</v>
+        <v>3.685252087196044e-17</v>
       </c>
       <c r="EI7" t="n">
-        <v>2.859068537475196e-11</v>
+        <v>7.598313023811641e-17</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1.76218848541021e-12</v>
+        <v>3.80522140015706e-17</v>
       </c>
       <c r="EK7" t="n">
-        <v>4.140346399061912e-11</v>
+        <v>3.053066151880653e-18</v>
       </c>
       <c r="EL7" t="n">
-        <v>5.769482114281743e-12</v>
+        <v>1.67549932935148e-17</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.542667382725682e-11</v>
+        <v>4.472587078770147e-18</v>
       </c>
       <c r="EN7" t="n">
-        <v>1.325798325291228e-11</v>
+        <v>5.273075234700579e-17</v>
       </c>
       <c r="EO7" t="n">
-        <v>2.016347852573652e-11</v>
+        <v>4.194522374926566e-17</v>
       </c>
       <c r="EP7" t="n">
-        <v>1.392747115552817e-11</v>
+        <v>7.739385699432355e-17</v>
       </c>
       <c r="EQ7" t="n">
-        <v>2.120806134875419e-11</v>
+        <v>9.066244944204985e-17</v>
       </c>
       <c r="ER7" t="n">
-        <v>5.644371081636734e-11</v>
+        <v>1.458928555734072e-17</v>
       </c>
       <c r="ES7" t="n">
-        <v>5.235180344786983e-12</v>
+        <v>1.721079958953357e-17</v>
       </c>
       <c r="ET7" t="n">
-        <v>1.296297791331114e-11</v>
+        <v>9.461386475843607e-17</v>
       </c>
       <c r="EU7" t="n">
-        <v>1.941920799511387e-12</v>
+        <v>5.732100255918915e-17</v>
       </c>
       <c r="EV7" t="n">
-        <v>4.668223273218697e-13</v>
+        <v>1.999359729756202e-17</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.890234496704224e-11</v>
+        <v>4.884046898660969e-17</v>
       </c>
       <c r="EX7" t="n">
-        <v>3.957427918352407e-13</v>
+        <v>4.006282868161344e-17</v>
       </c>
       <c r="EY7" t="n">
-        <v>1.812462853412189e-11</v>
+        <v>1.072570855020151e-17</v>
       </c>
       <c r="EZ7" t="n">
-        <v>3.046734739498014e-12</v>
+        <v>3.507975701397354e-17</v>
       </c>
       <c r="FA7" t="n">
-        <v>6.02087910778204e-12</v>
+        <v>5.690016615074667e-17</v>
       </c>
       <c r="FB7" t="n">
-        <v>1.601984170318538e-12</v>
+        <v>1.106134535555103e-17</v>
       </c>
       <c r="FC7" t="n">
-        <v>3.286325725437855e-11</v>
+        <v>4.50414898222272e-17</v>
       </c>
       <c r="FD7" t="n">
-        <v>2.936193996272429e-11</v>
+        <v>2.361167371634039e-17</v>
       </c>
       <c r="FE7" t="n">
-        <v>7.287057242344464e-12</v>
+        <v>1.086113042418563e-17</v>
       </c>
       <c r="FF7" t="n">
-        <v>8.504242449136612e-12</v>
+        <v>4.490001215897858e-17</v>
       </c>
       <c r="FG7" t="n">
-        <v>1.665415375051715e-11</v>
+        <v>1.192374897294779e-16</v>
       </c>
       <c r="FH7" t="n">
-        <v>2.061343630510581e-11</v>
+        <v>4.294154956219598e-17</v>
       </c>
       <c r="FI7" t="n">
-        <v>2.192310569193445e-11</v>
+        <v>3.416107699078235e-17</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.251839430727042e-11</v>
+        <v>3.399789079953789e-17</v>
       </c>
       <c r="FK7" t="n">
-        <v>6.19170860416407e-12</v>
+        <v>1.44501868655338e-17</v>
       </c>
       <c r="FL7" t="n">
-        <v>2.686514205541002e-12</v>
+        <v>4.79599484594368e-17</v>
       </c>
       <c r="FM7" t="n">
-        <v>2.576182843438968e-11</v>
+        <v>4.788496288254764e-17</v>
       </c>
       <c r="FN7" t="n">
-        <v>3.197654988018606e-11</v>
+        <v>2.192975414194652e-17</v>
       </c>
       <c r="FO7" t="n">
-        <v>5.272379408061134e-11</v>
+        <v>7.572430873317102e-17</v>
       </c>
       <c r="FP7" t="n">
-        <v>3.418667432475431e-11</v>
+        <v>2.313228450105773e-17</v>
       </c>
       <c r="FQ7" t="n">
-        <v>9.303358083911917e-11</v>
+        <v>1.52722852804033e-18</v>
       </c>
       <c r="FR7" t="n">
-        <v>2.754004489735618e-11</v>
+        <v>1.605486762304992e-17</v>
       </c>
       <c r="FS7" t="n">
-        <v>2.692911865720404e-12</v>
+        <v>5.373027769454546e-17</v>
       </c>
       <c r="FT7" t="n">
-        <v>9.211996616909079e-12</v>
+        <v>1.128236900784193e-16</v>
       </c>
       <c r="FU7" t="n">
-        <v>5.442434350411141e-11</v>
+        <v>4.018818624908462e-17</v>
       </c>
       <c r="FV7" t="n">
-        <v>1.069038607637296e-11</v>
+        <v>9.561071004079107e-17</v>
       </c>
       <c r="FW7" t="n">
-        <v>4.062943731453217e-11</v>
+        <v>1.173282079831953e-17</v>
       </c>
       <c r="FX7" t="n">
-        <v>2.18534045026697e-12</v>
+        <v>1.325066578949105e-17</v>
       </c>
       <c r="FY7" t="n">
-        <v>5.257046100520801e-12</v>
+        <v>2.567701466570974e-17</v>
       </c>
       <c r="FZ7" t="n">
-        <v>4.14174736174111e-11</v>
+        <v>2.67820038869887e-17</v>
       </c>
       <c r="GA7" t="n">
-        <v>7.375762500760885e-11</v>
+        <v>9.427756289987406e-18</v>
       </c>
       <c r="GB7" t="n">
-        <v>1.265478173639867e-11</v>
+        <v>5.616195046743495e-17</v>
       </c>
       <c r="GC7" t="n">
-        <v>1.597630881755574e-12</v>
+        <v>4.192185093387736e-17</v>
       </c>
       <c r="GD7" t="n">
-        <v>7.115291689174796e-11</v>
+        <v>5.079172187717328e-17</v>
       </c>
       <c r="GE7" t="n">
-        <v>3.606406839828935e-11</v>
+        <v>2.548783018781274e-17</v>
       </c>
       <c r="GF7" t="n">
-        <v>2.707257161504995e-12</v>
+        <v>1.856983252053982e-17</v>
       </c>
       <c r="GG7" t="n">
-        <v>2.943988108849993e-11</v>
+        <v>5.192174985559422e-17</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3985 +4982,3985 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.000720153795555234</v>
+        <v>0.0007925472455099225</v>
       </c>
       <c r="B9" t="n">
-        <v>0.005967602599412203</v>
+        <v>0.002742845797911286</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0006081163883209229</v>
+        <v>0.0003129689139313996</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003519285004585981</v>
+        <v>0.002578871324658394</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001628219848498702</v>
+        <v>0.0005634481203742325</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001285450533032417</v>
+        <v>0.002260505687445402</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003666733100544661</v>
+        <v>0.001278344541788101</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0005313010769896209</v>
+        <v>0.001288432511501014</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001240972080267966</v>
+        <v>0.0002645480562932789</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001349479076452553</v>
+        <v>0.0006742234108969569</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004327191039919853</v>
+        <v>0.002783761825412512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002392859023530036</v>
+        <v>0.001061415998265147</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003461614949628711</v>
+        <v>0.003645192598924041</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002088498789817095</v>
+        <v>0.001261655590496957</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002389704110100865</v>
+        <v>0.002219594782218337</v>
       </c>
       <c r="P9" t="n">
-        <v>7.042393554002047e-05</v>
+        <v>0.001751229865476489</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00049680529627949</v>
+        <v>0.0006053438992239535</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001151526696048677</v>
+        <v>0.0003996712330263108</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001468209957238287</v>
+        <v>0.0003610898857004941</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0004116158233955503</v>
+        <v>8.286653610412031e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.000514355197083205</v>
+        <v>0.0003232386370655149</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001124684233218431</v>
+        <v>0.0001015904199448414</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001508126268163323</v>
+        <v>0.0004481310024857521</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001184739812742919</v>
+        <v>0.001135136815719306</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0006065370398573577</v>
+        <v>0.000125574428238906</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0004070564173161983</v>
+        <v>0.0007725367322564125</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0006173498695716262</v>
+        <v>0.0005764440284110606</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0001228738983627409</v>
+        <v>0.0006490827654488385</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.001148910610936582</v>
+        <v>0.0006805124576203525</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0002920901752077043</v>
+        <v>0.0007105180993676186</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0003979900502599776</v>
+        <v>4.867906682193279e-05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.00083868985529989</v>
+        <v>0.0001287472550757229</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0007657885435037315</v>
+        <v>0.001285700011067092</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0001573225454194471</v>
+        <v>9.733322076499462e-05</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.48000423097983e-05</v>
+        <v>0.0007738979184068739</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0002317680045962334</v>
+        <v>0.0004695529351010919</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.000425622914917767</v>
+        <v>0.0003898984286934137</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0005080216214992106</v>
+        <v>0.0009878531564027071</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.979044751962647e-05</v>
+        <v>0.0009297785582020879</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0001190997209050693</v>
+        <v>0.000661987520288676</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001026339712552726</v>
+        <v>0.0001745083427522331</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0006984083447605371</v>
+        <v>0.0007217384991236031</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0001804803614504635</v>
+        <v>0.0004798647423740476</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.973212632350624e-07</v>
+        <v>0.000174766217241995</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0005290284170769155</v>
+        <v>0.000254668906563893</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.898686453700066e-05</v>
+        <v>0.0001723191526252776</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.003430608427152038</v>
+        <v>0.001505736261606216</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0001864808727987111</v>
+        <v>0.000579831306822598</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001093371189199388</v>
+        <v>0.001302413875237107</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0008305598166771233</v>
+        <v>0.002490206388756633</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0009484593756496906</v>
+        <v>0.001705485628917813</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0008565964526496828</v>
+        <v>1.082051312550902e-05</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.001130484626628458</v>
+        <v>1.334428088739514e-05</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.000385980645660311</v>
+        <v>0.0002661995822563767</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.891870336607099e-05</v>
+        <v>0.0006998237804509699</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.001578572555445135</v>
+        <v>5.433570186141878e-05</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001262985751964152</v>
+        <v>0.0005449102027341723</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0009167036623694003</v>
+        <v>0.0003371034690644592</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001088062068447471</v>
+        <v>0.001272134482860565</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0007163440459407866</v>
+        <v>0.0004014179285150021</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0006913439137861133</v>
+        <v>0.0002859052328858525</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0005354387685656548</v>
+        <v>0.0009055228438228369</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0008654756820760667</v>
+        <v>0.0005015990464016795</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0002980479039251804</v>
+        <v>0.0001681950234342366</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0006080040475353599</v>
+        <v>0.0001642207207623869</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0005106953904032707</v>
+        <v>0.0001034543092828244</v>
       </c>
       <c r="BO9" t="n">
-        <v>9.569391841068864e-05</v>
+        <v>0.0005256083095446229</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0007599319214932621</v>
+        <v>7.859505421947688e-05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0005202039028517902</v>
+        <v>2.117786607414018e-05</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.000150223495438695</v>
+        <v>3.0463510483969e-05</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0003210061113350093</v>
+        <v>0.0004716610710602254</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.0002286470698891208</v>
+        <v>0.0001550618035253137</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.139361458830535e-05</v>
+        <v>5.458158193505369e-05</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.001761959749273956</v>
+        <v>0.001018333365209401</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.000449038838269189</v>
+        <v>0.0004791422397829592</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001096414518542588</v>
+        <v>0.001583150122314692</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0006147519452497363</v>
+        <v>0.0006098127923905849</v>
       </c>
       <c r="BZ9" t="n">
-        <v>5.763491935795173e-05</v>
+        <v>0.001146150287240744</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0003223344101570547</v>
+        <v>0.0002311208372702822</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0007957089110277593</v>
+        <v>0.0001519601355539635</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0007142072427086532</v>
+        <v>0.0005027403822168708</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0001333238324150443</v>
+        <v>6.853890954516828e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001023966236971319</v>
+        <v>0.0009667424601502717</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0003892853565048426</v>
+        <v>4.453674773685634e-05</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0004038851766381413</v>
+        <v>0.001024507451802492</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0001523377723060548</v>
+        <v>7.549308065790683e-05</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0002247800584882498</v>
+        <v>0.0004575330822262913</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0001133278201450594</v>
+        <v>0.0001522997190477327</v>
       </c>
       <c r="CK9" t="n">
-        <v>6.761711119906977e-05</v>
+        <v>0.0002071648777928203</v>
       </c>
       <c r="CL9" t="n">
-        <v>8.250848622992635e-06</v>
+        <v>5.432066245703027e-06</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0007134558400139213</v>
+        <v>0.0001529813162051141</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0001832290145102888</v>
+        <v>0.00066715432330966</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0004768571525346488</v>
+        <v>0.001400341861881316</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0004402694758027792</v>
+        <v>0.001616939436644316</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.0001259816926904023</v>
+        <v>0.0001086558040697128</v>
       </c>
       <c r="CR9" t="n">
-        <v>6.02900399826467e-05</v>
+        <v>0.0004735147231258452</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0008573734667152166</v>
+        <v>0.0001335468696197495</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.001074027852155268</v>
+        <v>0.0005963578005321324</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.617521047592163e-05</v>
+        <v>0.0001578216324560344</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0001397885498590767</v>
+        <v>2.361379301873967e-05</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0008430577581748366</v>
+        <v>0.0009066347847692668</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.000493786355946213</v>
+        <v>0.0001053679152391851</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0005277452291920781</v>
+        <v>0.001124004134908319</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0001640947884880006</v>
+        <v>0.000346887216437608</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0001410793192917481</v>
+        <v>0.0004910616553388536</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0001440020569134504</v>
+        <v>0.0002045425644610077</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0001069629652192816</v>
+        <v>0.0001534590992378071</v>
       </c>
       <c r="DD9" t="n">
-        <v>5.586229963228106e-05</v>
+        <v>6.323102570604533e-05</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0006803485448472202</v>
+        <v>8.008079021237791e-06</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.000391695648431778</v>
+        <v>0.0006253647152334452</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0006193696171976626</v>
+        <v>0.0007158193038776517</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.002400002209469676</v>
+        <v>0.0004396106814965606</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001530177658423781</v>
+        <v>0.0002798955247271806</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0003661207447294146</v>
+        <v>0.001900691306218505</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0004695452516898513</v>
+        <v>9.763614070834592e-05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0007322327001020312</v>
+        <v>0.001823931699618697</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0001234073715750128</v>
+        <v>0.001103207003325224</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0004426580562721938</v>
+        <v>8.038742817007005e-05</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0005142081645317376</v>
+        <v>0.0006576344603672624</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0004983214312233031</v>
+        <v>5.954285734333098e-05</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0003468527283985168</v>
+        <v>0.0003829294582828879</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0003866208135150373</v>
+        <v>0.0001754101540427655</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0004535752232186496</v>
+        <v>0.0002194976550526917</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0002602988388389349</v>
+        <v>0.0004774409753736109</v>
       </c>
       <c r="DU9" t="n">
-        <v>4.588951560435817e-05</v>
+        <v>0.0009241136722266674</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0004316422273404896</v>
+        <v>0.001484543550759554</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0001250653876923025</v>
+        <v>6.804549775552005e-05</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0001252419460797682</v>
+        <v>8.482325938530266e-06</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0005246478831395507</v>
+        <v>0.0005659398157149553</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0001136041537392884</v>
+        <v>0.0004758304567076266</v>
       </c>
       <c r="EA9" t="n">
-        <v>3.689847653731704e-05</v>
+        <v>0.0002174302353523672</v>
       </c>
       <c r="EB9" t="n">
-        <v>3.226832632208243e-06</v>
+        <v>0.001153379096649587</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0001674677769187838</v>
+        <v>0.0003010468790307641</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0004672522481996566</v>
+        <v>0.001980011118575931</v>
       </c>
       <c r="EE9" t="n">
-        <v>6.755047797923908e-05</v>
+        <v>0.001582403783686459</v>
       </c>
       <c r="EF9" t="n">
-        <v>7.475299207726493e-05</v>
+        <v>0.0005373930907808244</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0006945519708096981</v>
+        <v>0.0004438487230800092</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0001743049506330863</v>
+        <v>0.0007490718271583319</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0002828636497724801</v>
+        <v>0.0009040508884936571</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0005202096072025597</v>
+        <v>0.0002150624495698139</v>
       </c>
       <c r="EK9" t="n">
-        <v>5.24500101164449e-05</v>
+        <v>0.0004407201195135713</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001771906681824476</v>
+        <v>7.175575592555106e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>1.862375938799232e-05</v>
+        <v>5.358344060368836e-05</v>
       </c>
       <c r="EN9" t="n">
-        <v>2.348454290768132e-05</v>
+        <v>0.0001238002441823483</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0003079655580222607</v>
+        <v>0.0003286654537077993</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0006996202282607555</v>
+        <v>0.001085991272702813</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0002991393557749689</v>
+        <v>2.153606328647584e-05</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0004446767561603338</v>
+        <v>0.0008199232397601008</v>
       </c>
       <c r="ES9" t="n">
-        <v>8.128178888000548e-05</v>
+        <v>0.000375981762772426</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.00113807967863977</v>
+        <v>0.0001963746908586472</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0005837329663336277</v>
+        <v>0.0004193455097265542</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0006984682404436171</v>
+        <v>0.0004734742105938494</v>
       </c>
       <c r="EW9" t="n">
-        <v>5.166017217561603e-05</v>
+        <v>0.0009065421181730926</v>
       </c>
       <c r="EX9" t="n">
-        <v>4.824158531846479e-05</v>
+        <v>5.813899406348355e-05</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0007860242039896548</v>
+        <v>0.001024060067720711</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0002766039106063545</v>
+        <v>1.645646989345551e-06</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0005200305604375899</v>
+        <v>0.00122494762763381</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0002141291624866426</v>
+        <v>0.0001311529340455309</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0003146051894873381</v>
+        <v>0.0004802930052392185</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0002216182474512607</v>
+        <v>0.0002810380246955901</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.000136611022753641</v>
+        <v>0.0003236925113014877</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0001918934722198173</v>
+        <v>0.0002262512425659224</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0001346517383353785</v>
+        <v>4.41207957919687e-05</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0001613219355931506</v>
+        <v>0.000397674652049318</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0001388563687214628</v>
+        <v>7.265579915838316e-05</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0002695866860449314</v>
+        <v>0.0005661789909936488</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0002949594345409423</v>
+        <v>0.0005207622307352722</v>
       </c>
       <c r="FL9" t="n">
-        <v>6.971507536945865e-05</v>
+        <v>0.0001325664925388992</v>
       </c>
       <c r="FM9" t="n">
-        <v>4.304325557313859e-06</v>
+        <v>0.0002211382379755378</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0001912268053274602</v>
+        <v>0.0001726858463371173</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001727698690956458</v>
+        <v>0.0002098197146551684</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.0008409761940129101</v>
+        <v>0.0008170293876901269</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0002025901630986482</v>
+        <v>0.001326852710917592</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0004486346733756363</v>
+        <v>0.001393326092511415</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0002481775300111622</v>
+        <v>0.001109163044020534</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0002149187203031033</v>
+        <v>0.0006731755565851927</v>
       </c>
       <c r="FU9" t="n">
-        <v>6.163394573377445e-05</v>
+        <v>0.0006096085417084396</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0004221955314278603</v>
+        <v>6.851417128928006e-05</v>
       </c>
       <c r="FW9" t="n">
-        <v>7.757919956929982e-05</v>
+        <v>0.001358374021947384</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0001450665877200663</v>
+        <v>0.0008724528015591204</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0005478187813423574</v>
+        <v>0.0001832871057558805</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0002147386112483218</v>
+        <v>0.0001906925754155964</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0003806080785579979</v>
+        <v>1.255022652912885e-05</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0001000713746179827</v>
+        <v>0.00094417086802423</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0002564387395977974</v>
+        <v>0.0002919720718637109</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0004258131375536323</v>
+        <v>0.0006618786137551069</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.001405735034495592</v>
+        <v>0.0006861394504085183</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0003728396259248257</v>
+        <v>0.0005375872715376318</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0002630202216096222</v>
+        <v>0.0005013722693547606</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.001992031466215849</v>
+        <v>0.0001233359798789024</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02910743467509747</v>
+        <v>0.002027818001806736</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00438915379345417</v>
+        <v>0.0002205808414146304</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01366453804075718</v>
+        <v>0.001955708954483271</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003885743673890829</v>
+        <v>0.0009058148134499788</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01260694861412048</v>
+        <v>0.001401993213221431</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001200519385747612</v>
+        <v>0.001423883251845837</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0002100105339195579</v>
+        <v>0.0002310947456862777</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003763956483453512</v>
+        <v>0.0001994003832805902</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002112552989274263</v>
+        <v>0.0005029080784879625</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01222636271268129</v>
+        <v>0.001438849954865873</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008404625579714775</v>
+        <v>0.0002431853936286643</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02545670978724957</v>
+        <v>0.003214509226381779</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01502394955605268</v>
+        <v>0.001833301968872547</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01832805946469307</v>
+        <v>0.001124418107792735</v>
       </c>
       <c r="P10" t="n">
-        <v>0.003855411894619465</v>
+        <v>0.001356928027234972</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001381043344736099</v>
+        <v>0.0008422902901656926</v>
       </c>
       <c r="R10" t="n">
-        <v>0.002987319603562355</v>
+        <v>0.0002056188095593825</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00149411940947175</v>
+        <v>0.0001435177982784808</v>
       </c>
       <c r="T10" t="n">
-        <v>0.005053594708442688</v>
+        <v>0.0005826351698487997</v>
       </c>
       <c r="U10" t="n">
-        <v>0.006866209208965302</v>
+        <v>0.0001404766517225653</v>
       </c>
       <c r="V10" t="n">
-        <v>0.006744084414094687</v>
+        <v>0.0002437383955111727</v>
       </c>
       <c r="W10" t="n">
-        <v>0.005921815522015095</v>
+        <v>0.0003551549452822655</v>
       </c>
       <c r="X10" t="n">
-        <v>0.006736921612173319</v>
+        <v>0.0004399607132654637</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.002430144464597106</v>
+        <v>8.032967889448628e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.002626699628308415</v>
+        <v>0.0005423967959359288</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.00292715011164546</v>
+        <v>0.0004939443897455931</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.003655892796814442</v>
+        <v>0.0002789938589558005</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.002012253040447831</v>
+        <v>0.0003477000864222646</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0003939988673664629</v>
+        <v>9.764020796865225e-05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.006585525348782539</v>
+        <v>4.108292341697961e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00117994996253401</v>
+        <v>7.207054295577109e-05</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.001411315519362688</v>
+        <v>0.000418773153796792</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0002481164410710335</v>
+        <v>4.038474435219541e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.001934007974341512</v>
+        <v>0.001306340098381042</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0001216596574522555</v>
+        <v>0.0003883499302901328</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.004899816587567329</v>
+        <v>2.987682819366455e-06</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0007761388551443815</v>
+        <v>0.0009854927193373442</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.004368934314697981</v>
+        <v>0.000176558765815571</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.004958355333656073</v>
+        <v>4.25518664997071e-05</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.005423039197921753</v>
+        <v>0.000340492813847959</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.004784338641911745</v>
+        <v>0.0004347567155491561</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.001381781650707126</v>
+        <v>0.0004299417196307331</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.001462827436625957</v>
+        <v>5.765375317423604e-05</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0004077846533618867</v>
+        <v>0.0003884389880113304</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0001084749892470427</v>
+        <v>9.964736818801612e-05</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.02982348762452602</v>
+        <v>0.0007819883758202195</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.01114013604819775</v>
+        <v>0.0003095676947850734</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0009163813083432615</v>
+        <v>0.0002665873616933823</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.01284377463161945</v>
+        <v>0.002506661461666226</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.006536275614053011</v>
+        <v>0.0001272699155379087</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.003068318124860525</v>
+        <v>1.949764555320144e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0056079369969666</v>
+        <v>0.0009708331781439483</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.004068076144903898</v>
+        <v>0.0001695903483778238</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.004852218087762594</v>
+        <v>0.0006275192718021572</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00235804496333003</v>
+        <v>0.0001515041949460283</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.005379712209105492</v>
+        <v>1.875285670394078e-05</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.00650096544995904</v>
+        <v>0.000689291104208678</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.01073310896754265</v>
+        <v>0.0005356910987757146</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0125017873942852</v>
+        <v>0.0007122172391973436</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.004849746357649565</v>
+        <v>0.0004747708735521883</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.294538378715515e-06</v>
+        <v>0.001652883016504347</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0009689130820333958</v>
+        <v>0.0004717284173239022</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.01118450425565243</v>
+        <v>9.519644663669169e-06</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.007908341474831104</v>
+        <v>0.0005325713427737355</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.000893077056389302</v>
+        <v>0.0002226975775556639</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.008817269466817379</v>
+        <v>0.0005359468050301075</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01269435603171587</v>
+        <v>0.0004235771775711328</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.001398043124936521</v>
+        <v>0.0008820423972792923</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.001301726792007685</v>
+        <v>0.000181827213964425</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.00394404074177146</v>
+        <v>0.0006646023248322308</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.003238663310185075</v>
+        <v>0.0002767126425169408</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.001327684614807367</v>
+        <v>0.0003118047316092998</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.01508849207311869</v>
+        <v>0.0007895668386481702</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.006964758038520813</v>
+        <v>0.0002496563538443297</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.00109746481757611</v>
+        <v>0.0008264986099675298</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.004018350038677454</v>
+        <v>0.0009803043212741613</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.01277175080031157</v>
+        <v>0.0007025373633950949</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.001372813363559544</v>
+        <v>0.0002707522653508931</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.003980413544923067</v>
+        <v>0.00041207778849639</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.004833958111703396</v>
+        <v>0.0003012231318280101</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.002239796100184321</v>
+        <v>0.0001064647076418623</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.004294165875762701</v>
+        <v>0.0005184862529858947</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0008602266316302121</v>
+        <v>2.728353865677491e-05</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.00136234296951443</v>
+        <v>0.0006082673789933324</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.002156897913664579</v>
+        <v>3.657827255665325e-05</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.002947729313746095</v>
+        <v>0.0004959512734785676</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.001958217937499285</v>
+        <v>5.253014387562871e-05</v>
       </c>
       <c r="CK10" t="n">
-        <v>9.17186844162643e-05</v>
+        <v>0.000136066199047491</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.00190925772767514</v>
+        <v>0.0002068369940388948</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.004630417097359896</v>
+        <v>0.0004656634409911931</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.006297130137681961</v>
+        <v>4.917593469144776e-05</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.006857686676084995</v>
+        <v>0.0004329501243773848</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.003471959847956896</v>
+        <v>0.001717707491479814</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.003482752945274115</v>
+        <v>0.0007491876604035497</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.009609379805624485</v>
+        <v>0.0007326097693294287</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0002936772652901709</v>
+        <v>0.0007134779007174075</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0007358378497883677</v>
+        <v>0.0004417886666487902</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.001501044491305947</v>
+        <v>9.237262929673307e-06</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.00229521794244647</v>
+        <v>0.0001378169981762767</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.003022783435881138</v>
+        <v>0.0004388538654893637</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0002408449072390795</v>
+        <v>3.527784065227024e-05</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.002871170174330473</v>
+        <v>0.0007350904634222388</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.001767715904861689</v>
+        <v>0.0002105203311657533</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.004066659137606621</v>
+        <v>0.0005217624129727483</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.001070242607966065</v>
+        <v>6.227930134627968e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.000134092231746763</v>
+        <v>0.0001806777145247906</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.001992057776078582</v>
+        <v>0.0002902022970374674</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.001688028918579221</v>
+        <v>0.0004770462983287871</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.001803456107154489</v>
+        <v>0.0005870661698281765</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001869479543529451</v>
+        <v>0.0007904373924247921</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.003336417721584439</v>
+        <v>0.001205678447149694</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.005171297118067741</v>
+        <v>0.0004371497489046305</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0003540424513630569</v>
+        <v>0.000623755156993866</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.003898811293765903</v>
+        <v>0.0004926089313812554</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.003882561810314655</v>
+        <v>0.0005549061461351812</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.000172249972820282</v>
+        <v>0.0005876863724552095</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.009238787926733494</v>
+        <v>8.031198376556858e-06</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.002084168139845133</v>
+        <v>6.968195521039888e-05</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.003888152772560716</v>
+        <v>0.0004019331536255777</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.00273997476324439</v>
+        <v>0.0004289169446565211</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.003082477953284979</v>
+        <v>5.017375951865688e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.00815208163112402</v>
+        <v>0.0002718888863455504</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.003234637202695012</v>
+        <v>0.0001947948185261339</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.003575927345082164</v>
+        <v>0.0007902184152044356</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.002504867734387517</v>
+        <v>0.0007619020179845393</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.002169675659388304</v>
+        <v>1.155554491560906e-05</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.004069625865668058</v>
+        <v>0.0003900981973856688</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.007905174046754837</v>
+        <v>0.0005298590403981507</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.002715876558795571</v>
+        <v>0.0005355128087103367</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.003479269100353122</v>
+        <v>2.436711838527117e-05</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.003021880984306335</v>
+        <v>0.0002994730020873249</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.001957162516191602</v>
+        <v>0.0003138545725960284</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.002124236896634102</v>
+        <v>0.0008276465232484043</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.005094774998724461</v>
+        <v>0.0001330188533756882</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.002020783256739378</v>
+        <v>0.0005528252804651856</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.002228942234069109</v>
+        <v>0.0003141415072605014</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.003604991361498833</v>
+        <v>0.0001437510800315067</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0007208880269899964</v>
+        <v>0.0004282802401576191</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0003067301586270332</v>
+        <v>6.192321598064154e-05</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.001245163031853735</v>
+        <v>0.0009062297758646309</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.002883517649024725</v>
+        <v>9.07401044969447e-07</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.001880485331639647</v>
+        <v>0.0001821604091674089</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.003239486133679748</v>
+        <v>0.0003232582239434123</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.00401024054735899</v>
+        <v>0.0001150985699496232</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.005687786731868982</v>
+        <v>0.0006049041985534132</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.006280234083533287</v>
+        <v>0.0005614194669760764</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.004698367323726416</v>
+        <v>0.0005662450566887856</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.005336232949048281</v>
+        <v>0.000190500621101819</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.01433302648365498</v>
+        <v>0.0001123974216170609</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.001118237618356943</v>
+        <v>0.0003538833116181195</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.006319453008472919</v>
+        <v>0.0001083226961782202</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.003578354138880968</v>
+        <v>0.000109884022094775</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.002229838632047176</v>
+        <v>0.0001224783190991729</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.003184443339705467</v>
+        <v>0.0005036242655478418</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0004518387140706182</v>
+        <v>3.420979192014784e-05</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.001406087772920728</v>
+        <v>0.0008741130586713552</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0008836593478918076</v>
+        <v>0.0001182978085125796</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.004741175100207329</v>
+        <v>0.0004475120513234288</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0006657963385805488</v>
+        <v>5.499034887179732e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001235917909070849</v>
+        <v>0.0001194653450511396</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.003091038204729557</v>
+        <v>0.0002176128909923136</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.001767744077369571</v>
+        <v>0.0003833109803963453</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0008866094285622239</v>
+        <v>0.0001337291323579848</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.003417149418964982</v>
+        <v>0.0004755849076900631</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0003423350281082094</v>
+        <v>0.0002740879426710308</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.001307948492467403</v>
+        <v>0.0003203307278454304</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.002857031300663948</v>
+        <v>0.0004190225154161453</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.0001615820219740272</v>
+        <v>0.0001403752103215083</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.002582551445811987</v>
+        <v>0.0002441052929498255</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.001911950763314962</v>
+        <v>0.0003943239280488342</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.004908388946205378</v>
+        <v>0.0007865105872042477</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.01953811943531036</v>
+        <v>0.0007094118045642972</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.01150115113705397</v>
+        <v>0.0001932399754878134</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.00767588010057807</v>
+        <v>0.0005060405237600207</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.02326302602887154</v>
+        <v>0.0004097833589185029</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.003168832510709763</v>
+        <v>0.000804149080067873</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.00146413326729089</v>
+        <v>0.0009950733510777354</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.00143547379411757</v>
+        <v>0.0001621370320208371</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0005625935737043619</v>
+        <v>0.001683971262536943</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0003960371541325003</v>
+        <v>0.0003138066385872662</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.007449793629348278</v>
+        <v>0.0001324792101513594</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.004022168461233377</v>
+        <v>0.0006821498391218483</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.002085913438349962</v>
+        <v>0.0006756019429303706</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.01165261771529913</v>
+        <v>0.0004002984787803143</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.002454246859997511</v>
+        <v>8.835820335661992e-05</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.0001760537852533162</v>
+        <v>0.001010530046187341</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.00174212281126529</v>
+        <v>0.0001612453779671341</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.002668054774403572</v>
+        <v>0.001368998433463275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7.878166798036546e-05</v>
+        <v>0.0001051668732543476</v>
       </c>
       <c r="B11" t="n">
-        <v>0.001805145293474197</v>
+        <v>0.0002173137036152184</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0001945844123838469</v>
+        <v>3.156752427457832e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000671743880957365</v>
+        <v>6.778112583560869e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001753499731421471</v>
+        <v>3.033427128684707e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001150388037785888</v>
+        <v>0.0002084360457956791</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0004329930525273085</v>
+        <v>0.0001039578637573868</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0005294604343362153</v>
+        <v>0.0001292397791985422</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0002557558764237911</v>
+        <v>7.175331120379269e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001874669105745852</v>
+        <v>7.915527385193855e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0009690099395811558</v>
+        <v>0.0002824990660883486</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000120192657050211</v>
+        <v>5.653395783156157e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0008201501332223415</v>
+        <v>6.453417881857604e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>0.002398792421445251</v>
+        <v>9.776405931916088e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001567579107359052</v>
+        <v>0.0002147065824829042</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0003784652217291296</v>
+        <v>2.954423871415202e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0007064576493576169</v>
+        <v>3.200733772246167e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0001883750228444114</v>
+        <v>7.643153367098421e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>5.349614730221219e-05</v>
+        <v>1.311342111876002e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0005866239662282169</v>
+        <v>4.439523036126047e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>7.553651084890589e-05</v>
+        <v>4.554984479909763e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>8.351907308679074e-05</v>
+        <v>6.466605555033311e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>0.000285644899122417</v>
+        <v>4.452582743397215e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0007855066796764731</v>
+        <v>2.736942860792624e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0003164318040944636</v>
+        <v>2.504627082089428e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.314100417308509e-05</v>
+        <v>7.067995466059074e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.00014441717939917</v>
+        <v>7.86340024205856e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.263503408059478e-05</v>
+        <v>2.501868584658951e-05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.0005139902932569385</v>
+        <v>3.159695188514888e-05</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.333490167278796e-05</v>
+        <v>2.235645661130548e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0007072151638567448</v>
+        <v>6.943221524124965e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0004851168778259307</v>
+        <v>4.568028816720471e-05</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.000662748992908746</v>
+        <v>8.217486902140081e-05</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0001993559417314827</v>
+        <v>2.302906068507582e-05</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.164921119809151e-05</v>
+        <v>0.000141501848702319</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0005343067459762096</v>
+        <v>4.538764187600464e-05</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0002879611274693161</v>
+        <v>3.23453605233226e-07</v>
       </c>
       <c r="AL11" t="n">
-        <v>7.818992889951915e-05</v>
+        <v>5.82293068873696e-05</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.09805761591997e-05</v>
+        <v>5.870267341379076e-05</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.239203452831134e-05</v>
+        <v>1.705160502751824e-05</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0003725019341800362</v>
+        <v>1.376575255562784e-06</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0001525210245745257</v>
+        <v>3.372943319845945e-05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0002517020329833031</v>
+        <v>1.69756131072063e-05</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.867475268431008e-05</v>
+        <v>6.123909406596795e-05</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0003008053754456341</v>
+        <v>1.092111961042974e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0007893992005847394</v>
+        <v>4.198030364932492e-05</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.00227368320338428</v>
+        <v>0.0002242831833427772</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0001356014981865883</v>
+        <v>6.40224025119096e-05</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0004555420018732548</v>
+        <v>1.505487216491019e-05</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0003564134531188756</v>
+        <v>9.807942842599005e-05</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.000871170952450484</v>
+        <v>0.0001218868928845041</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.361769919749349e-05</v>
+        <v>4.141952558711637e-06</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0008449852466583252</v>
+        <v>4.143932528677396e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.203792195767164e-05</v>
+        <v>1.759798124112422e-06</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0002489075413905084</v>
+        <v>1.095902462111553e-06</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.70207474892959e-06</v>
+        <v>1.00350616776268e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0006675744662061334</v>
+        <v>4.665470623876899e-05</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0002388344146311283</v>
+        <v>5.124013114254922e-05</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.002292382065206766</v>
+        <v>1.512090420874301e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.0009852191433310509</v>
+        <v>6.40482030576095e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.0001309954677708447</v>
+        <v>3.535703217494301e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.001109138829633594</v>
+        <v>0.0001173709388240241</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0002057792735286057</v>
+        <v>1.503967359894887e-05</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.0001187007219414227</v>
+        <v>3.983590431744233e-06</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.001365535892546177</v>
+        <v>6.531864346470684e-05</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.0003003160527441651</v>
+        <v>1.196184894070029e-05</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.001178018283098936</v>
+        <v>3.492271935101599e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0006877395790070295</v>
+        <v>5.576427065534517e-05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0004004293587058783</v>
+        <v>8.868350414559245e-05</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0004758474824484438</v>
+        <v>5.503497595782392e-05</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0006310899625532329</v>
+        <v>1.060539852915099e-05</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0001087415148504078</v>
+        <v>6.286167626967654e-05</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0002972908550873399</v>
+        <v>2.271488483529538e-06</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.0007166618015617132</v>
+        <v>0.0001615326327737421</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.0004215546068735421</v>
+        <v>3.745677895494737e-05</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0001210862246807665</v>
+        <v>6.913654215168208e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0001532274909550324</v>
+        <v>1.002155840978958e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>7.353271212195978e-05</v>
+        <v>4.5873734052293e-05</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0005437090876512229</v>
+        <v>3.654533429653384e-05</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0004190223990008235</v>
+        <v>5.371994120650925e-06</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0001464971574023366</v>
+        <v>2.896645582950441e-06</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0001520859805168584</v>
+        <v>4.662646460928954e-05</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.0004085386754013598</v>
+        <v>7.024808292044327e-05</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0002438167866785079</v>
+        <v>8.277731467387639e-06</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0003475492703728378</v>
+        <v>4.033389359392459e-06</v>
       </c>
       <c r="CH11" t="n">
-        <v>2.734253939706832e-05</v>
+        <v>1.923549280036241e-05</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0002153954119421542</v>
+        <v>5.029323801863939e-05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.000187095909495838</v>
+        <v>1.027644248097204e-05</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0002131073561031371</v>
+        <v>9.214571946358774e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>9.813821816351265e-05</v>
+        <v>1.06451589090284e-05</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.0008489257306791842</v>
+        <v>4.889810952590778e-06</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0004959686193615198</v>
+        <v>0.0001142295659519732</v>
       </c>
       <c r="CO11" t="n">
-        <v>7.102805830072612e-05</v>
+        <v>7.539133366663009e-05</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0003138568717986345</v>
+        <v>7.057730545056984e-05</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.000225466545089148</v>
+        <v>1.026770678436151e-05</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0005627702339552343</v>
+        <v>5.538089681067504e-06</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0004569589800667018</v>
+        <v>8.339705527760088e-05</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0001410520053468645</v>
+        <v>1.571385291754268e-05</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0001924499520100653</v>
+        <v>8.781567885307595e-06</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.000156581198098138</v>
+        <v>3.447619383223355e-05</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0002034433273365721</v>
+        <v>5.908244202146307e-05</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0002756131289061159</v>
+        <v>5.541241989703849e-07</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0005095559172332287</v>
+        <v>3.900964657077566e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>3.327307786094025e-05</v>
+        <v>1.483949563407805e-05</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0001684062299318612</v>
+        <v>4.764849290950224e-05</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0002093883522320539</v>
+        <v>8.694186362845358e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0001392964622937143</v>
+        <v>5.150006472831592e-06</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0001091900703613646</v>
+        <v>5.184082510822918e-06</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.0005377393099479377</v>
+        <v>4.713365342468023e-07</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.001123619033023715</v>
+        <v>6.678314821328968e-05</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0001096989872166887</v>
+        <v>1.902431904454716e-05</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.001067237695679069</v>
+        <v>2.453969864291139e-05</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0001071087172022089</v>
+        <v>6.799490074627101e-05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0001416455197613686</v>
+        <v>2.806116572173778e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0007825532811693847</v>
+        <v>1.024051744025201e-05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0001484191161580384</v>
+        <v>6.973442214075476e-05</v>
       </c>
       <c r="DM11" t="n">
-        <v>7.930559513624758e-05</v>
+        <v>0.0001043410738930106</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.000270653807092458</v>
+        <v>1.579015588504262e-06</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0002145040343748406</v>
+        <v>4.471605643630028e-05</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0005846998537890613</v>
+        <v>3.194157761754468e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0001256207906408235</v>
+        <v>3.53418909071479e-05</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.286464824574068e-05</v>
+        <v>1.320876890531508e-05</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0001464284723624587</v>
+        <v>2.595431942609139e-05</v>
       </c>
       <c r="DT11" t="n">
-        <v>2.374576069996692e-05</v>
+        <v>2.825780939019751e-05</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0002846034767571837</v>
+        <v>4.063705637236126e-05</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0001806376385502517</v>
+        <v>4.611777967511443e-06</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0002787842822726816</v>
+        <v>1.782521212589927e-05</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0001785887870937586</v>
+        <v>4.149897904426325e-06</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0002812620950862765</v>
+        <v>2.628664333315101e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.000525103707332164</v>
+        <v>1.796536889742129e-05</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0004660268896259367</v>
+        <v>2.514252628316171e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0001113761536544189</v>
+        <v>1.064450043486431e-05</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0002787245030049235</v>
+        <v>7.435005954903318e-06</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.00014313924475573</v>
+        <v>4.441721102921292e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0002523290168028325</v>
+        <v>0.0001004012010525912</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0002766488178167492</v>
+        <v>4.430629633134231e-05</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0002097520482493564</v>
+        <v>8.236551366280764e-06</v>
       </c>
       <c r="EH11" t="n">
-        <v>3.866566839860752e-05</v>
+        <v>3.316161382826976e-05</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0005872136680409312</v>
+        <v>4.409144457895309e-05</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0002457955270074308</v>
+        <v>3.378829569555819e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>3.730927710421383e-05</v>
+        <v>2.439066520310007e-05</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0004120004596188664</v>
+        <v>5.806316949019674e-06</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0002324019442312419</v>
+        <v>9.680420589575078e-07</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0001475188764743507</v>
+        <v>1.115581380872754e-05</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0005455153295770288</v>
+        <v>3.252858732594177e-05</v>
       </c>
       <c r="EP11" t="n">
-        <v>1.216752298205392e-05</v>
+        <v>4.236925451550633e-05</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0001156206199084409</v>
+        <v>8.657528269395698e-06</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0002126262115780264</v>
+        <v>5.750571290263906e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0004208161844871938</v>
+        <v>0.0001091491867555305</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0002453620254527777</v>
+        <v>4.893841105513275e-05</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0001431268465239555</v>
+        <v>1.628832433198113e-05</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.0002039542741840705</v>
+        <v>2.732064967858605e-05</v>
       </c>
       <c r="EW11" t="n">
-        <v>1.850324042607099e-05</v>
+        <v>1.246256215381436e-05</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0001741471642162651</v>
+        <v>4.486915713641793e-05</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.00015739091031719</v>
+        <v>7.546420965809375e-05</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.000130815344164148</v>
+        <v>1.387677230013651e-06</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0003676201158668846</v>
+        <v>1.101408815884497e-05</v>
       </c>
       <c r="FB11" t="n">
-        <v>5.338263872545213e-05</v>
+        <v>2.560009306762367e-05</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0003271753084845841</v>
+        <v>3.695161285577342e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0002064879226963967</v>
+        <v>1.345419877907261e-05</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0001656899985391647</v>
+        <v>1.754651293595089e-06</v>
       </c>
       <c r="FF11" t="n">
-        <v>5.057507951278239e-05</v>
+        <v>2.068011417577509e-05</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0003733386110980064</v>
+        <v>2.783203854050953e-05</v>
       </c>
       <c r="FH11" t="n">
-        <v>2.476129884598777e-05</v>
+        <v>7.401160837616771e-05</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0002496991364751011</v>
+        <v>4.069397982675582e-05</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.000109120926936157</v>
+        <v>8.885325223673135e-05</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.00036407116567716</v>
+        <v>4.12608751503285e-05</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0003066901699639857</v>
+        <v>8.748711843509227e-05</v>
       </c>
       <c r="FM11" t="n">
-        <v>2.074757503578439e-05</v>
+        <v>4.4048203562852e-05</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0001728127099340782</v>
+        <v>8.980781421996653e-05</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0004321744199842215</v>
+        <v>6.584162474609911e-05</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.0005068458267487586</v>
+        <v>4.102607636014e-05</v>
       </c>
       <c r="FQ11" t="n">
-        <v>1.673492079135031e-06</v>
+        <v>4.332778189564124e-05</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0001355560525553301</v>
+        <v>7.835391443222761e-05</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.0009725781856104732</v>
+        <v>8.706869266461581e-06</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.0009882443118840456</v>
+        <v>1.612607775314245e-05</v>
       </c>
       <c r="FU11" t="n">
-        <v>2.63826223090291e-07</v>
+        <v>3.03907654597424e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0007507055997848511</v>
+        <v>1.563089608680457e-05</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0001600425457581878</v>
+        <v>9.7200449090451e-05</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0002782559313345701</v>
+        <v>4.315664409659803e-05</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.0006444682367146015</v>
+        <v>5.224504275247455e-05</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0006833037477917969</v>
+        <v>1.950829391716979e-05</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0002762364165391773</v>
+        <v>5.051792322774418e-05</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0007015374139882624</v>
+        <v>2.228473022114486e-06</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0003934543929062784</v>
+        <v>0.0001061670700437389</v>
       </c>
       <c r="GD11" t="n">
-        <v>9.133033745456487e-05</v>
+        <v>6.316019425867125e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.0002861190005205572</v>
+        <v>8.225948477047496e-06</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0007254097727127373</v>
+        <v>1.359671205136692e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0003799241676460952</v>
+        <v>5.376563422032632e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.157431663363241e-05</v>
+        <v>5.484704524860717e-05</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0001468023692723364</v>
+        <v>0.0007432471611537039</v>
       </c>
       <c r="C12" t="n">
-        <v>1.05480521597201e-05</v>
+        <v>0.0001697379484539852</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0001053658343153074</v>
+        <v>0.0004331337695475668</v>
       </c>
       <c r="E12" t="n">
-        <v>4.803393676411361e-05</v>
+        <v>0.0001202791900141165</v>
       </c>
       <c r="F12" t="n">
-        <v>3.765665314858779e-05</v>
+        <v>0.0002902446140069515</v>
       </c>
       <c r="G12" t="n">
-        <v>1.135353159043007e-06</v>
+        <v>0.000188387930393219</v>
       </c>
       <c r="H12" t="n">
-        <v>9.59411590883974e-06</v>
+        <v>0.0001770816743373871</v>
       </c>
       <c r="I12" t="n">
-        <v>1.614358188817278e-05</v>
+        <v>4.222366987960413e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>2.945557025668677e-05</v>
+        <v>1.653746039664838e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>9.529879753245041e-05</v>
+        <v>0.0007527837296947837</v>
       </c>
       <c r="L12" t="n">
-        <v>2.963068936878699e-06</v>
+        <v>0.000235437648370862</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0001125559938373044</v>
+        <v>0.0005873589543625712</v>
       </c>
       <c r="N12" t="n">
-        <v>7.103286043275148e-05</v>
+        <v>0.0003155636077281088</v>
       </c>
       <c r="O12" t="n">
-        <v>6.456531264120713e-05</v>
+        <v>0.000227946977247484</v>
       </c>
       <c r="P12" t="n">
-        <v>6.877326086396351e-06</v>
+        <v>0.0001678548869676888</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.063165422645397e-06</v>
+        <v>3.413580634514801e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>2.437033253954723e-05</v>
+        <v>0.0001160693791462108</v>
       </c>
       <c r="S12" t="n">
-        <v>2.153483364963904e-06</v>
+        <v>4.826403710467275e-06</v>
       </c>
       <c r="T12" t="n">
-        <v>2.286471863044426e-05</v>
+        <v>7.114034815458581e-06</v>
       </c>
       <c r="U12" t="n">
-        <v>4.786329554917756e-07</v>
+        <v>2.686308471311349e-05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.030270141200162e-05</v>
+        <v>3.578426185413264e-05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.163220986200031e-05</v>
+        <v>8.146751497406512e-05</v>
       </c>
       <c r="X12" t="n">
-        <v>2.571389995864592e-05</v>
+        <v>0.0001487416739109904</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.392957685515285e-05</v>
+        <v>8.482305565848947e-05</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.69966951943934e-05</v>
+        <v>8.52350567583926e-05</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.252706169907469e-06</v>
+        <v>0.0001099448854802176</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.565900129207876e-05</v>
+        <v>7.463066867785528e-05</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.947820030385628e-05</v>
+        <v>1.617557427380234e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.114088708069175e-06</v>
+        <v>9.75483053480275e-05</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.229434176115319e-05</v>
+        <v>9.579303878126666e-05</v>
       </c>
       <c r="AF12" t="n">
-        <v>3.973620187025517e-05</v>
+        <v>6.752331682946533e-05</v>
       </c>
       <c r="AG12" t="n">
-        <v>9.412810868525412e-06</v>
+        <v>0.0002702444617170841</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.233299099112628e-05</v>
+        <v>6.498157017631456e-05</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.111345778161194e-06</v>
+        <v>0.0001125941562349908</v>
       </c>
       <c r="AJ12" t="n">
-        <v>8.033501899262774e-07</v>
+        <v>3.893844404956326e-05</v>
       </c>
       <c r="AK12" t="n">
-        <v>7.579858902317937e-06</v>
+        <v>3.316590664326213e-07</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.236283696925966e-05</v>
+        <v>0.0002125742321368307</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.693877599493135e-06</v>
+        <v>0.0001025331221171655</v>
       </c>
       <c r="AN12" t="n">
-        <v>8.535456572644762e-07</v>
+        <v>0.0001177749072667211</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.057500205410179e-05</v>
+        <v>9.598896576790139e-05</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.5461875894689e-06</v>
+        <v>0.0001298507704632357</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5.738479558203835e-07</v>
+        <v>5.114441955811344e-05</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.894380360085052e-06</v>
+        <v>2.238284423583536e-06</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.730464752356056e-06</v>
+        <v>3.261115853092633e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.249294837180059e-05</v>
+        <v>5.440972017822787e-06</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.0001010774067253806</v>
+        <v>0.0003901597810909152</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.828826033393852e-06</v>
+        <v>0.0001172003248939291</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.221404363604961e-05</v>
+        <v>0.0001248511543963104</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.751411092409398e-06</v>
+        <v>0.000388161075534299</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.6730215116404e-06</v>
+        <v>0.0002249910467071459</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.731977317831479e-05</v>
+        <v>3.619875496951863e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.78916593035683e-06</v>
+        <v>6.708933506160975e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.024658558890224e-06</v>
+        <v>3.058598304050975e-05</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.00351153378142e-05</v>
+        <v>5.572209920501336e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.401146412012167e-05</v>
+        <v>7.723436283413321e-05</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.53544840234099e-05</v>
+        <v>0.0001510772854089737</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.166519672959112e-05</v>
+        <v>3.450696385698393e-05</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.31193834124133e-05</v>
+        <v>0.0001498234050814062</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.15457421290921e-05</v>
+        <v>7.331506640184671e-05</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.884277637349442e-05</v>
+        <v>0.0001102620153687894</v>
       </c>
       <c r="BJ12" t="n">
-        <v>3.333465429022908e-06</v>
+        <v>0.0001344645716017112</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.88651119970018e-05</v>
+        <v>7.207364978967234e-05</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.350502134300768e-05</v>
+        <v>3.26411536661908e-05</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.310413244937081e-05</v>
+        <v>4.539888323051855e-05</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.139545202022418e-05</v>
+        <v>8.313509169965982e-06</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.521236405707896e-06</v>
+        <v>8.015357161639258e-05</v>
       </c>
       <c r="BP12" t="n">
-        <v>8.118629011732992e-06</v>
+        <v>6.408212357200682e-05</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.888888492539991e-06</v>
+        <v>4.786709723703098e-06</v>
       </c>
       <c r="BR12" t="n">
-        <v>3.018004281329922e-05</v>
+        <v>8.37626703287242e-06</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.532946771476418e-05</v>
+        <v>4.808093217434362e-05</v>
       </c>
       <c r="BT12" t="n">
-        <v>1.651364073040895e-06</v>
+        <v>6.114585175964748e-06</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.550987680180697e-06</v>
+        <v>8.136433280014899e-06</v>
       </c>
       <c r="BV12" t="n">
-        <v>4.944619286106899e-05</v>
+        <v>0.0003002649755217135</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.027773487294326e-05</v>
+        <v>7.962548988871276e-05</v>
       </c>
       <c r="BX12" t="n">
-        <v>2.263765418319963e-05</v>
+        <v>0.0001958724169526249</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.427375294355443e-06</v>
+        <v>6.990491965552792e-05</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.443850644340273e-05</v>
+        <v>0.0001923650270327926</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.567261046555359e-06</v>
+        <v>6.926184869371355e-05</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.32537138092448e-06</v>
+        <v>2.664221938175615e-05</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.583589892106829e-06</v>
+        <v>9.836134995566681e-05</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.813343821297167e-06</v>
+        <v>1.545982559036929e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>2.630275776027702e-05</v>
+        <v>0.0002423283003736287</v>
       </c>
       <c r="CF12" t="n">
-        <v>7.587737854919396e-06</v>
+        <v>2.749361919995863e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>4.605557933246018e-06</v>
+        <v>0.0001591868349350989</v>
       </c>
       <c r="CH12" t="n">
-        <v>4.675060608860804e-06</v>
+        <v>1.370124300592579e-05</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.117483225243632e-05</v>
+        <v>7.244689913932234e-05</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.136084483732702e-05</v>
+        <v>2.580772161309142e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>5.12929091200931e-06</v>
+        <v>2.410651541140396e-05</v>
       </c>
       <c r="CL12" t="n">
-        <v>4.943267413182184e-07</v>
+        <v>2.497092737030471e-06</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.779045487637632e-05</v>
+        <v>9.609781409380957e-05</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.985613036798895e-06</v>
+        <v>0.0001995626953430474</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.173771215690067e-05</v>
+        <v>0.0002353895106352866</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.829207005561329e-05</v>
+        <v>0.0002458298986312002</v>
       </c>
       <c r="CQ12" t="n">
-        <v>3.155349986627698e-06</v>
+        <v>1.66883892234182e-05</v>
       </c>
       <c r="CR12" t="n">
-        <v>2.270647928526159e-05</v>
+        <v>0.0001498865167377517</v>
       </c>
       <c r="CS12" t="n">
-        <v>1.057901681633666e-05</v>
+        <v>7.588481821585447e-05</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.127660238533281e-05</v>
+        <v>1.019844148686389e-05</v>
       </c>
       <c r="CU12" t="n">
-        <v>2.039730588876409e-06</v>
+        <v>3.766398731386289e-05</v>
       </c>
       <c r="CV12" t="n">
-        <v>4.15014665122726e-06</v>
+        <v>2.250760417155107e-06</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.935951513587497e-05</v>
+        <v>0.0002286477683810517</v>
       </c>
       <c r="CX12" t="n">
-        <v>9.17292527446989e-06</v>
+        <v>4.272489968570881e-05</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.05392300611129e-05</v>
+        <v>0.0001662456779740751</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.04753848972905e-06</v>
+        <v>6.389994086930528e-05</v>
       </c>
       <c r="DA12" t="n">
-        <v>9.89416366792284e-06</v>
+        <v>7.527851266786456e-05</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.127514042309485e-05</v>
+        <v>1.73438911588164e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>8.068518582149409e-06</v>
+        <v>2.66388087766245e-05</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.409310127404751e-06</v>
+        <v>1.972446443687659e-05</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.650287049415056e-05</v>
+        <v>7.193030614871532e-05</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.464633143972605e-05</v>
+        <v>0.0001701032160781324</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.129810804442968e-06</v>
+        <v>1.033751323120669e-05</v>
       </c>
       <c r="DH12" t="n">
-        <v>3.423739326535724e-05</v>
+        <v>0.0001669991324888542</v>
       </c>
       <c r="DI12" t="n">
-        <v>9.78991920419503e-07</v>
+        <v>6.967487570364028e-05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.027453345159302e-05</v>
+        <v>0.000339702790370211</v>
       </c>
       <c r="DK12" t="n">
-        <v>9.831575880525634e-06</v>
+        <v>1.807573426049203e-06</v>
       </c>
       <c r="DL12" t="n">
-        <v>6.880824912514072e-06</v>
+        <v>0.0002738275798037648</v>
       </c>
       <c r="DM12" t="n">
-        <v>6.26411747361999e-06</v>
+        <v>0.0001380369649268687</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.939480898727197e-05</v>
+        <v>1.660300949879456e-05</v>
       </c>
       <c r="DO12" t="n">
-        <v>9.279388905270025e-06</v>
+        <v>0.0001352254475932568</v>
       </c>
       <c r="DP12" t="n">
-        <v>1.732923010422383e-05</v>
+        <v>3.00277242786251e-05</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2.447073711664416e-05</v>
+        <v>0.0001114055048674345</v>
       </c>
       <c r="DR12" t="n">
-        <v>2.081715138047002e-05</v>
+        <v>2.245566520286957e-06</v>
       </c>
       <c r="DS12" t="n">
-        <v>5.55875612917589e-06</v>
+        <v>5.400871305027977e-05</v>
       </c>
       <c r="DT12" t="n">
-        <v>4.900812655250775e-06</v>
+        <v>9.355931251775473e-05</v>
       </c>
       <c r="DU12" t="n">
-        <v>1.39360463435878e-06</v>
+        <v>6.911669333931059e-05</v>
       </c>
       <c r="DV12" t="n">
-        <v>3.621050609581289e-06</v>
+        <v>0.0002183649921789765</v>
       </c>
       <c r="DW12" t="n">
-        <v>4.683682846007287e-07</v>
+        <v>2.931700146291405e-05</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.86963277682662e-06</v>
+        <v>4.149105734541081e-05</v>
       </c>
       <c r="DY12" t="n">
-        <v>1.437745959265158e-05</v>
+        <v>0.0001311830710619688</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2.358905476285145e-05</v>
+        <v>5.685195355908945e-05</v>
       </c>
       <c r="EA12" t="n">
-        <v>1.876518945209682e-05</v>
+        <v>4.41491647507064e-05</v>
       </c>
       <c r="EB12" t="n">
-        <v>5.743704605265521e-07</v>
+        <v>0.0001435939047951251</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.069209065462928e-05</v>
+        <v>2.268417301820591e-05</v>
       </c>
       <c r="ED12" t="n">
-        <v>8.572485057811718e-06</v>
+        <v>0.0002888524031732231</v>
       </c>
       <c r="EE12" t="n">
-        <v>9.937039976648521e-06</v>
+        <v>0.0002617529826238751</v>
       </c>
       <c r="EF12" t="n">
-        <v>2.860270797100384e-06</v>
+        <v>3.307841689093038e-05</v>
       </c>
       <c r="EG12" t="n">
-        <v>1.070454163709655e-05</v>
+        <v>0.0001661918795434758</v>
       </c>
       <c r="EH12" t="n">
-        <v>9.000049772112106e-07</v>
+        <v>0.0001057231784216128</v>
       </c>
       <c r="EI12" t="n">
-        <v>3.703236416185973e-06</v>
+        <v>0.0001349910307908431</v>
       </c>
       <c r="EJ12" t="n">
-        <v>2.050401963060722e-05</v>
+        <v>7.53917993279174e-05</v>
       </c>
       <c r="EK12" t="n">
-        <v>3.84315808332758e-06</v>
+        <v>6.306776776909828e-05</v>
       </c>
       <c r="EL12" t="n">
-        <v>2.291613418492489e-05</v>
+        <v>2.097542164847255e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>1.516147131042089e-05</v>
+        <v>1.166948186437367e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>4.20602646045154e-06</v>
+        <v>4.555123450700194e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>1.65046385518508e-05</v>
+        <v>3.927682701032609e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>1.725158654153347e-05</v>
+        <v>0.0002096057578455657</v>
       </c>
       <c r="EQ12" t="n">
-        <v>7.074442009979975e-07</v>
+        <v>7.901504432084039e-06</v>
       </c>
       <c r="ER12" t="n">
-        <v>1.760479972290341e-05</v>
+        <v>0.0001338392903562635</v>
       </c>
       <c r="ES12" t="n">
-        <v>1.370939799016924e-06</v>
+        <v>1.042246731230989e-05</v>
       </c>
       <c r="ET12" t="n">
-        <v>4.119612640351988e-05</v>
+        <v>1.670334313530475e-06</v>
       </c>
       <c r="EU12" t="n">
-        <v>2.160104850190692e-05</v>
+        <v>5.834861076436937e-05</v>
       </c>
       <c r="EV12" t="n">
-        <v>3.689100594783667e-06</v>
+        <v>6.529035454150289e-05</v>
       </c>
       <c r="EW12" t="n">
-        <v>7.832504707039334e-07</v>
+        <v>9.941025200532749e-05</v>
       </c>
       <c r="EX12" t="n">
-        <v>5.307249466568464e-07</v>
+        <v>1.683949813013896e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>2.060432416328695e-05</v>
+        <v>0.0002601944142952561</v>
       </c>
       <c r="EZ12" t="n">
-        <v>3.92601123166969e-06</v>
+        <v>3.24778666254133e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>1.08402527985163e-05</v>
+        <v>0.0001852576970122755</v>
       </c>
       <c r="FB12" t="n">
-        <v>3.239319426029397e-07</v>
+        <v>2.233260602224618e-05</v>
       </c>
       <c r="FC12" t="n">
-        <v>1.731639531499241e-05</v>
+        <v>8.936149970395491e-05</v>
       </c>
       <c r="FD12" t="n">
-        <v>1.339841219305526e-05</v>
+        <v>1.445213911210885e-06</v>
       </c>
       <c r="FE12" t="n">
-        <v>4.785109013027977e-06</v>
+        <v>3.437672057771124e-05</v>
       </c>
       <c r="FF12" t="n">
-        <v>9.389605111209676e-07</v>
+        <v>3.575503797037527e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>1.374188514091657e-07</v>
+        <v>4.099611396668479e-05</v>
       </c>
       <c r="FH12" t="n">
-        <v>3.632554580690339e-06</v>
+        <v>8.817049092613161e-05</v>
       </c>
       <c r="FI12" t="n">
-        <v>3.784647105931072e-06</v>
+        <v>6.321696673694532e-06</v>
       </c>
       <c r="FJ12" t="n">
-        <v>2.116626819770318e-05</v>
+        <v>5.081655035610311e-05</v>
       </c>
       <c r="FK12" t="n">
-        <v>7.229413768072845e-06</v>
+        <v>6.147076783236116e-05</v>
       </c>
       <c r="FL12" t="n">
-        <v>6.069327355362475e-06</v>
+        <v>1.245786916115321e-05</v>
       </c>
       <c r="FM12" t="n">
-        <v>1.619212707737461e-05</v>
+        <v>4.021898348582909e-06</v>
       </c>
       <c r="FN12" t="n">
-        <v>2.133653651981149e-06</v>
+        <v>6.617578765144572e-05</v>
       </c>
       <c r="FO12" t="n">
-        <v>1.168226481240708e-05</v>
+        <v>5.255837459117174e-05</v>
       </c>
       <c r="FP12" t="n">
-        <v>1.177197009383235e-05</v>
+        <v>9.683815733296797e-05</v>
       </c>
       <c r="FQ12" t="n">
-        <v>5.851739388162969e-06</v>
+        <v>0.0001817122829379514</v>
       </c>
       <c r="FR12" t="n">
-        <v>7.965732947923243e-06</v>
+        <v>0.0001205997468787245</v>
       </c>
       <c r="FS12" t="n">
-        <v>1.015384168567834e-05</v>
+        <v>7.474989979527891e-05</v>
       </c>
       <c r="FT12" t="n">
-        <v>5.104117735754699e-05</v>
+        <v>0.0003326040459796786</v>
       </c>
       <c r="FU12" t="n">
-        <v>9.571531336405315e-06</v>
+        <v>4.900393832940608e-07</v>
       </c>
       <c r="FV12" t="n">
-        <v>1.967617572518066e-05</v>
+        <v>3.51913295162376e-05</v>
       </c>
       <c r="FW12" t="n">
-        <v>2.34299532166915e-05</v>
+        <v>0.000116656745376531</v>
       </c>
       <c r="FX12" t="n">
-        <v>1.500977032264927e-05</v>
+        <v>9.326228610007092e-05</v>
       </c>
       <c r="FY12" t="n">
-        <v>1.569244886923116e-05</v>
+        <v>7.724772876827046e-05</v>
       </c>
       <c r="FZ12" t="n">
-        <v>1.056667770171771e-05</v>
+        <v>9.351763583254069e-05</v>
       </c>
       <c r="GA12" t="n">
-        <v>4.507678568188567e-07</v>
+        <v>7.975387416081503e-05</v>
       </c>
       <c r="GB12" t="n">
-        <v>4.539419933280442e-06</v>
+        <v>0.0001584799319971353</v>
       </c>
       <c r="GC12" t="n">
-        <v>1.564051126479171e-05</v>
+        <v>3.348146856296808e-05</v>
       </c>
       <c r="GD12" t="n">
-        <v>4.46331159764668e-06</v>
+        <v>0.0001244913437403738</v>
       </c>
       <c r="GE12" t="n">
-        <v>1.524313574918779e-05</v>
+        <v>0.0001441942586097866</v>
       </c>
       <c r="GF12" t="n">
-        <v>8.563858500565402e-06</v>
+        <v>2.94569708785275e-05</v>
       </c>
       <c r="GG12" t="n">
-        <v>7.695975000387989e-06</v>
+        <v>3.931931860279292e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.006840693764388561</v>
+        <v>0.000626781489700079</v>
       </c>
       <c r="B13" t="n">
-        <v>0.07561153173446655</v>
+        <v>0.1097464486956596</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007363454438745975</v>
+        <v>0.02088509686291218</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04497835785150528</v>
+        <v>0.03091821074485779</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03457587212324142</v>
+        <v>0.0007306933403015137</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05753908306360245</v>
+        <v>0.1140240579843521</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01627708040177822</v>
+        <v>0.04039450734853745</v>
       </c>
       <c r="H13" t="n">
-        <v>0.006845265626907349</v>
+        <v>0.08850305527448654</v>
       </c>
       <c r="I13" t="n">
-        <v>0.006551308557391167</v>
+        <v>0.01962216198444366</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01541309617459774</v>
+        <v>0.008261662907898426</v>
       </c>
       <c r="K13" t="n">
-        <v>0.05757366493344307</v>
+        <v>0.1284949481487274</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0005820505321025848</v>
+        <v>0.04138670861721039</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05448300391435623</v>
+        <v>0.0756838247179985</v>
       </c>
       <c r="N13" t="n">
-        <v>0.04234687238931656</v>
+        <v>0.06021099165081978</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07327611744403839</v>
+        <v>0.1645490378141403</v>
       </c>
       <c r="P13" t="n">
-        <v>0.02386248111724854</v>
+        <v>0.05165410041809082</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02001672051846981</v>
+        <v>0.05981148034334183</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01206421665847301</v>
+        <v>0.03604201972484589</v>
       </c>
       <c r="S13" t="n">
-        <v>0.007509475573897362</v>
+        <v>0.002890468575060368</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01957343704998493</v>
+        <v>0.004309939686208963</v>
       </c>
       <c r="U13" t="n">
-        <v>0.006380942184478045</v>
+        <v>0.0367610976099968</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001301518524996936</v>
+        <v>0.0251034963876009</v>
       </c>
       <c r="W13" t="n">
-        <v>0.01632793992757797</v>
+        <v>0.05706605315208435</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01243989355862141</v>
+        <v>0.0389106422662735</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01227307226508856</v>
+        <v>0.003916917368769646</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.002762132324278355</v>
+        <v>0.004713069181889296</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.007307193242013454</v>
+        <v>0.01275025494396687</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.005325254518538713</v>
+        <v>0.01907274685800076</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01383186131715775</v>
+        <v>0.002303913235664368</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0045210518874228</v>
+        <v>0.005705868359655142</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.02128816023468971</v>
+        <v>0.01308432035148144</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01585446111857891</v>
+        <v>0.02727750316262245</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01086830534040928</v>
+        <v>0.03493429720401764</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.009439953602850437</v>
+        <v>0.0293239951133728</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.001874156296253204</v>
+        <v>0.07345619052648544</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.000931993592530489</v>
+        <v>0.02551658265292645</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.008997601456940174</v>
+        <v>0.01972195133566856</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01410304754972458</v>
+        <v>0.01553979702293873</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.004223557189106941</v>
+        <v>0.01677090302109718</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.001543270424008369</v>
+        <v>0.01568086631596088</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0007053795270621777</v>
+        <v>0.02643673121929169</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.008230340667068958</v>
+        <v>0.0383245088160038</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.00709515018388629</v>
+        <v>0.01016402058303356</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.004476224072277546</v>
+        <v>0.02512931078672409</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.00855591893196106</v>
+        <v>0.01325457170605659</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.02161115407943726</v>
+        <v>0.01710470765829086</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.07176642119884491</v>
+        <v>0.1656492948532104</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.000417503877542913</v>
+        <v>0.07281176000833511</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.003333150874823332</v>
+        <v>0.02502653002738953</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.004960359539836645</v>
+        <v>0.09617404639720917</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.02193224616348743</v>
+        <v>0.1108132377266884</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.007260031066834927</v>
+        <v>0.06854812800884247</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.01576702296733856</v>
+        <v>0.03371156379580498</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.007705107796937227</v>
+        <v>0.01285057608038187</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.009392676874995232</v>
+        <v>0.03480829298496246</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.01102482061833143</v>
+        <v>0.001402236754074693</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.02672976069152355</v>
+        <v>0.01182780228555202</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.00732797384262085</v>
+        <v>0.01757677271962166</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.03908924013376236</v>
+        <v>0.05761447176337242</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.02966242842376232</v>
+        <v>0.01823387295007706</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0003358359099365771</v>
+        <v>0.005168899428099394</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.02733435481786728</v>
+        <v>0.05713219940662384</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.007627734914422035</v>
+        <v>0.0001869155094027519</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.003490924835205078</v>
+        <v>0.01268302835524082</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.02383003756403923</v>
+        <v>0.05290038138628006</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.008249667473137379</v>
+        <v>0.00584286917001009</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.02480542659759521</v>
+        <v>0.01246506907045841</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.01315290667116642</v>
+        <v>0.02246749959886074</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.005291723180562258</v>
+        <v>0.02803661301732063</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0135458717122674</v>
+        <v>0.05277129262685776</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.006077842321246862</v>
+        <v>0.0003825130697805434</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.00525317806750536</v>
+        <v>0.008778526447713375</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.01092126406729221</v>
+        <v>0.02138380147516727</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.02829988114535809</v>
+        <v>0.0816945806145668</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0110804196447134</v>
+        <v>0.03102754801511765</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.01127655059099197</v>
+        <v>0.05483163893222809</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.004682182334363461</v>
+        <v>0.075372613966465</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.008189598098397255</v>
+        <v>0.08831221610307693</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.007705180440098047</v>
+        <v>0.01676614955067635</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0127729494124651</v>
+        <v>0.01351692248135805</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.008081654086709023</v>
+        <v>0.02117477171123028</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0005331957945600152</v>
+        <v>0.01272281631827354</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01428490597754717</v>
+        <v>0.03635294362902641</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.009741424582898617</v>
+        <v>0.000906636007130146</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.01214780937880278</v>
+        <v>0.007793208584189415</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.003852382767945528</v>
+        <v>0.01102108415216208</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.00936247780919075</v>
+        <v>0.03844365105032921</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.006147716660052538</v>
+        <v>0.003185789799317718</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.779472950147465e-05</v>
+        <v>0.01996739208698273</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.003947996068745852</v>
+        <v>0.004341267980635166</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.02173675037920475</v>
+        <v>0.05339360237121582</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01483159326016903</v>
+        <v>0.08291401714086533</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.002163065131753683</v>
+        <v>0.05144460126757622</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.008470400236546993</v>
+        <v>0.06563785672187805</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01442612614482641</v>
+        <v>0.03530040755867958</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.00195824564434588</v>
+        <v>0.07331174612045288</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.003067611716687679</v>
+        <v>0.03520475327968597</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01117746718227863</v>
+        <v>0.01854714192450047</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.002888021059334278</v>
+        <v>0.001349207013845444</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.002305783331394196</v>
+        <v>0.01858941279351711</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.009824237786233425</v>
+        <v>0.02865209802985191</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01012586709111929</v>
+        <v>0.007644332014024258</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.01686756685376167</v>
+        <v>0.004154998809099197</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.001898245769552886</v>
+        <v>0.01166917290538549</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.008782337419688702</v>
+        <v>0.03435595706105232</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.006903538480401039</v>
+        <v>0.009508478455245495</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.005088504403829575</v>
+        <v>0.01461694482713938</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0007483700755983591</v>
+        <v>0.004548820666968822</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.01330390945076942</v>
+        <v>0.00655036186799407</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.02708088234066963</v>
+        <v>0.01271464675664902</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.003450805554166436</v>
+        <v>0.02329700998961926</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.02454096451401711</v>
+        <v>0.001779193058609962</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001717235893011093</v>
+        <v>0.01723376289010048</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.003651427570730448</v>
+        <v>0.001953505910933018</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.02562710829079151</v>
+        <v>0.02998395264148712</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.01047715172171593</v>
+        <v>0.02799640409648418</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.008856476284563541</v>
+        <v>0.02882395498454571</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.006008030381053686</v>
+        <v>0.01361059490591288</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.009803357534110546</v>
+        <v>0.01317932270467281</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.005361157469451427</v>
+        <v>0.001291184686124325</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0069876778870821</v>
+        <v>0.0528331845998764</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.008978813886642456</v>
+        <v>0.01854709163308144</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.001619962975382805</v>
+        <v>0.02822583541274071</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.002801337046548724</v>
+        <v>0.02189898863434792</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.005539322271943092</v>
+        <v>0.02971796691417694</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.002907906658947468</v>
+        <v>0.00225476361811161</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.002056007506325841</v>
+        <v>0.02314564771950245</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.003996568266302347</v>
+        <v>0.002217524917796254</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0107903890311718</v>
+        <v>0.06254499405622482</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.008874624967575073</v>
+        <v>0.01974395476281643</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.004671034868806601</v>
+        <v>0.002999605843797326</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.007771031465381384</v>
+        <v>0.03100159764289856</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.008800309151411057</v>
+        <v>0.008950343355536461</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.002539656590670347</v>
+        <v>0.01418896671384573</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.009574936702847481</v>
+        <v>0.05052515864372253</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.008998310193419456</v>
+        <v>0.03387568145990372</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0004333041433710605</v>
+        <v>0.01384665165096521</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.004247348755598068</v>
+        <v>0.02034788578748703</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01551265548914671</v>
+        <v>0.01157041359692812</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.004645213950425386</v>
+        <v>0.006096915807574987</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.01140690222382545</v>
+        <v>0.01472526602447033</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.01095106825232506</v>
+        <v>0.007748498115688562</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.004324789624661207</v>
+        <v>0.003123576752841473</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0006949154194444418</v>
+        <v>0.0142752667888999</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.00919595081359148</v>
+        <v>0.002775274217128754</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.001500035519711673</v>
+        <v>0.03266191855072975</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.01498556137084961</v>
+        <v>0.01358738727867603</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.01144422776997089</v>
+        <v>0.007840405218303204</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.004881515167653561</v>
+        <v>0.01108858454972506</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01329176500439644</v>
+        <v>0.03209792077541351</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.01040077302604914</v>
+        <v>0.01451164018362761</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.01076499465852976</v>
+        <v>0.01018720492720604</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.005954495631158352</v>
+        <v>0.01468797959387302</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001865665894001722</v>
+        <v>0.01947389915585518</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.009113134816288948</v>
+        <v>0.04229766502976418</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.007715746760368347</v>
+        <v>0.004599664825946093</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.01413063984364271</v>
+        <v>0.00416432972997427</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.003529679728671908</v>
+        <v>0.001607033424079418</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.009867582470178604</v>
+        <v>0.03112541325390339</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.009001683443784714</v>
+        <v>0.003320148214697838</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.002048670081421733</v>
+        <v>0.01243937946856022</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.004177865572273731</v>
+        <v>0.001089292112737894</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.009555774740874767</v>
+        <v>0.01211471389979124</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.007446452043950558</v>
+        <v>0.04714769124984741</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.007811675779521465</v>
+        <v>0.03604359179735184</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.001585801132023335</v>
+        <v>0.02554163336753845</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.001263578538782895</v>
+        <v>0.02141381800174713</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01156407222151756</v>
+        <v>0.008782870136201382</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.002768268808722496</v>
+        <v>0.004479104653000832</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0002810268197208643</v>
+        <v>0.02164500765502453</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.01008627843111753</v>
+        <v>0.06796088814735413</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.008123445324599743</v>
+        <v>0.01114887557923794</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0130779817700386</v>
+        <v>0.1311415284872055</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.003855067770928144</v>
+        <v>0.02180684730410576</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.03207819908857346</v>
+        <v>0.05014479905366898</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01595617271959782</v>
+        <v>0.110481895506382</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.007242346648126841</v>
+        <v>0.06382207572460175</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0009454558603465557</v>
+        <v>0.06779054552316666</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.009455127641558647</v>
+        <v>0.04855042323470116</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.00322451489046216</v>
+        <v>0.0006064767949283123</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01180213131010532</v>
+        <v>0.007768690120428801</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01680423505604267</v>
+        <v>0.01644048467278481</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0004695536335930228</v>
+        <v>0.05855802446603775</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01528344955295324</v>
+        <v>0.01510524842888117</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.003357333596795797</v>
+        <v>0.07007473707199097</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.006931996438652277</v>
+        <v>0.05372600257396698</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.02782107144594193</v>
+        <v>0.001426678150892258</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.02115885354578495</v>
+        <v>6.715476047247648e-05</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.003212625626474619</v>
+        <v>0.01522495038807392</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9.381811651110183e-06</v>
+        <v>0.0002022156259045005</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001011632848531008</v>
+        <v>0.001870073843747377</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001213608629768714</v>
+        <v>0.0004511773004196584</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004561938112601638</v>
+        <v>0.0008228473016060889</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0003320030518807471</v>
+        <v>0.0008646133355796337</v>
       </c>
       <c r="F14" t="n">
-        <v>7.076014298945665e-05</v>
+        <v>0.0007559856749139726</v>
       </c>
       <c r="G14" t="n">
-        <v>4.89318190375343e-05</v>
+        <v>0.0007169217569753528</v>
       </c>
       <c r="H14" t="n">
-        <v>1.391336263623089e-05</v>
+        <v>0.000436376896686852</v>
       </c>
       <c r="I14" t="n">
-        <v>8.147809421643615e-05</v>
+        <v>0.0001110394150600769</v>
       </c>
       <c r="J14" t="n">
-        <v>3.139830369036645e-06</v>
+        <v>3.672879029181786e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0007297155680134892</v>
+        <v>0.002416599774733186</v>
       </c>
       <c r="L14" t="n">
-        <v>1.123236597777577e-05</v>
+        <v>0.0005926151643507183</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0004003154172096401</v>
+        <v>0.001315153203904629</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0004108361317776144</v>
+        <v>0.001276866882108152</v>
       </c>
       <c r="O14" t="n">
-        <v>1.679656998021528e-05</v>
+        <v>0.0003540058969520032</v>
       </c>
       <c r="P14" t="n">
-        <v>4.281147630535997e-05</v>
+        <v>0.000497847911901772</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0001698864507488906</v>
+        <v>0.0002848682925105095</v>
       </c>
       <c r="R14" t="n">
-        <v>1.665582385612652e-05</v>
+        <v>0.0001413936988683417</v>
       </c>
       <c r="S14" t="n">
-        <v>5.020343814976513e-05</v>
+        <v>4.01498909923248e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0001728955248836428</v>
+        <v>0.0001497925986768678</v>
       </c>
       <c r="U14" t="n">
-        <v>7.098953938111663e-05</v>
+        <v>7.272160473803524e-06</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0001218235556734726</v>
+        <v>0.0002488766040187329</v>
       </c>
       <c r="W14" t="n">
-        <v>7.777735299896449e-05</v>
+        <v>0.0001712881057756022</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0001287593913730234</v>
+        <v>0.0002666678337845951</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.33494133176282e-05</v>
+        <v>0.0002271726552862674</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.842821802711114e-05</v>
+        <v>0.0002104313171003014</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.460264216912037e-07</v>
+        <v>0.0002960678830277175</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.063334098551422e-05</v>
+        <v>0.0001847837993409485</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.824167500482872e-05</v>
+        <v>0.0004257990512996912</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.427906787896063e-07</v>
+        <v>0.0002695498405955732</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.185432120109908e-05</v>
+        <v>0.0004134477931074798</v>
       </c>
       <c r="AF14" t="n">
-        <v>8.815251931082457e-05</v>
+        <v>0.0002845053095370531</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0001551750756334513</v>
+        <v>0.0005292011774145067</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.062860337697202e-05</v>
+        <v>4.662583523895591e-05</v>
       </c>
       <c r="AI14" t="n">
-        <v>8.394011092605069e-05</v>
+        <v>0.0006366558955051005</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4.017708488390781e-05</v>
+        <v>9.373234206577763e-07</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0001516473712399602</v>
+        <v>1.75646291609155e-05</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.122345671930816e-06</v>
+        <v>0.000636604439932853</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.437984923948534e-05</v>
+        <v>0.0002277719613630325</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0001124027330661193</v>
+        <v>0.0003703782567754388</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.00017898905207403</v>
+        <v>0.0002677507582120597</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0001673153456067666</v>
+        <v>0.0002548315096646547</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.687875621631974e-06</v>
+        <v>1.79727649083361e-05</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.12801847839728e-05</v>
+        <v>0.0002898458042182028</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.704596408875659e-05</v>
+        <v>1.897867696243338e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.730173820164055e-06</v>
+        <v>0.0001206198357976973</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.0006727034342475235</v>
+        <v>0.00221210578456521</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.202337170980172e-05</v>
+        <v>1.065221294993535e-05</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.161163790035062e-05</v>
+        <v>0.0002699440228752792</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.951156734023243e-05</v>
+        <v>0.0007759261061437428</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.62877426596242e-06</v>
+        <v>0.0003716488718055189</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7.750021904939786e-05</v>
+        <v>6.32188020972535e-05</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0001197385645355098</v>
+        <v>8.358154445886612e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.750324534252286e-05</v>
+        <v>0.0001609495375305414</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.819203655235469e-05</v>
+        <v>5.789560236735269e-05</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0001326245110249147</v>
+        <v>0.000422088080085814</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0002063229621853679</v>
+        <v>0.0004508155107032508</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0001689183554844931</v>
+        <v>2.796863554976881e-05</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0004628202295862138</v>
+        <v>2.695361763471738e-05</v>
       </c>
       <c r="BH14" t="n">
-        <v>1.737577622407116e-05</v>
+        <v>0.0001765975030139089</v>
       </c>
       <c r="BI14" t="n">
-        <v>8.653386612422764e-05</v>
+        <v>0.0001414503785781562</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0001265232422156259</v>
+        <v>0.0002614018158055842</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.37385932248435e-05</v>
+        <v>0.00018960380111821</v>
       </c>
       <c r="BL14" t="n">
-        <v>7.755251863272861e-05</v>
+        <v>1.176185833173804e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0002101731224684045</v>
+        <v>0.0004161496763117611</v>
       </c>
       <c r="BN14" t="n">
-        <v>6.723123806295916e-05</v>
+        <v>0.0001238736149389297</v>
       </c>
       <c r="BO14" t="n">
-        <v>8.038926353037823e-06</v>
+        <v>0.0002405361738055944</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0002200141607318074</v>
+        <v>0.0005082260468043387</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0001397028972860426</v>
+        <v>0.0001764119951985776</v>
       </c>
       <c r="BR14" t="n">
-        <v>6.992526323301718e-05</v>
+        <v>0.0004764554614666849</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.767715189605951e-05</v>
+        <v>7.946158439153805e-05</v>
       </c>
       <c r="BT14" t="n">
-        <v>8.55045800562948e-05</v>
+        <v>4.244607407599688e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>6.930201197974384e-05</v>
+        <v>0.0001668130280449986</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0003399972047191113</v>
+        <v>0.001397427171468735</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.070202941074967e-05</v>
+        <v>6.427467451430857e-05</v>
       </c>
       <c r="BX14" t="n">
-        <v>2.659593974385643e-06</v>
+        <v>0.0006272562313824892</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.036259502347093e-05</v>
+        <v>0.0001860399206634611</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0001521305384812877</v>
+        <v>0.0002443215344101191</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.080163565347902e-05</v>
+        <v>0.0003710301825776696</v>
       </c>
       <c r="CB14" t="n">
-        <v>1.378838715027086e-05</v>
+        <v>2.69170031970134e-05</v>
       </c>
       <c r="CC14" t="n">
-        <v>7.203984569059685e-05</v>
+        <v>0.0001857711613411084</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.417897434905171e-05</v>
+        <v>5.621773379971273e-05</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.0001845294609665871</v>
+        <v>0.0006961114704608917</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.697557258419693e-05</v>
+        <v>0.0001153053235611878</v>
       </c>
       <c r="CG14" t="n">
-        <v>5.680439426214434e-05</v>
+        <v>0.0002569560892879963</v>
       </c>
       <c r="CH14" t="n">
-        <v>3.197944897692651e-05</v>
+        <v>0.0001770632079569623</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.225106643687468e-05</v>
+        <v>0.0001979036605916917</v>
       </c>
       <c r="CJ14" t="n">
-        <v>7.170384924393147e-05</v>
+        <v>3.279395969002508e-05</v>
       </c>
       <c r="CK14" t="n">
-        <v>3.639694477897137e-05</v>
+        <v>4.48289247287903e-05</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.019792762235738e-05</v>
+        <v>5.06675751239527e-05</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0003153658180963248</v>
+        <v>0.0004562857211567461</v>
       </c>
       <c r="CN14" t="n">
-        <v>8.689900278113782e-05</v>
+        <v>0.001383245573379099</v>
       </c>
       <c r="CO14" t="n">
-        <v>9.15778218768537e-06</v>
+        <v>0.0003083646297454834</v>
       </c>
       <c r="CP14" t="n">
-        <v>7.634705252712592e-05</v>
+        <v>0.0004988886648789048</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0001208064059028402</v>
+        <v>9.566533844918013e-05</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0003466129710432142</v>
+        <v>3.876509799738415e-05</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.748315455392003e-05</v>
+        <v>0.0002896432706620544</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.048131475225091e-06</v>
+        <v>4.934230310027488e-05</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0001536732888780534</v>
+        <v>1.283809797314461e-05</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.894110002671368e-05</v>
+        <v>2.50207340286579e-05</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0001710164797259495</v>
+        <v>0.0006547531229443848</v>
       </c>
       <c r="CX14" t="n">
-        <v>7.212222408270463e-05</v>
+        <v>0.0001086442134692334</v>
       </c>
       <c r="CY14" t="n">
-        <v>7.44346107239835e-05</v>
+        <v>0.0003587137325666845</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.691596455406398e-05</v>
+        <v>0.0001743628527037799</v>
       </c>
       <c r="DA14" t="n">
-        <v>3.128502839899738e-06</v>
+        <v>0.0001951602462213486</v>
       </c>
       <c r="DB14" t="n">
-        <v>6.645327084697783e-05</v>
+        <v>1.333135696768295e-05</v>
       </c>
       <c r="DC14" t="n">
-        <v>4.815568900085054e-05</v>
+        <v>2.054182732535992e-05</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.091769369551912e-06</v>
+        <v>9.633153240429237e-05</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0001444954832550138</v>
+        <v>0.0002961610443890095</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0002828470023814589</v>
+        <v>0.0002036785735981539</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0001508230925537646</v>
+        <v>3.810597991105169e-05</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0002075350203085691</v>
+        <v>0.0003611257998272777</v>
       </c>
       <c r="DI14" t="n">
-        <v>6.815810047555715e-05</v>
+        <v>0.0001171879848698154</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.846638042479753e-06</v>
+        <v>0.0008177774725481868</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.772542838007212e-05</v>
+        <v>0.0001251498761121184</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.0001280529249925166</v>
+        <v>0.0007758092833682895</v>
       </c>
       <c r="DM14" t="n">
-        <v>8.869892917573452e-05</v>
+        <v>0.0001235447998624295</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.000119241900392808</v>
+        <v>4.901899956166744e-06</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.154645673930645e-05</v>
+        <v>0.0004583279660437256</v>
       </c>
       <c r="DP14" t="n">
-        <v>7.99930148787098e-07</v>
+        <v>7.452170393662527e-05</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0001655595988268033</v>
+        <v>0.0001253987720701844</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.543796578422189e-05</v>
+        <v>9.336404764326289e-05</v>
       </c>
       <c r="DS14" t="n">
-        <v>1.068970959750004e-06</v>
+        <v>6.397702964022756e-05</v>
       </c>
       <c r="DT14" t="n">
-        <v>5.191741365706548e-05</v>
+        <v>0.0002009886084124446</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.000121939112432301</v>
+        <v>0.0005409159930422902</v>
       </c>
       <c r="DV14" t="n">
-        <v>8.56267215567641e-05</v>
+        <v>0.0005495576770044863</v>
       </c>
       <c r="DW14" t="n">
-        <v>7.282239675987512e-05</v>
+        <v>7.874517177697271e-05</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.222371980082244e-05</v>
+        <v>0.0004264234157744795</v>
       </c>
       <c r="DY14" t="n">
-        <v>2.83771805698052e-05</v>
+        <v>4.452571738511324e-05</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.232111364719458e-05</v>
+        <v>9.667447011452168e-05</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0001646111631998792</v>
+        <v>0.0005320749478414655</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0001693712547421455</v>
+        <v>0.000434372021118179</v>
       </c>
       <c r="EC14" t="n">
-        <v>9.38815574045293e-05</v>
+        <v>9.486918861512095e-05</v>
       </c>
       <c r="ED14" t="n">
-        <v>2.555761057010386e-05</v>
+        <v>0.000912153220269829</v>
       </c>
       <c r="EE14" t="n">
-        <v>5.277954915072769e-05</v>
+        <v>0.0004720314173027873</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0001561410317663103</v>
+        <v>0.0001086030024453066</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0001886515674414113</v>
+        <v>0.0002707811072468758</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.0001417663443135098</v>
+        <v>0.0001465775567339733</v>
       </c>
       <c r="EI14" t="n">
-        <v>8.702911873115227e-05</v>
+        <v>0.0002259763568872586</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0001051227009156719</v>
+        <v>0.0002089972404064611</v>
       </c>
       <c r="EK14" t="n">
-        <v>5.422971298685297e-07</v>
+        <v>0.0002511871280148625</v>
       </c>
       <c r="EL14" t="n">
-        <v>9.588961984263733e-05</v>
+        <v>8.933588105719537e-06</v>
       </c>
       <c r="EM14" t="n">
-        <v>4.726199404103681e-05</v>
+        <v>2.498203230061335e-06</v>
       </c>
       <c r="EN14" t="n">
-        <v>2.143922574759927e-05</v>
+        <v>5.776400939794257e-05</v>
       </c>
       <c r="EO14" t="n">
-        <v>6.033899626345374e-05</v>
+        <v>0.0001636180531932041</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0001875004963949323</v>
+        <v>0.0003587618994060904</v>
       </c>
       <c r="EQ14" t="n">
-        <v>1.265498576685786e-05</v>
+        <v>0.000117416784632951</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0001046877296175808</v>
+        <v>0.0003221379593014717</v>
       </c>
       <c r="ES14" t="n">
-        <v>5.284714279696345e-05</v>
+        <v>0.0001284276804653928</v>
       </c>
       <c r="ET14" t="n">
-        <v>8.144706953316927e-08</v>
+        <v>0.0001668063632678241</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0001092955862986855</v>
+        <v>0.0001502648374298587</v>
       </c>
       <c r="EV14" t="n">
-        <v>6.497359572676942e-05</v>
+        <v>0.0001315569243161008</v>
       </c>
       <c r="EW14" t="n">
-        <v>3.579671101761051e-06</v>
+        <v>0.0003130714176222682</v>
       </c>
       <c r="EX14" t="n">
-        <v>7.365956844296306e-05</v>
+        <v>2.791447514027823e-06</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0001786749780876562</v>
+        <v>0.0008005995769053698</v>
       </c>
       <c r="EZ14" t="n">
-        <v>4.208664176985621e-05</v>
+        <v>9.074758418137208e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>7.707376789767295e-05</v>
+        <v>0.0003519599558785558</v>
       </c>
       <c r="FB14" t="n">
-        <v>1.918120688060299e-06</v>
+        <v>0.000128477651742287</v>
       </c>
       <c r="FC14" t="n">
-        <v>1.207051445817342e-05</v>
+        <v>0.0002522396680433303</v>
       </c>
       <c r="FD14" t="n">
-        <v>5.943933138041757e-05</v>
+        <v>0.0001076179323717952</v>
       </c>
       <c r="FE14" t="n">
-        <v>5.777146725449711e-05</v>
+        <v>0.000105337385321036</v>
       </c>
       <c r="FF14" t="n">
-        <v>1.543371035950258e-05</v>
+        <v>0.0001442867069272324</v>
       </c>
       <c r="FG14" t="n">
-        <v>2.242327536805533e-05</v>
+        <v>2.519944973755628e-05</v>
       </c>
       <c r="FH14" t="n">
-        <v>1.557250288897194e-05</v>
+        <v>0.0001969832519534975</v>
       </c>
       <c r="FI14" t="n">
-        <v>2.89672716462519e-05</v>
+        <v>0.0001618875248823315</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.000162012453074567</v>
+        <v>0.0003321093681734055</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0001535160699859262</v>
+        <v>9.81699486146681e-05</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0001273469824809581</v>
+        <v>6.144022336229682e-05</v>
       </c>
       <c r="FM14" t="n">
-        <v>4.674494994105771e-05</v>
+        <v>4.156396244070493e-05</v>
       </c>
       <c r="FN14" t="n">
-        <v>1.04149839899037e-05</v>
+        <v>2.070349364657886e-05</v>
       </c>
       <c r="FO14" t="n">
-        <v>4.254397936165333e-07</v>
+        <v>0.0001822967897169292</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.0001757171412464231</v>
+        <v>0.0003567099338397384</v>
       </c>
       <c r="FQ14" t="n">
-        <v>1.186536519526271e-05</v>
+        <v>0.0003991897392552346</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.0002222200710093603</v>
+        <v>0.0005551647627726197</v>
       </c>
       <c r="FS14" t="n">
-        <v>9.411603059561457e-06</v>
+        <v>4.502318915911019e-06</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0001030476560117677</v>
+        <v>0.0005997869302518666</v>
       </c>
       <c r="FU14" t="n">
-        <v>3.067001671297476e-05</v>
+        <v>0.0002408616855973378</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0001139184605563059</v>
+        <v>0.0001957988133653998</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0001410499098710716</v>
+        <v>0.0002668896340765059</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0001520759687991813</v>
+        <v>0.0003388600598555058</v>
       </c>
       <c r="FY14" t="n">
-        <v>8.505659207003191e-05</v>
+        <v>4.245802847435698e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>5.230376336839981e-05</v>
+        <v>0.0002623008622322232</v>
       </c>
       <c r="GA14" t="n">
-        <v>1.071631777449511e-05</v>
+        <v>0.0001661617425270379</v>
       </c>
       <c r="GB14" t="n">
-        <v>1.940535184985492e-05</v>
+        <v>0.0001058988564182073</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0001164276181953028</v>
+        <v>0.0003624724049586803</v>
       </c>
       <c r="GD14" t="n">
-        <v>4.731757508125156e-05</v>
+        <v>0.0003012920788023621</v>
       </c>
       <c r="GE14" t="n">
-        <v>6.782184937037528e-05</v>
+        <v>0.0004821117909159511</v>
       </c>
       <c r="GF14" t="n">
-        <v>4.605271897162311e-05</v>
+        <v>0.0002539450360927731</v>
       </c>
       <c r="GG14" t="n">
-        <v>5.44840149814263e-05</v>
+        <v>3.560981713235378e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.0008848531870171428</v>
+        <v>0.001564322970807552</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02114017121493816</v>
+        <v>0.01357057224959135</v>
       </c>
       <c r="C15" t="n">
-        <v>0.004075835458934307</v>
+        <v>0.003816482145339251</v>
       </c>
       <c r="D15" t="n">
-        <v>0.008379168808460236</v>
+        <v>0.008790021762251854</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0073583098128438</v>
+        <v>0.0002143130986951292</v>
       </c>
       <c r="F15" t="n">
-        <v>0.002848426345735788</v>
+        <v>0.004257299471646547</v>
       </c>
       <c r="G15" t="n">
-        <v>0.003730226308107376</v>
+        <v>0.004025153815746307</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001516175805591047</v>
+        <v>0.003820988582447171</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0007184736896306276</v>
+        <v>0.001259737298823893</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0009921867167577147</v>
+        <v>0.0006303704576566815</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01693116128444672</v>
+        <v>0.01439487561583519</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001651783823035657</v>
+        <v>0.004461790435016155</v>
       </c>
       <c r="M15" t="n">
-        <v>0.007486594375222921</v>
+        <v>0.01277441345155239</v>
       </c>
       <c r="N15" t="n">
-        <v>0.00592773174867034</v>
+        <v>0.001806754968129098</v>
       </c>
       <c r="O15" t="n">
-        <v>0.002502877498045564</v>
+        <v>0.001739088329486549</v>
       </c>
       <c r="P15" t="n">
-        <v>0.00356090534478426</v>
+        <v>0.003708067815750837</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.001415685517713428</v>
+        <v>0.0002158131683245301</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0001909344573505223</v>
+        <v>0.0007233901997096837</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0002248647506348789</v>
+        <v>0.0003918604052159935</v>
       </c>
       <c r="T15" t="n">
-        <v>0.003438295098021626</v>
+        <v>0.001582092838361859</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0008532245410606265</v>
+        <v>1.468921254854649e-05</v>
       </c>
       <c r="V15" t="n">
-        <v>0.00209560408256948</v>
+        <v>0.0008481059339828789</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0001528851862531155</v>
+        <v>0.0009724646806716919</v>
       </c>
       <c r="X15" t="n">
-        <v>0.002416815375909209</v>
+        <v>0.001837608171626925</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.002148485742509365</v>
+        <v>0.0003281931858509779</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.001584930112585425</v>
+        <v>0.00130464555695653</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.001743692788295448</v>
+        <v>0.002365598920732737</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.002150720916688442</v>
+        <v>0.00130445952527225</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.003284008707851171</v>
+        <v>0.0002130930661223829</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0002605664194561541</v>
+        <v>0.001694468315690756</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0009575084550306201</v>
+        <v>0.003600078169256449</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001533919596113265</v>
+        <v>7.555189949925989e-05</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0004947695997543633</v>
+        <v>0.002123092301189899</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.00136927398853004</v>
+        <v>0.001552886795252562</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.001095514744520187</v>
+        <v>0.0005852837930433452</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0007737184059806168</v>
+        <v>0.001044758828356862</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0004884451045654714</v>
+        <v>0.000775299733504653</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.003264190629124641</v>
+        <v>0.00340184522792697</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0004177770169917494</v>
+        <v>0.001652249600738287</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.0004905764362774789</v>
+        <v>0.002614803146570921</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.00118668470531702</v>
+        <v>0.003242360893636942</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.001969434786587954</v>
+        <v>0.002233859151601791</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.0009309074375778437</v>
+        <v>0.0004798420704901218</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.001054767519235611</v>
+        <v>4.263498703949153e-05</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.0008218532311730087</v>
+        <v>0.0004300994332879782</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.002786356490105391</v>
+        <v>0.0003669284633360803</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.0141438664868474</v>
+        <v>0.00775764137506485</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.000893855991307646</v>
+        <v>0.0004307186172809452</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.002403111895546317</v>
+        <v>0.004376548808068037</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.003089352045208216</v>
+        <v>0.004961203318089247</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.0002236757427453995</v>
+        <v>0.0007795296842232347</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.0002147553750546649</v>
+        <v>0.0002067960740532726</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.0003436730476096272</v>
+        <v>0.0007346186903305352</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.0003209541027899832</v>
+        <v>0.0009193943114951253</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0002068612957373261</v>
+        <v>0.001194345415569842</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.003670824691653252</v>
+        <v>0.0002704813377931714</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.003322336124256253</v>
+        <v>0.00259461672976613</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.001379677560180426</v>
+        <v>0.001252062735147774</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.006738872732967138</v>
+        <v>0.0007629324682056904</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.363177191000432e-05</v>
+        <v>0.001860187272541225</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.002925967797636986</v>
+        <v>0.0004757298156619072</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.001611581188626587</v>
+        <v>0.001490676659159362</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.0008027476724237204</v>
+        <v>0.002176405396312475</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.002743163146078587</v>
+        <v>0.0008302923524752259</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0007667192840017378</v>
+        <v>0.001131126075051725</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.0005206003552302718</v>
+        <v>0.000899178150575608</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0002232910192105919</v>
+        <v>0.0008914737845771015</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0004096205811947584</v>
+        <v>0.0002408792497590184</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.002515375381335616</v>
+        <v>0.000305277993902564</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.0003139987238682806</v>
+        <v>0.001377335283905268</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.000115518516395241</v>
+        <v>0.0004275269748177379</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.0002331909781787544</v>
+        <v>0.0002834229671861976</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.00217730738222599</v>
+        <v>0.001213147304952145</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.007990839891135693</v>
+        <v>0.006424502935260534</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.002815145067870617</v>
+        <v>0.0008834148175083101</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.002138188807293773</v>
+        <v>0.003591346787288785</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0007418901659548283</v>
+        <v>0.0008710540132597089</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.002505480078980327</v>
+        <v>0.002052931115031242</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.0009576519951224327</v>
+        <v>0.001192124909721315</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0002817802305798978</v>
+        <v>0.0003688003635033965</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.00135930092073977</v>
+        <v>0.001745323417708278</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0002288599062012509</v>
+        <v>0.0004713383386842906</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.003235168289393187</v>
+        <v>0.004024741239845753</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0005188375944271684</v>
+        <v>0.001245481194928288</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.001308097038418055</v>
+        <v>0.003176942933350801</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0003754661302082241</v>
+        <v>0.0004014058504253626</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.001073971390724182</v>
+        <v>0.0007518298225477338</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0002955578966066241</v>
+        <v>0.0001323575852438807</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.0002713039284572005</v>
+        <v>0.0009389762417413294</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.00119308358989656</v>
+        <v>0.0003396858228370547</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.002717230934649706</v>
+        <v>0.00132312870118767</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.001140923239290714</v>
+        <v>0.003763412125408649</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.0003313540364615619</v>
+        <v>0.002270670840516686</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.00111323525197804</v>
+        <v>0.005804590880870819</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.00207892875187099</v>
+        <v>0.002621176419779658</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.001859105308540165</v>
+        <v>0.000440343254012987</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.001940263668075204</v>
+        <v>0.002061898121610284</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.002967201871797442</v>
+        <v>0.0003818433615379035</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.0005083513678982854</v>
+        <v>0.001045371522195637</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.0001322335447184741</v>
+        <v>0.000112403096864</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.002839767374098301</v>
+        <v>0.00387337151914835</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.0008542397990822792</v>
+        <v>0.00110156531445682</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.001794107840396464</v>
+        <v>0.003338868962600827</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0002784065436571836</v>
+        <v>0.000136847491376102</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.001655154279433191</v>
+        <v>0.0006500323070213199</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.0001391354744555429</v>
+        <v>0.0003164499066770077</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.0001395094150211662</v>
+        <v>0.000888716836925596</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.0007336845737881958</v>
+        <v>0.0006643080851063132</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.001081051770597696</v>
+        <v>0.0007829858222976327</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.003889430779963732</v>
+        <v>0.002231785096228123</v>
       </c>
       <c r="DG15" t="n">
-        <v>6.319313251879066e-05</v>
+        <v>6.931420648470521e-05</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.006283474620431662</v>
+        <v>0.002158053684979677</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0001866557286120951</v>
+        <v>0.001903783297166228</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.001650672173127532</v>
+        <v>0.004058500751852989</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.002699763048440218</v>
+        <v>0.0001986189745366573</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.00112432730384171</v>
+        <v>0.004543936811387539</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.001012359745800495</v>
+        <v>0.000841211061924696</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.00132802885491401</v>
+        <v>0.0005361001240089536</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.0008994811796583235</v>
+        <v>0.002568574622273445</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.002394750015810132</v>
+        <v>0.001705564791336656</v>
       </c>
       <c r="DQ15" t="n">
-        <v>3.710207965923473e-05</v>
+        <v>0.001963802147656679</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.003005545819178224</v>
+        <v>0.0007655275985598564</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.001027116784825921</v>
+        <v>9.767936717253178e-05</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.001029228093102574</v>
+        <v>0.001991092693060637</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.001296888571232557</v>
+        <v>0.0006454467657022178</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.001093037542887032</v>
+        <v>0.003258587792515755</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0003206711262464523</v>
+        <v>0.0006296961801126599</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0006403340958058834</v>
+        <v>0.000649520312435925</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.002385349245741963</v>
+        <v>0.000976354000158608</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.002206029137596488</v>
+        <v>0.0004989369190298021</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.002200064714998007</v>
+        <v>0.001029783976264298</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.0009781577391549945</v>
+        <v>0.001074314233846962</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.000533978221938014</v>
+        <v>0.000525397714227438</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.0008971410570666194</v>
+        <v>0.004673500545322895</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.0002106415049638599</v>
+        <v>0.003591869492083788</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.0003225448890589178</v>
+        <v>0.0001636837550904602</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.003035681787878275</v>
+        <v>0.003751997370272875</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.0006912720273248851</v>
+        <v>0.000647246721200645</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.001387799740768969</v>
+        <v>0.002653178293257952</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.002088993787765503</v>
+        <v>0.0002283511566929519</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.002138220937922597</v>
+        <v>0.000715788803063333</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.000488641788251698</v>
+        <v>0.0001597860537003726</v>
       </c>
       <c r="EM15" t="n">
-        <v>3.945051139453426e-05</v>
+        <v>0.001008093589916825</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.0006255348562262952</v>
+        <v>0.0001785794738680124</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.0008532617357559502</v>
+        <v>5.70608681300655e-05</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.001519335433840752</v>
+        <v>0.003561917692422867</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.00241614761762321</v>
+        <v>0.0005249670357443392</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.0008604215690866113</v>
+        <v>0.002352216746658087</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.0003690695157274604</v>
+        <v>0.0002248395758215338</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.003268575295805931</v>
+        <v>0.0009395083761774004</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.000450761232059449</v>
+        <v>0.002476260764524341</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.0009459221037104726</v>
+        <v>0.0007087977137416601</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.0003950465470552444</v>
+        <v>0.001217168290168047</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.0002922171261161566</v>
+        <v>0.0003578427422326058</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.003071574959903955</v>
+        <v>0.004606673028320074</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.0001264122984139249</v>
+        <v>0.001121229957789183</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.001923387288115919</v>
+        <v>0.003669343655928969</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.0003083005722146481</v>
+        <v>0.0001393080165144056</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.001525341183878481</v>
+        <v>0.0009579889010637999</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.0004126274725422263</v>
+        <v>0.0004685870371758938</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.0001197671808768064</v>
+        <v>0.001129623386077583</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.001198499114252627</v>
+        <v>0.0007645898149348795</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.0001545578415971249</v>
+        <v>0.0007392527768388391</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.001855229260399938</v>
+        <v>0.001901640323922038</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.0006940005696378648</v>
+        <v>0.0003177910402882844</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.001306340796872973</v>
+        <v>0.001686940784566104</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.001583499368280172</v>
+        <v>0.001776572782546282</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.001289154170081019</v>
+        <v>0.00141236197669059</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.0004408745444379747</v>
+        <v>0.0005536373355425894</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.0003656661137938499</v>
+        <v>0.0008620197186246514</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.000970998196862638</v>
+        <v>0.001657933928072453</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0008940745610743761</v>
+        <v>7.70166952861473e-05</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.003880875883623958</v>
+        <v>0.004652415402233601</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.002185221528634429</v>
+        <v>0.0007401600596494973</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.003927616402506828</v>
+        <v>0.0007119489600881934</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.002308555645868182</v>
+        <v>0.001670072204433382</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0002274135185871273</v>
+        <v>0.0005389126599766314</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.0003438285202719271</v>
+        <v>0.001463845605030656</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.001344465301372111</v>
+        <v>0.000412488472647965</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.000752344960346818</v>
+        <v>0.002373252063989639</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.002792974933981895</v>
+        <v>0.001399918226525187</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.000679398828651756</v>
+        <v>0.002619842067360878</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.0002763630182016641</v>
+        <v>0.0003819187986664474</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.001454296871088445</v>
+        <v>0.001893415814265609</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.001501016900874674</v>
+        <v>0.002950346795842052</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.001550004701130092</v>
+        <v>0.001087843673303723</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.0045077302493155</v>
+        <v>0.002676088595762849</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.0005537302931770682</v>
+        <v>0.001498870784416795</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.0005979466950520873</v>
+        <v>0.0005592087400145829</v>
       </c>
     </row>
     <row r="16">
@@ -9534,1140 +9534,1140 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5.988532211631536e-05</v>
+        <v>0.0002718868490774184</v>
       </c>
       <c r="B17" t="n">
-        <v>0.03268299251794815</v>
+        <v>0.00657519418746233</v>
       </c>
       <c r="C17" t="n">
-        <v>0.003818913828581572</v>
+        <v>0.0007506870897486806</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01870683953166008</v>
+        <v>0.001637946115806699</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01964791491627693</v>
+        <v>0.001225475803948939</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01821006834506989</v>
+        <v>0.006871606688946486</v>
       </c>
       <c r="G17" t="n">
-        <v>0.005201333668082952</v>
+        <v>0.00109973712824285</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01230450719594955</v>
+        <v>0.002470135921612382</v>
       </c>
       <c r="I17" t="n">
-        <v>0.003014979651197791</v>
+        <v>0.0007298571872524917</v>
       </c>
       <c r="J17" t="n">
-        <v>0.001740600680932403</v>
+        <v>0.0003626523248385638</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0248603243380785</v>
+        <v>0.009361225180327892</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00148867757525295</v>
+        <v>0.0001216084929183125</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01097076572477818</v>
+        <v>0.002373711206018925</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01596936397254467</v>
+        <v>0.003040977055206895</v>
       </c>
       <c r="O17" t="n">
-        <v>0.02043700218200684</v>
+        <v>0.00704240333288908</v>
       </c>
       <c r="P17" t="n">
-        <v>0.004100301768630743</v>
+        <v>8.276346488855779e-05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.00346746388822794</v>
+        <v>1.409591641277075e-05</v>
       </c>
       <c r="R17" t="n">
-        <v>0.002699162112548947</v>
+        <v>0.002397235250100493</v>
       </c>
       <c r="S17" t="n">
-        <v>0.001593612949363887</v>
+        <v>0.0006649624556303024</v>
       </c>
       <c r="T17" t="n">
-        <v>0.005681770853698254</v>
+        <v>0.0001405768125550821</v>
       </c>
       <c r="U17" t="n">
-        <v>0.001544113270938396</v>
+        <v>0.0007802547770552337</v>
       </c>
       <c r="V17" t="n">
-        <v>0.005107109900563955</v>
+        <v>0.001422024797648191</v>
       </c>
       <c r="W17" t="n">
-        <v>0.003630452789366245</v>
+        <v>0.001660427777096629</v>
       </c>
       <c r="X17" t="n">
-        <v>0.003695289604365826</v>
+        <v>0.001314290449954569</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.003094506682828069</v>
+        <v>0.0003011787193827331</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.002168329898267984</v>
+        <v>0.001280798809602857</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.002404320053756237</v>
+        <v>0.0002133216476067901</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0001293562818318605</v>
+        <v>0.0009785752044990659</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.00379354483447969</v>
+        <v>0.0004024149384349585</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0005654734559357166</v>
+        <v>0.001173722092062235</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0008575802785344422</v>
+        <v>0.0004249580088071525</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0002476898953318596</v>
+        <v>0.002190816914662719</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.002347167115658522</v>
+        <v>0.001293121138587594</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.006346859037876129</v>
+        <v>0.0006665515247732401</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.003795115742832422</v>
+        <v>0.003092795610427856</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0009311676258221269</v>
+        <v>0.0003101894399151206</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.002788262907415628</v>
+        <v>0.0004445400554686785</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.00716632092371583</v>
+        <v>0.0002702614874579012</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0003522602200973779</v>
+        <v>0.001059566275216639</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.002029518596827984</v>
+        <v>0.001124519389122725</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.000742850941605866</v>
+        <v>0.001641946146264672</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.004609912168234587</v>
+        <v>0.0005856113275513053</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.0006250374717637897</v>
+        <v>0.0008333866135217249</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.003163773799315095</v>
+        <v>0.001830934430472553</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.004294182173907757</v>
+        <v>0.0006022081943228841</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.002371931681409478</v>
+        <v>0.001032511005178094</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.02328421734273434</v>
+        <v>0.006055913865566254</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.002975113224238157</v>
+        <v>0.001198730431497097</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.002401631092652678</v>
+        <v>0.0004503324453253299</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.006219160277396441</v>
+        <v>0.001984752481803298</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.01276369486004114</v>
+        <v>0.004209358710795641</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.001130530377849936</v>
+        <v>0.0003169048868585378</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.007725917734205723</v>
+        <v>0.0001580575626576319</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.001742888707667589</v>
+        <v>0.001022790791466832</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.00117568951100111</v>
+        <v>3.752188058570027e-05</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.005137959029525518</v>
+        <v>0.001160172512754798</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.004956343676894903</v>
+        <v>0.0001668984768912196</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.006182212848216295</v>
+        <v>0.0005189605290070176</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.01438376866281033</v>
+        <v>0.001380798406898975</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.002934315009042621</v>
+        <v>0.001030260464176536</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.00639435974881053</v>
+        <v>7.256821845658123e-05</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.005247815046459436</v>
+        <v>0.001809350331313908</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.002175224013626575</v>
+        <v>0.0007249605259858072</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.003739029169082642</v>
+        <v>0.0004475003806874156</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.006851437035948038</v>
+        <v>0.00256625865586102</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.003655557986348867</v>
+        <v>0.0001037833062582649</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0004345861962065101</v>
+        <v>0.0004312590463086963</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.001425317954272032</v>
+        <v>0.002147239865735173</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.003329742467030883</v>
+        <v>0.001578926108777523</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.007374019362032413</v>
+        <v>0.002482865005731583</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.0006645384710282087</v>
+        <v>0.0002145181642845273</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.003549619577825069</v>
+        <v>0.001249078311957419</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.002470785519108176</v>
+        <v>0.0007593195769004524</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.01377809047698975</v>
+        <v>0.003905352437868714</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.007243089377880096</v>
+        <v>8.360686479136348e-05</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.00266575813293457</v>
+        <v>0.001347670913673937</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.004991321824491024</v>
+        <v>0.0002408786676824093</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.001525407191365957</v>
+        <v>0.001701013650745153</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.002128583146259189</v>
+        <v>0.0004565756826195866</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.001974644372239709</v>
+        <v>8.33206286188215e-05</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.002164200413972139</v>
+        <v>0.0004027833929285407</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0002962659345939755</v>
+        <v>0.0004294801328796893</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.005198362283408642</v>
+        <v>0.001780638936907053</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.00233805738389492</v>
+        <v>0.0002551147772464901</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.002013359218835831</v>
+        <v>3.186601679772139e-05</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0007904777303338051</v>
+        <v>0.0002684962237253785</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.003573440946638584</v>
+        <v>0.001980086555704474</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.003181030042469501</v>
+        <v>0.0008104186854325235</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.002374810166656971</v>
+        <v>0.00024449682678096</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.00127364310901612</v>
+        <v>0.0003048217622563243</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.005298368632793427</v>
+        <v>0.0004309983341954648</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.001347425626590848</v>
+        <v>0.003101963782683015</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0009106002980843186</v>
+        <v>0.001630445476621389</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.005396724678575993</v>
+        <v>9.982060873880982e-06</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0003968812525272369</v>
+        <v>0.001727956812828779</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.001142933848313987</v>
+        <v>0.0003738427185453475</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.006429056636989117</v>
+        <v>0.0002427065483061597</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.004309173673391342</v>
+        <v>0.0002039815008174628</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0008437167853116989</v>
+        <v>0.0009818371618166566</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0004352822143118829</v>
+        <v>2.668880915734917e-05</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.003848807653412223</v>
+        <v>0.001768010202795267</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.002891112817451358</v>
+        <v>8.529085607733577e-05</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.00363480718806386</v>
+        <v>0.000212077284231782</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0001679408887866884</v>
+        <v>0.0002644315827637911</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.004278830718249083</v>
+        <v>0.002058499492704868</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.002946668770164251</v>
+        <v>0.000316060904879123</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.00312467385083437</v>
+        <v>0.0003070739039685577</v>
       </c>
       <c r="DD17" t="n">
-        <v>9.167846292257309e-05</v>
+        <v>0.0004142795514781028</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.004267334472388029</v>
+        <v>0.000500543275848031</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.002560286317020655</v>
+        <v>0.003043909091502428</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.0008172300877049565</v>
+        <v>0.00129329867195338</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.0155047420412302</v>
+        <v>0.002221392467617989</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.0008868160075508058</v>
+        <v>0.0007215368095785379</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.0009178534965030849</v>
+        <v>0.0004492122679948807</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.004493433516472578</v>
+        <v>0.0001794266572687775</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.003957700915634632</v>
+        <v>0.001239547971636057</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.003158959560096264</v>
+        <v>0.0003672636521514505</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.0002783759264275432</v>
+        <v>0.002153533976525068</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.0006724775303155184</v>
+        <v>0.001333571271970868</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.001095839077606797</v>
+        <v>0.0008400552324019372</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.004295134916901588</v>
+        <v>0.00135450589004904</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.001280661439523101</v>
+        <v>0.001253855763934553</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.004423314705491066</v>
+        <v>3.254537296015769e-05</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.001218249904923141</v>
+        <v>2.738295734161511e-05</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.0009747186559252441</v>
+        <v>0.001523182028904557</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.001004169462248683</v>
+        <v>0.0001307235070271417</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.001405076938681304</v>
+        <v>0.001528149005025625</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0002432115143164992</v>
+        <v>0.0006521256873384118</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.004571765195578337</v>
+        <v>0.0005425096023827791</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.001863565063104033</v>
+        <v>0.0001067907433025539</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.00281078414991498</v>
+        <v>0.00014459528028965</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.001625244738534093</v>
+        <v>0.001518606091849506</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.002223071875050664</v>
+        <v>0.0008018314838409424</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.001248568296432495</v>
+        <v>8.190429798560217e-05</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.0003122653579339385</v>
+        <v>0.001331485458649695</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.001642562914639711</v>
+        <v>0.0003713886835612357</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.00494448421522975</v>
+        <v>0.0001657545508351177</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.002053396543487906</v>
+        <v>0.001106324372813106</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.002994611393660307</v>
+        <v>0.0001240827259607613</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.004463952034711838</v>
+        <v>0.0004439954645931721</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.001526825129985809</v>
+        <v>0.002383207436650991</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.005285266786813736</v>
+        <v>0.0004364391206763685</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0005790558061562479</v>
+        <v>9.806419257074594e-06</v>
       </c>
       <c r="EN17" t="n">
-        <v>4.867900861427188e-05</v>
+        <v>0.0001778849109541625</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0005575019167736173</v>
+        <v>0.0005914181238040328</v>
       </c>
       <c r="EP17" t="n">
-        <v>6.808076432207599e-05</v>
+        <v>0.0006226695841178298</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.005564062856137753</v>
+        <v>0.001304591656662524</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.003330509178340435</v>
+        <v>0.0004999124212190509</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0008007044671103358</v>
+        <v>0.001492196694016457</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.00551263615489006</v>
+        <v>0.0007827925146557391</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.003277468029409647</v>
+        <v>0.000115114038635511</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.006153156980872154</v>
+        <v>0.0003457067941781133</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0007009640103206038</v>
+        <v>0.000189427169971168</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.0002450029132887721</v>
+        <v>0.0002657831064425409</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.003483354346826673</v>
+        <v>0.002163160126656294</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.002077571349218488</v>
+        <v>0.0001713141246000305</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.003071960061788559</v>
+        <v>0.0001609012251719832</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.0005967302713543177</v>
+        <v>0.0001200405386043712</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.003726623021066189</v>
+        <v>0.001786944107152522</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.003874916350468993</v>
+        <v>0.0008077452075667679</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.003303063334897161</v>
+        <v>0.000351552153006196</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.001581275020726025</v>
+        <v>7.999305671546608e-05</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0009064105688594282</v>
+        <v>0.0002322860527783632</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.003694281913340092</v>
+        <v>0.001843083999119699</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.004952961578965187</v>
+        <v>0.001840813783928752</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.006218309979885817</v>
+        <v>0.001145200221799314</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.001470986753702164</v>
+        <v>0.0005675465799868107</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.002221320755779743</v>
+        <v>0.0008018548833206296</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.002240182599052787</v>
+        <v>0.0007189242169260979</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.001920191920362413</v>
+        <v>0.002208483871072531</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.002868086099624634</v>
+        <v>0.001810788759030402</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.002223776653409004</v>
+        <v>0.0005760350031778216</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.004326937720179558</v>
+        <v>0.0006275997729972005</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.001872768276371062</v>
+        <v>0.00331807741895318</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.002724850084632635</v>
+        <v>0.001907602651044726</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.003809133777394891</v>
+        <v>0.0001388556265737861</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.002721362747251987</v>
+        <v>0.0009491792879998684</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.005993733182549477</v>
+        <v>6.679979560431093e-05</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0006562276976183057</v>
+        <v>0.001880174851976335</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0004730259533971548</v>
+        <v>0.0003980283509008586</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.005487458780407906</v>
+        <v>0.0008917329832911491</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.00141804083250463</v>
+        <v>0.000124426675029099</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.002181224059313536</v>
+        <v>0.0007738608401268721</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.00338148744776845</v>
+        <v>0.000513820443302393</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.00237049488350749</v>
+        <v>0.001042539137415588</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.00478374445810914</v>
+        <v>0.002225246280431747</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.01491521019488573</v>
+        <v>0.000324500841088593</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.0007837166776880622</v>
+        <v>0.001359458430670202</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0007229852490127087</v>
+        <v>0.0007177873631007969</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.001868358114734292</v>
+        <v>4.588956471707206e-06</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01907926984131336</v>
+        <v>9.22333711059764e-05</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001540365628898144</v>
+        <v>1.654797415540088e-05</v>
       </c>
       <c r="D18" t="n">
-        <v>0.005545707419514656</v>
+        <v>3.288274456281215e-06</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01875437796115875</v>
+        <v>1.3981034499011e-05</v>
       </c>
       <c r="F18" t="n">
-        <v>0.001704735681414604</v>
+        <v>9.411264909431338e-05</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002544384682551026</v>
+        <v>1.29010859382106e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.003813860239461064</v>
+        <v>2.938389479822945e-05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001195999444462359</v>
+        <v>1.983207403100096e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.003179162042215466</v>
+        <v>1.226606946147513e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01758156158030033</v>
+        <v>0.0001418719039065763</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003441810607910156</v>
+        <v>6.561382178915665e-06</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0007711196085438132</v>
+        <v>2.080457852571271e-05</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01468040607869625</v>
+        <v>5.133448576088995e-05</v>
       </c>
       <c r="O18" t="n">
-        <v>0.001914982218295336</v>
+        <v>0.000104024526081048</v>
       </c>
       <c r="P18" t="n">
-        <v>0.001269083237275481</v>
+        <v>1.947571217897348e-05</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0001265883765881881</v>
+        <v>3.974182982346974e-05</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0004998292424716055</v>
+        <v>5.67648748983629e-05</v>
       </c>
       <c r="S18" t="n">
-        <v>0.001223323866724968</v>
+        <v>9.344246791442856e-06</v>
       </c>
       <c r="T18" t="n">
-        <v>0.003872070927172899</v>
+        <v>1.478854301240062e-07</v>
       </c>
       <c r="U18" t="n">
-        <v>0.001956816762685776</v>
+        <v>1.944369432749227e-05</v>
       </c>
       <c r="V18" t="n">
-        <v>0.002261254470795393</v>
+        <v>2.965302155644167e-05</v>
       </c>
       <c r="W18" t="n">
-        <v>0.002729518339037895</v>
+        <v>2.649027737788856e-05</v>
       </c>
       <c r="X18" t="n">
-        <v>0.003765742992982268</v>
+        <v>2.475638575560879e-05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.0007509642746299505</v>
+        <v>5.8365708355268e-06</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.001144548412412405</v>
+        <v>3.017986455233768e-05</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0007156524807214737</v>
+        <v>2.793428848235635e-06</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0002434845082461834</v>
+        <v>4.939123027725145e-05</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0006420168210752308</v>
+        <v>8.910330507205799e-06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.003964074421674013</v>
+        <v>1.348629029962467e-05</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0005710539408028126</v>
+        <v>2.342966399737634e-05</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.431046545505524e-05</v>
+        <v>5.270725523587316e-05</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.001242653816007078</v>
+        <v>2.50107841566205e-05</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.004183072131127119</v>
+        <v>1.728410279611126e-05</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.002972678979858756</v>
+        <v>5.488705937750638e-05</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002130237873643637</v>
+        <v>4.36916252510855e-06</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.001233736169524491</v>
+        <v>2.902162577811396e-06</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.005390484817326069</v>
+        <v>5.001684257877059e-07</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.002614794299006462</v>
+        <v>1.852707100624684e-05</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.001309618353843689</v>
+        <v>2.006098111451138e-05</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.001073931576684117</v>
+        <v>3.906232450390235e-05</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.001637896755710244</v>
+        <v>9.761091860127635e-06</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.0003366887103766203</v>
+        <v>1.408396747137886e-05</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.001334401895292103</v>
+        <v>3.554454451659694e-05</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.001240673009306192</v>
+        <v>1.273681755264988e-05</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.001622179406695068</v>
+        <v>1.924086063809227e-05</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.01248898357152939</v>
+        <v>0.0001255456008948386</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.0005090758786536753</v>
+        <v>1.267837615159806e-05</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.001867626560851932</v>
+        <v>2.32885713558062e-06</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.004530047066509724</v>
+        <v>3.161218774039298e-05</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.004436714574694633</v>
+        <v>6.465442129410803e-05</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.002429546788334846</v>
+        <v>9.907173080136999e-06</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.0015127242077142</v>
+        <v>1.40941974677844e-05</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.003176409751176834</v>
+        <v>3.208042471669614e-05</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.003282630816102028</v>
+        <v>2.821602538460866e-05</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.004506552126258612</v>
+        <v>2.462230895616813e-06</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.001254680682905018</v>
+        <v>2.239677087345626e-06</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.002897637896239758</v>
+        <v>1.037187757901847e-05</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.01049045938998461</v>
+        <v>3.909154838765971e-05</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.0008755550952628255</v>
+        <v>1.303221324633341e-06</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.002423177473247051</v>
+        <v>5.4836082199472e-06</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.0005545111489482224</v>
+        <v>3.631237632362172e-05</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.001593811437487602</v>
+        <v>8.555728527426254e-06</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.004907042253762484</v>
+        <v>8.27591065899469e-06</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.001859112526290119</v>
+        <v>5.026133294450119e-05</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.001763645326718688</v>
+        <v>2.404667611699551e-06</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.001652334467507899</v>
+        <v>1.068318670149893e-05</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.0003839405253529549</v>
+        <v>5.010962195228785e-05</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.001525735249742866</v>
+        <v>2.581465741968714e-05</v>
       </c>
       <c r="BR18" t="n">
-        <v>0.0006914493860676885</v>
+        <v>4.411808549775742e-05</v>
       </c>
       <c r="BS18" t="n">
-        <v>0.0006117835291661322</v>
+        <v>5.838057859364199e-06</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.001518276520073414</v>
+        <v>3.181899592163973e-05</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.002235827269032598</v>
+        <v>7.667917088838294e-06</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.009703360497951508</v>
+        <v>6.290552846621722e-05</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.0025981564540416</v>
+        <v>4.980543053534348e-06</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.0003139548352919519</v>
+        <v>3.990075492765754e-05</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.002343738451600075</v>
+        <v>1.156721646111691e-05</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.003129023592919111</v>
+        <v>3.965308133047074e-05</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.001650654128752649</v>
+        <v>6.72081705488381e-06</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.000248376396484673</v>
+        <v>3.896834641636815e-06</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.0002418282383587211</v>
+        <v>1.249124034075066e-05</v>
       </c>
       <c r="CD18" t="n">
-        <v>0.0002340218925382942</v>
+        <v>1.702853114693426e-05</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.003489542519673705</v>
+        <v>2.691790723474696e-05</v>
       </c>
       <c r="CF18" t="n">
-        <v>0.0007564617553725839</v>
+        <v>9.174805200018454e-06</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.001388922333717346</v>
+        <v>8.2669384937617e-07</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.00222389679402113</v>
+        <v>1.871556946753117e-06</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.0004985008854418993</v>
+        <v>2.989989116031211e-05</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.001971443183720112</v>
+        <v>1.469396011088975e-05</v>
       </c>
       <c r="CK18" t="n">
-        <v>0.0002120517892763019</v>
+        <v>1.526147343611228e-06</v>
       </c>
       <c r="CL18" t="n">
-        <v>0.0004625782603397965</v>
+        <v>5.54216603632085e-06</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.003190324641764164</v>
+        <v>6.087891961215064e-06</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.002711273496970534</v>
+        <v>6.56746924505569e-05</v>
       </c>
       <c r="CO18" t="n">
-        <v>0.0004508609999902546</v>
+        <v>1.429235817340668e-05</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.0008500164840370417</v>
+        <v>5.580403922067489e-06</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.001230893423780799</v>
+        <v>4.413017813931219e-05</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.0006437713745981455</v>
+        <v>1.098634129448328e-05</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.005598620977252722</v>
+        <v>5.423223228717688e-06</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.003902738681063056</v>
+        <v>1.102387068385724e-05</v>
       </c>
       <c r="CU18" t="n">
-        <v>0.001275037531740963</v>
+        <v>5.975091426080326e-06</v>
       </c>
       <c r="CV18" t="n">
-        <v>0.0002848667500074953</v>
+        <v>1.094193430617452e-05</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.002794575178995728</v>
+        <v>2.53081616392592e-05</v>
       </c>
       <c r="CX18" t="n">
-        <v>0.0001696334948064759</v>
+        <v>5.795966899313498e-06</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.001752035808749497</v>
+        <v>6.238904461497441e-06</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.001855366746895015</v>
+        <v>1.307898401137209e-06</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.001440905150957406</v>
+        <v>3.092040788033046e-05</v>
       </c>
       <c r="DB18" t="n">
-        <v>0.001382732763886452</v>
+        <v>5.34097125637345e-06</v>
       </c>
       <c r="DC18" t="n">
-        <v>0.0001245869207195938</v>
+        <v>5.161977242096327e-06</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.0007110086735337973</v>
+        <v>6.29036185273435e-06</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.002575914142653346</v>
+        <v>8.811546649667434e-06</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.002715694718062878</v>
+        <v>4.285712930141017e-05</v>
       </c>
       <c r="DG18" t="n">
-        <v>0.0008399218204431236</v>
+        <v>2.122233854606748e-05</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.005661932751536369</v>
+        <v>1.784334199328441e-05</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.00400746101513505</v>
+        <v>1.477557088946924e-05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.0001636820961721241</v>
+        <v>5.038318704464473e-06</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.002980534918606281</v>
+        <v>1.939490357472096e-05</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.0001085316762328148</v>
+        <v>1.941753362189047e-05</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.0008909180760383606</v>
+        <v>1.201785744342487e-05</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.0001516244083177298</v>
+        <v>1.886347672552802e-05</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.001379713416099548</v>
+        <v>1.445260113541735e-05</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.0003288424341008067</v>
+        <v>1.309517392655835e-05</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0.003225723747164011</v>
+        <v>3.174555604346097e-05</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.002017799997702241</v>
+        <v>1.824784885684494e-05</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.00425548292696476</v>
+        <v>4.941762654198101e-06</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.0001662315626163036</v>
+        <v>1.314657311013434e-05</v>
       </c>
       <c r="DU18" t="n">
-        <v>0.0003000286815222353</v>
+        <v>3.712987745529972e-05</v>
       </c>
       <c r="DV18" t="n">
-        <v>0.0003852151276078075</v>
+        <v>1.1840735169244e-05</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.0001111176388803869</v>
+        <v>1.906005491036922e-05</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.00114134477917105</v>
+        <v>1.222533956024563e-05</v>
       </c>
       <c r="DY18" t="n">
-        <v>0.001403310219757259</v>
+        <v>3.303575795143843e-07</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.0009590404806658626</v>
+        <v>8.440010788035579e-06</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.001283169258385897</v>
+        <v>3.416459094296442e-06</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.002241955371573567</v>
+        <v>2.076924465654884e-05</v>
       </c>
       <c r="EC18" t="n">
-        <v>0.002312714233994484</v>
+        <v>6.146722171251895e-06</v>
       </c>
       <c r="ED18" t="n">
-        <v>0.001938973786309361</v>
+        <v>7.849658686609473e-06</v>
       </c>
       <c r="EE18" t="n">
-        <v>0.000496039807330817</v>
+        <v>2.346802830288652e-05</v>
       </c>
       <c r="EF18" t="n">
-        <v>0.000356737116817385</v>
+        <v>1.655285450397059e-05</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.003650984959676862</v>
+        <v>1.793923843251832e-06</v>
       </c>
       <c r="EH18" t="n">
-        <v>0.0002333156880922616</v>
+        <v>1.674623672442976e-05</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.001847562496550381</v>
+        <v>2.223240699095186e-06</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.002236375352367759</v>
+        <v>1.490346585342195e-05</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.001241148915141821</v>
+        <v>2.450202737236395e-05</v>
       </c>
       <c r="EL18" t="n">
-        <v>0.00110229616984725</v>
+        <v>6.442004178097704e-06</v>
       </c>
       <c r="EM18" t="n">
-        <v>0.0002713389112614095</v>
+        <v>4.757735496241366e-06</v>
       </c>
       <c r="EN18" t="n">
-        <v>0.000481784634757787</v>
+        <v>3.544840183167253e-06</v>
       </c>
       <c r="EO18" t="n">
-        <v>0.000754836481064558</v>
+        <v>1.442162192688556e-05</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.0006734998896718025</v>
+        <v>5.534261617867742e-06</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0.002472878433763981</v>
+        <v>3.787702098634327e-06</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.001730471849441528</v>
+        <v>1.222634364239639e-05</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.0002202798204962164</v>
+        <v>2.189445694966707e-05</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.003377736313268542</v>
+        <v>2.284411493747029e-05</v>
       </c>
       <c r="EU18" t="n">
-        <v>0.0005079705151729286</v>
+        <v>1.124154186982196e-05</v>
       </c>
       <c r="EV18" t="n">
-        <v>0.001298381481319666</v>
+        <v>8.851293387124315e-06</v>
       </c>
       <c r="EW18" t="n">
-        <v>0.0004585630376823246</v>
+        <v>1.201266513817245e-05</v>
       </c>
       <c r="EX18" t="n">
-        <v>7.880007615312934e-05</v>
+        <v>1.271090422960697e-05</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.002546495059505105</v>
+        <v>3.413713784539141e-05</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0.0003716435167007148</v>
+        <v>6.823912372055929e-06</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.001394887804053724</v>
+        <v>1.958917437150376e-06</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.001969685778021812</v>
+        <v>4.55740928373416e-06</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.001478738151490688</v>
+        <v>2.432711153232958e-05</v>
       </c>
       <c r="FD18" t="n">
-        <v>0.001683633192442358</v>
+        <v>1.538006472401321e-05</v>
       </c>
       <c r="FE18" t="n">
-        <v>0.00017637072596699</v>
+        <v>5.220114871917758e-06</v>
       </c>
       <c r="FF18" t="n">
-        <v>0.0001272141234949231</v>
+        <v>3.458586206761538e-06</v>
       </c>
       <c r="FG18" t="n">
-        <v>0.0007217630045488477</v>
+        <v>6.985671916481806e-06</v>
       </c>
       <c r="FH18" t="n">
-        <v>0.003387715667486191</v>
+        <v>3.167155227856711e-05</v>
       </c>
       <c r="FI18" t="n">
-        <v>0.001245611230842769</v>
+        <v>2.079654950648546e-05</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0.003398572327569127</v>
+        <v>1.868993058451451e-05</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.0003287341096438468</v>
+        <v>9.863970262813382e-07</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.0003838349948637187</v>
+        <v>2.713487629080191e-05</v>
       </c>
       <c r="FM18" t="n">
-        <v>4.455746238818392e-05</v>
+        <v>1.738628634484485e-05</v>
       </c>
       <c r="FN18" t="n">
-        <v>0.0005159616703167558</v>
+        <v>3.941205432056449e-05</v>
       </c>
       <c r="FO18" t="n">
-        <v>0.0001732304226607084</v>
+        <v>2.549030250520445e-05</v>
       </c>
       <c r="FP18" t="n">
-        <v>0.001934519968926907</v>
+        <v>5.371685347199673e-06</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.001903286203742027</v>
+        <v>1.102864644053625e-06</v>
       </c>
       <c r="FR18" t="n">
-        <v>0.0005562585429288447</v>
+        <v>4.260585774318315e-05</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.002330770483240485</v>
+        <v>4.521767550613731e-05</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.002587532624602318</v>
+        <v>2.911583578679711e-07</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.0007147063734009862</v>
+        <v>1.995173442992382e-05</v>
       </c>
       <c r="FV18" t="n">
-        <v>0.002111323177814484</v>
+        <v>1.880045601865277e-05</v>
       </c>
       <c r="FW18" t="n">
-        <v>0.001663683331571519</v>
+        <v>6.204715464264154e-05</v>
       </c>
       <c r="FX18" t="n">
-        <v>0.002482863608747721</v>
+        <v>4.243836156092584e-05</v>
       </c>
       <c r="FY18" t="n">
-        <v>0.0006232368759810925</v>
+        <v>2.180940646212548e-05</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.0009500138112343848</v>
+        <v>1.209326728712767e-05</v>
       </c>
       <c r="GA18" t="n">
-        <v>0.004998625256121159</v>
+        <v>1.494343177910196e-05</v>
       </c>
       <c r="GB18" t="n">
-        <v>0.001920207170769572</v>
+        <v>3.249190740461927e-06</v>
       </c>
       <c r="GC18" t="n">
-        <v>0.0004966847482137382</v>
+        <v>3.413872764213011e-05</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.003765806322917342</v>
+        <v>4.612101474776864e-05</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.003828572109341621</v>
+        <v>7.872134119679686e-06</v>
       </c>
       <c r="GF18" t="n">
-        <v>0.001328870072029531</v>
+        <v>2.222741750301793e-05</v>
       </c>
       <c r="GG18" t="n">
-        <v>0.0002225809148512781</v>
+        <v>2.540943205531221e-05</v>
       </c>
     </row>
     <row r="19">
